--- a/outputs/layered-payroll-20261016/主播月度薪酬核算示例.xlsx
+++ b/outputs/layered-payroll-20261016/主播月度薪酬核算示例.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工月薪汇总" sheetId="1" r:id="R9b2467696f674e40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度核算明细" sheetId="2" r:id="R11609d2e1ab248b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐规则计算" sheetId="3" r:id="R4fc901bc3a654fb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工月薪汇总" sheetId="1" r:id="R15bfad0c00934ad1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度核算明细" sheetId="2" r:id="R11a022c0ed924f55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐规则计算" sheetId="3" r:id="R0016c894292b4dc4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -960,7 +960,7 @@
       <x:c r="H10" s="107"/>
       <x:c r="I10" s="107"/>
     </x:row>
-    <x:row r="11" ht="28" customHeight="1">
+    <x:row r="11" ht="12" customHeight="1">
       <x:c r="A11" s="3"/>
       <x:c r="B11" s="3"/>
       <x:c r="C11" s="107"/>
@@ -971,7 +971,7 @@
       <x:c r="H11" s="107"/>
       <x:c r="I11" s="107"/>
     </x:row>
-    <x:row r="12" ht="28" customHeight="1">
+    <x:row r="12" ht="12" customHeight="1">
       <x:c r="A12" s="3"/>
       <x:c r="B12" s="3"/>
       <x:c r="C12" s="107"/>
@@ -982,7 +982,7 @@
       <x:c r="H12" s="107"/>
       <x:c r="I12" s="107"/>
     </x:row>
-    <x:row r="13" ht="28" customHeight="1">
+    <x:row r="13" ht="12" customHeight="1">
       <x:c r="A13" s="3"/>
       <x:c r="B13" s="3"/>
       <x:c r="C13" s="107"/>
@@ -1026,25 +1026,25 @@
       <x:c r="B16" s="64" t="str">
         <x:v>直播间</x:v>
       </x:c>
-      <x:c r="C16" s="112" t="str">
+      <x:c r="C16" s="64" t="str">
         <x:v>三类保底最大值</x:v>
       </x:c>
-      <x:c r="D16" s="112" t="str">
+      <x:c r="D16" s="64" t="str">
         <x:v>三类加成合计</x:v>
       </x:c>
-      <x:c r="E16" s="112" t="str">
+      <x:c r="E16" s="64" t="str">
         <x:v>总补贴</x:v>
       </x:c>
-      <x:c r="F16" s="112" t="str">
+      <x:c r="F16" s="64" t="str">
         <x:v>总计月薪</x:v>
       </x:c>
-      <x:c r="G16" s="112" t="str">
+      <x:c r="G16" s="64" t="str">
         <x:v>有效总保费</x:v>
       </x:c>
-      <x:c r="H16" s="112" t="str">
+      <x:c r="H16" s="64" t="str">
         <x:v>有效ROI</x:v>
       </x:c>
-      <x:c r="I16" s="113" t="str">
+      <x:c r="I16" s="65" t="str">
         <x:v>同房主播排名</x:v>
       </x:c>
     </x:row>

--- a/outputs/layered-payroll-20261016/主播月度薪酬核算示例.xlsx
+++ b/outputs/layered-payroll-20261016/主播月度薪酬核算示例.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工月薪汇总" sheetId="1" r:id="R15bfad0c00934ad1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度核算明细" sheetId="2" r:id="R11a022c0ed924f55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐规则计算" sheetId="3" r:id="R0016c894292b4dc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工月薪汇总" sheetId="1" r:id="R1dae1ec5850040b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度核算明细" sheetId="2" r:id="R659c32a78bc341ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐规则计算" sheetId="3" r:id="Ra03d76b14aa24925"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,12 +18,12 @@
   <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="yyyy-mm"/>
-    <x:numFmt numFmtId="202" formatCode="#,##0.00;[Red](#,##0.00);&quot;—&quot;"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0;[Red](#,##0);&quot;—&quot;"/>
+    <x:numFmt numFmtId="202" formatCode="#,##0.00;[Red](#,##0.00);0.00"/>
+    <x:numFmt numFmtId="203" formatCode="#,##0;[Red](#,##0);0"/>
     <x:numFmt numFmtId="204" formatCode="0.0"/>
     <x:numFmt numFmtId="205" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -63,18 +63,13 @@
       <x:name val="Arial"/>
     </x:font>
     <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF8994A1"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
       <x:b/>
       <x:sz val="10"/>
       <x:color rgb="FF24364B"/>
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -99,11 +94,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF6C5A84"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF976C28"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -193,7 +183,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="122">
+  <x:cellXfs count="105">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -358,58 +348,22 @@
     <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -418,16 +372,16 @@
     <x:xf numFmtId="202" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -442,64 +396,49 @@
     <x:xf numFmtId="202" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="203" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="8" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="7" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="203" fontId="8" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="7" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -514,46 +453,46 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="8" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="7" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="8" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="7" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="204" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="204" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="204" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="205" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="205" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="204" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="205" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="205" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -832,22 +771,22 @@
       <x:c r="I5" s="3"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="63" t="str">
+      <x:c r="A6" s="51" t="str">
         <x:v>员工名称</x:v>
       </x:c>
-      <x:c r="B6" s="64" t="str">
+      <x:c r="B6" s="52" t="str">
         <x:v>员工ID</x:v>
       </x:c>
-      <x:c r="C6" s="64" t="str">
+      <x:c r="C6" s="52" t="str">
         <x:v>核算行数</x:v>
       </x:c>
-      <x:c r="D6" s="64" t="str">
+      <x:c r="D6" s="52" t="str">
         <x:v>总补贴</x:v>
       </x:c>
-      <x:c r="E6" s="64" t="str">
+      <x:c r="E6" s="52" t="str">
         <x:v>系数后总保费</x:v>
       </x:c>
-      <x:c r="F6" s="65" t="str">
+      <x:c r="F6" s="53" t="str">
         <x:v>总计月薪</x:v>
       </x:c>
       <x:c r="G6" s="3"/>
@@ -861,52 +800,52 @@
       <x:c r="B7" s="3" t="str">
         <x:v>example-lin</x:v>
       </x:c>
-      <x:c r="C7" s="105" t="n">
+      <x:c r="C7" s="88" t="n">
         <x:f>COUNTIFS('月度核算明细'!$A$7:$A$10,B7)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="83" t="n">
+      <x:c r="D7" s="71" t="n">
+        <x:f>SUMIFS('月度核算明细'!$AR$7:$AR$10,'月度核算明细'!$A$7:$A$10,B7)</x:f>
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="E7" s="71" t="n">
+        <x:f>SUMIFS('月度核算明细'!$AS$7:$AS$10,'月度核算明细'!$A$7:$A$10,B7)</x:f>
+        <x:v>49000</x:v>
+      </x:c>
+      <x:c r="F7" s="89" t="n">
         <x:f>SUMIFS('月度核算明细'!$AT$7:$AT$10,'月度核算明细'!$A$7:$A$10,B7)</x:f>
-        <x:v>530</x:v>
-      </x:c>
-      <x:c r="E7" s="83" t="n">
-        <x:f>SUMIFS('月度核算明细'!$AU$7:$AU$10,'月度核算明细'!$A$7:$A$10,B7)</x:f>
-        <x:v>49000</x:v>
-      </x:c>
-      <x:c r="F7" s="106" t="n">
-        <x:f>SUMIFS('月度核算明细'!$AV$7:$AV$10,'月度核算明细'!$A$7:$A$10,B7)</x:f>
         <x:v>9530</x:v>
       </x:c>
-      <x:c r="G7" s="107"/>
-      <x:c r="H7" s="107"/>
-      <x:c r="I7" s="107"/>
+      <x:c r="G7" s="90"/>
+      <x:c r="H7" s="90"/>
+      <x:c r="I7" s="90"/>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
-      <x:c r="A8" s="67" t="str">
+      <x:c r="A8" s="55" t="str">
         <x:v>周宁</x:v>
       </x:c>
-      <x:c r="B8" s="67" t="str">
+      <x:c r="B8" s="55" t="str">
         <x:v>example-zhou</x:v>
       </x:c>
-      <x:c r="C8" s="108" t="n">
+      <x:c r="C8" s="91" t="n">
         <x:f>COUNTIFS('月度核算明细'!$A$7:$A$10,B8)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D8" s="87" t="n">
+      <x:c r="D8" s="75" t="n">
+        <x:f>SUMIFS('月度核算明细'!$AR$7:$AR$10,'月度核算明细'!$A$7:$A$10,B8)</x:f>
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E8" s="75" t="n">
+        <x:f>SUMIFS('月度核算明细'!$AS$7:$AS$10,'月度核算明细'!$A$7:$A$10,B8)</x:f>
+        <x:v>28000</x:v>
+      </x:c>
+      <x:c r="F8" s="92" t="n">
         <x:f>SUMIFS('月度核算明细'!$AT$7:$AT$10,'月度核算明细'!$A$7:$A$10,B8)</x:f>
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="E8" s="87" t="n">
-        <x:f>SUMIFS('月度核算明细'!$AU$7:$AU$10,'月度核算明细'!$A$7:$A$10,B8)</x:f>
-        <x:v>28000</x:v>
-      </x:c>
-      <x:c r="F8" s="109" t="n">
-        <x:f>SUMIFS('月度核算明细'!$AV$7:$AV$10,'月度核算明细'!$A$7:$A$10,B8)</x:f>
-        <x:v>4120</x:v>
-      </x:c>
-      <x:c r="G8" s="107"/>
-      <x:c r="H8" s="107"/>
-      <x:c r="I8" s="107"/>
+        <x:v>4595</x:v>
+      </x:c>
+      <x:c r="G8" s="90"/>
+      <x:c r="H8" s="90"/>
+      <x:c r="I8" s="90"/>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
       <x:c r="A9" s="3" t="str">
@@ -915,136 +854,136 @@
       <x:c r="B9" s="3" t="str">
         <x:v>example-chen</x:v>
       </x:c>
-      <x:c r="C9" s="105" t="n">
+      <x:c r="C9" s="88" t="n">
         <x:f>COUNTIFS('月度核算明细'!$A$7:$A$10,B9)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D9" s="83" t="n">
+      <x:c r="D9" s="71" t="n">
+        <x:f>SUMIFS('月度核算明细'!$AR$7:$AR$10,'月度核算明细'!$A$7:$A$10,B9)</x:f>
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="E9" s="71" t="n">
+        <x:f>SUMIFS('月度核算明细'!$AS$7:$AS$10,'月度核算明细'!$A$7:$A$10,B9)</x:f>
+        <x:v>36000</x:v>
+      </x:c>
+      <x:c r="F9" s="89" t="n">
         <x:f>SUMIFS('月度核算明细'!$AT$7:$AT$10,'月度核算明细'!$A$7:$A$10,B9)</x:f>
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="E9" s="83" t="n">
-        <x:f>SUMIFS('月度核算明细'!$AU$7:$AU$10,'月度核算明细'!$A$7:$A$10,B9)</x:f>
-        <x:v>36000</x:v>
-      </x:c>
-      <x:c r="F9" s="106" t="n">
-        <x:f>SUMIFS('月度核算明细'!$AV$7:$AV$10,'月度核算明细'!$A$7:$A$10,B9)</x:f>
         <x:v>4565</x:v>
       </x:c>
-      <x:c r="G9" s="107"/>
-      <x:c r="H9" s="107"/>
-      <x:c r="I9" s="107"/>
+      <x:c r="G9" s="90"/>
+      <x:c r="H9" s="90"/>
+      <x:c r="I9" s="90"/>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
-      <x:c r="A10" s="97" t="str">
+      <x:c r="A10" s="80" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B10" s="97"/>
-      <x:c r="C10" s="110" t="n">
+      <x:c r="B10" s="80"/>
+      <x:c r="C10" s="93" t="n">
         <x:f>SUM(C7:C9)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D10" s="111" t="n">
+      <x:c r="D10" s="94" t="n">
         <x:f>SUM(D7:D9)</x:f>
-        <x:v>815</x:v>
-      </x:c>
-      <x:c r="E10" s="111" t="n">
+        <x:v>890</x:v>
+      </x:c>
+      <x:c r="E10" s="94" t="n">
         <x:f>SUM(E7:E9)</x:f>
         <x:v>113000</x:v>
       </x:c>
-      <x:c r="F10" s="111" t="n">
+      <x:c r="F10" s="94" t="n">
         <x:f>SUM(F7:F9)</x:f>
-        <x:v>18215</x:v>
-      </x:c>
-      <x:c r="G10" s="107"/>
-      <x:c r="H10" s="107"/>
-      <x:c r="I10" s="107"/>
+        <x:v>18690</x:v>
+      </x:c>
+      <x:c r="G10" s="90"/>
+      <x:c r="H10" s="90"/>
+      <x:c r="I10" s="90"/>
     </x:row>
     <x:row r="11" ht="12" customHeight="1">
       <x:c r="A11" s="3"/>
       <x:c r="B11" s="3"/>
-      <x:c r="C11" s="107"/>
-      <x:c r="D11" s="107"/>
-      <x:c r="E11" s="107"/>
-      <x:c r="F11" s="107"/>
-      <x:c r="G11" s="107"/>
-      <x:c r="H11" s="107"/>
-      <x:c r="I11" s="107"/>
+      <x:c r="C11" s="90"/>
+      <x:c r="D11" s="90"/>
+      <x:c r="E11" s="90"/>
+      <x:c r="F11" s="90"/>
+      <x:c r="G11" s="90"/>
+      <x:c r="H11" s="90"/>
+      <x:c r="I11" s="90"/>
     </x:row>
     <x:row r="12" ht="12" customHeight="1">
       <x:c r="A12" s="3"/>
       <x:c r="B12" s="3"/>
-      <x:c r="C12" s="107"/>
-      <x:c r="D12" s="107"/>
-      <x:c r="E12" s="107"/>
-      <x:c r="F12" s="107"/>
-      <x:c r="G12" s="107"/>
-      <x:c r="H12" s="107"/>
-      <x:c r="I12" s="107"/>
+      <x:c r="C12" s="90"/>
+      <x:c r="D12" s="90"/>
+      <x:c r="E12" s="90"/>
+      <x:c r="F12" s="90"/>
+      <x:c r="G12" s="90"/>
+      <x:c r="H12" s="90"/>
+      <x:c r="I12" s="90"/>
     </x:row>
     <x:row r="13" ht="12" customHeight="1">
       <x:c r="A13" s="3"/>
       <x:c r="B13" s="3"/>
-      <x:c r="C13" s="107"/>
-      <x:c r="D13" s="107"/>
-      <x:c r="E13" s="107"/>
-      <x:c r="F13" s="107"/>
-      <x:c r="G13" s="107"/>
-      <x:c r="H13" s="107"/>
-      <x:c r="I13" s="107"/>
+      <x:c r="C13" s="90"/>
+      <x:c r="D13" s="90"/>
+      <x:c r="E13" s="90"/>
+      <x:c r="F13" s="90"/>
+      <x:c r="G13" s="90"/>
+      <x:c r="H13" s="90"/>
+      <x:c r="I13" s="90"/>
     </x:row>
     <x:row r="14" ht="28" customHeight="1">
-      <x:c r="A14" s="104" t="str">
+      <x:c r="A14" s="87" t="str">
         <x:v>各直播间结算过程</x:v>
       </x:c>
       <x:c r="B14" s="3"/>
-      <x:c r="C14" s="107"/>
-      <x:c r="D14" s="107"/>
-      <x:c r="E14" s="107"/>
-      <x:c r="F14" s="107"/>
-      <x:c r="G14" s="107"/>
-      <x:c r="H14" s="107"/>
-      <x:c r="I14" s="107"/>
+      <x:c r="C14" s="90"/>
+      <x:c r="D14" s="90"/>
+      <x:c r="E14" s="90"/>
+      <x:c r="F14" s="90"/>
+      <x:c r="G14" s="90"/>
+      <x:c r="H14" s="90"/>
+      <x:c r="I14" s="90"/>
     </x:row>
     <x:row r="15" ht="28" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>先按员工和直播间核算，再把该员工各房间月薪相加。</x:v>
       </x:c>
       <x:c r="B15" s="3"/>
-      <x:c r="C15" s="107"/>
-      <x:c r="D15" s="107"/>
-      <x:c r="E15" s="107"/>
-      <x:c r="F15" s="107"/>
-      <x:c r="G15" s="107"/>
-      <x:c r="H15" s="107"/>
-      <x:c r="I15" s="107"/>
+      <x:c r="C15" s="90"/>
+      <x:c r="D15" s="90"/>
+      <x:c r="E15" s="90"/>
+      <x:c r="F15" s="90"/>
+      <x:c r="G15" s="90"/>
+      <x:c r="H15" s="90"/>
+      <x:c r="I15" s="90"/>
     </x:row>
     <x:row r="16" ht="40" customHeight="1">
-      <x:c r="A16" s="63" t="str">
+      <x:c r="A16" s="51" t="str">
         <x:v>员工名称</x:v>
       </x:c>
-      <x:c r="B16" s="64" t="str">
+      <x:c r="B16" s="52" t="str">
         <x:v>直播间</x:v>
       </x:c>
-      <x:c r="C16" s="64" t="str">
-        <x:v>三类保底最大值</x:v>
-      </x:c>
-      <x:c r="D16" s="64" t="str">
-        <x:v>三类加成合计</x:v>
-      </x:c>
-      <x:c r="E16" s="64" t="str">
+      <x:c r="C16" s="52" t="str">
+        <x:v>两类保底最大值</x:v>
+      </x:c>
+      <x:c r="D16" s="52" t="str">
+        <x:v>两类加成合计</x:v>
+      </x:c>
+      <x:c r="E16" s="52" t="str">
         <x:v>总补贴</x:v>
       </x:c>
-      <x:c r="F16" s="64" t="str">
+      <x:c r="F16" s="52" t="str">
         <x:v>总计月薪</x:v>
       </x:c>
-      <x:c r="G16" s="64" t="str">
+      <x:c r="G16" s="52" t="str">
         <x:v>有效总保费</x:v>
       </x:c>
-      <x:c r="H16" s="64" t="str">
+      <x:c r="H16" s="52" t="str">
         <x:v>有效ROI</x:v>
       </x:c>
-      <x:c r="I16" s="65" t="str">
+      <x:c r="I16" s="53" t="str">
         <x:v>同房主播排名</x:v>
       </x:c>
     </x:row>
@@ -1055,67 +994,67 @@
       <x:c r="B17" s="3" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C17" s="83" t="n">
-        <x:f>MAX('月度核算明细'!AI7,'月度核算明细'!AM7,'月度核算明细'!AQ7)</x:f>
+      <x:c r="C17" s="71" t="n">
+        <x:f>MAX('月度核算明细'!AK7,'月度核算明细'!AO7)</x:f>
         <x:v>6600</x:v>
       </x:c>
-      <x:c r="D17" s="83" t="n">
-        <x:f>SUM('月度核算明细'!AJ7,'月度核算明细'!AN7,'月度核算明细'!AR7)</x:f>
+      <x:c r="D17" s="71" t="n">
+        <x:f>SUM('月度核算明细'!AL7,'月度核算明细'!AP7)</x:f>
         <x:v>6800</x:v>
       </x:c>
-      <x:c r="E17" s="83" t="n">
+      <x:c r="E17" s="71" t="n">
+        <x:f>'月度核算明细'!AR7</x:f>
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="F17" s="89" t="n">
         <x:f>'月度核算明细'!AT7</x:f>
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="F17" s="106" t="n">
-        <x:f>'月度核算明细'!AV7</x:f>
         <x:v>7250</x:v>
       </x:c>
-      <x:c r="G17" s="83" t="n">
-        <x:f>'月度核算明细'!AU7</x:f>
+      <x:c r="G17" s="71" t="n">
+        <x:f>'月度核算明细'!AS7</x:f>
         <x:v>40000</x:v>
       </x:c>
-      <x:c r="H17" s="83" t="n">
+      <x:c r="H17" s="71" t="n">
         <x:f>IF('月度核算明细'!T7=0,"n.a.",G17/'月度核算明细'!T7)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I17" s="105" t="n">
+      <x:c r="I17" s="88" t="n">
         <x:f>1+COUNTIFS($B$17:$B$20,B17,$H$17:$H$20,"&gt;"&amp;H17)</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="28" customHeight="1">
-      <x:c r="A18" s="67" t="str">
+      <x:c r="A18" s="55" t="str">
         <x:v>周宁</x:v>
       </x:c>
-      <x:c r="B18" s="67" t="str">
+      <x:c r="B18" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C18" s="87" t="n">
-        <x:f>MAX('月度核算明细'!AI8,'月度核算明细'!AM8,'月度核算明细'!AQ8)</x:f>
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="D18" s="87" t="n">
-        <x:f>SUM('月度核算明细'!AJ8,'月度核算明细'!AN8,'月度核算明细'!AR8)</x:f>
-        <x:v>3000</x:v>
-      </x:c>
-      <x:c r="E18" s="87" t="n">
+      <x:c r="C18" s="75" t="n">
+        <x:f>MAX('月度核算明细'!AK8,'月度核算明细'!AO8)</x:f>
+        <x:v>4400</x:v>
+      </x:c>
+      <x:c r="D18" s="75" t="n">
+        <x:f>SUM('月度核算明细'!AL8,'月度核算明细'!AP8)</x:f>
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="E18" s="75" t="n">
+        <x:f>'月度核算明细'!AR8</x:f>
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F18" s="92" t="n">
         <x:f>'月度核算明细'!AT8</x:f>
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F18" s="109" t="n">
-        <x:f>'月度核算明细'!AV8</x:f>
-        <x:v>4120</x:v>
-      </x:c>
-      <x:c r="G18" s="87" t="n">
-        <x:f>'月度核算明细'!AU8</x:f>
+        <x:v>4595</x:v>
+      </x:c>
+      <x:c r="G18" s="75" t="n">
+        <x:f>'月度核算明细'!AS8</x:f>
         <x:v>28000</x:v>
       </x:c>
-      <x:c r="H18" s="87" t="n">
+      <x:c r="H18" s="75" t="n">
         <x:f>IF('月度核算明细'!T8=0,"n.a.",G18/'月度核算明细'!T8)</x:f>
         <x:v>2.8</x:v>
       </x:c>
-      <x:c r="I18" s="108" t="n">
+      <x:c r="I18" s="91" t="n">
         <x:f>1+COUNTIFS($B$17:$B$20,B18,$H$17:$H$20,"&gt;"&amp;H18)</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -1127,67 +1066,67 @@
       <x:c r="B19" s="3" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C19" s="83" t="n">
-        <x:f>MAX('月度核算明细'!AI9,'月度核算明细'!AM9,'月度核算明细'!AQ9)</x:f>
+      <x:c r="C19" s="71" t="n">
+        <x:f>MAX('月度核算明细'!AK9,'月度核算明细'!AO9)</x:f>
         <x:v>4400</x:v>
       </x:c>
-      <x:c r="D19" s="83" t="n">
-        <x:f>SUM('月度核算明细'!AJ9,'月度核算明细'!AN9,'月度核算明细'!AR9)</x:f>
+      <x:c r="D19" s="71" t="n">
+        <x:f>SUM('月度核算明细'!AL9,'月度核算明细'!AP9)</x:f>
         <x:v>3800</x:v>
       </x:c>
-      <x:c r="E19" s="83" t="n">
+      <x:c r="E19" s="71" t="n">
+        <x:f>'月度核算明细'!AR9</x:f>
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F19" s="89" t="n">
         <x:f>'月度核算明细'!AT9</x:f>
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="F19" s="106" t="n">
-        <x:f>'月度核算明细'!AV9</x:f>
         <x:v>4565</x:v>
       </x:c>
-      <x:c r="G19" s="83" t="n">
-        <x:f>'月度核算明细'!AU9</x:f>
+      <x:c r="G19" s="71" t="n">
+        <x:f>'月度核算明细'!AS9</x:f>
         <x:v>36000</x:v>
       </x:c>
-      <x:c r="H19" s="83" t="n">
+      <x:c r="H19" s="71" t="n">
         <x:f>IF('月度核算明细'!T9=0,"n.a.",G19/'月度核算明细'!T9)</x:f>
         <x:v>3.6</x:v>
       </x:c>
-      <x:c r="I19" s="105" t="n">
+      <x:c r="I19" s="88" t="n">
         <x:f>1+COUNTIFS($B$17:$B$20,B19,$H$17:$H$20,"&gt;"&amp;H19)</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="28" customHeight="1">
-      <x:c r="A20" s="67" t="str">
+      <x:c r="A20" s="55" t="str">
         <x:v>林晓</x:v>
       </x:c>
-      <x:c r="B20" s="67" t="str">
+      <x:c r="B20" s="55" t="str">
         <x:v>示例二号房</x:v>
       </x:c>
-      <x:c r="C20" s="87" t="n">
-        <x:f>MAX('月度核算明细'!AI10,'月度核算明细'!AM10,'月度核算明细'!AQ10)</x:f>
+      <x:c r="C20" s="75" t="n">
+        <x:f>MAX('月度核算明细'!AK10,'月度核算明细'!AO10)</x:f>
         <x:v>2200</x:v>
       </x:c>
-      <x:c r="D20" s="87" t="n">
-        <x:f>SUM('月度核算明细'!AJ10,'月度核算明细'!AN10,'月度核算明细'!AR10)</x:f>
+      <x:c r="D20" s="75" t="n">
+        <x:f>SUM('月度核算明细'!AL10,'月度核算明细'!AP10)</x:f>
         <x:v>1850</x:v>
       </x:c>
-      <x:c r="E20" s="87" t="n">
+      <x:c r="E20" s="75" t="n">
+        <x:f>'月度核算明细'!AR10</x:f>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F20" s="92" t="n">
         <x:f>'月度核算明细'!AT10</x:f>
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F20" s="109" t="n">
-        <x:f>'月度核算明细'!AV10</x:f>
         <x:v>2280</x:v>
       </x:c>
-      <x:c r="G20" s="87" t="n">
-        <x:f>'月度核算明细'!AU10</x:f>
+      <x:c r="G20" s="75" t="n">
+        <x:f>'月度核算明细'!AS10</x:f>
         <x:v>9000</x:v>
       </x:c>
-      <x:c r="H20" s="87" t="n">
+      <x:c r="H20" s="75" t="n">
         <x:f>IF('月度核算明细'!T10=0,"n.a.",G20/'月度核算明细'!T10)</x:f>
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="I20" s="108" t="n">
+      <x:c r="I20" s="91" t="n">
         <x:f>1+COUNTIFS($B$17:$B$20,B20,$H$17:$H$20,"&gt;"&amp;H20)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -1216,7 +1155,7 @@
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="6" t="str">
-        <x:v>每行月薪 = MAX（三类保底最大值，三类加成合计）+ 总补贴。系数后保费只用于指标计算。</x:v>
+        <x:v>每行月薪 = MAX（全局与直播间保底最大值，两类加成合计）+ 总补贴。系数后保费用于ROI与排名。</x:v>
       </x:c>
       <x:c r="B23" s="3"/>
       <x:c r="C23" s="3"/>
@@ -1255,7 +1194,7 @@
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="6" t="str">
-        <x:v>来源：固定虚构演示样例。员工范围与适用规则固定；身份、规则或数据粒度改变后须在系统重新核算。</x:v>
+        <x:v>来源：固定虚构演示样例。仅使用全局和直播间规则；身份、规则或数据粒度改变后须在系统重新核算。</x:v>
       </x:c>
       <x:c r="B26" s="3"/>
       <x:c r="C26" s="3"/>
@@ -1267,7 +1206,9 @@
       <x:c r="I26" s="3"/>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
-      <x:c r="A27" s="3"/>
+      <x:c r="A27" s="6" t="str">
+        <x:v>兼容输入：旧式条件保费；当前新建保费规则采用固定系数项目。</x:v>
+      </x:c>
       <x:c r="B27" s="3"/>
       <x:c r="C27" s="3"/>
       <x:c r="D27" s="3"/>
@@ -1322,21 +1263,19 @@
     <x:col min="31" max="31" width="14" hidden="0" customWidth="1"/>
     <x:col min="32" max="32" width="14" hidden="0" customWidth="1"/>
     <x:col min="33" max="33" width="14" hidden="0" customWidth="1"/>
-    <x:col min="34" max="34" width="16" hidden="0" customWidth="1"/>
-    <x:col min="35" max="35" width="16" hidden="0" customWidth="1"/>
-    <x:col min="36" max="36" width="16" hidden="0" customWidth="1"/>
-    <x:col min="37" max="37" width="16" hidden="0" customWidth="1"/>
-    <x:col min="38" max="38" width="16" hidden="0" customWidth="1"/>
-    <x:col min="39" max="39" width="16" hidden="0" customWidth="1"/>
-    <x:col min="40" max="40" width="16" hidden="0" customWidth="1"/>
-    <x:col min="41" max="41" width="16" hidden="0" customWidth="1"/>
-    <x:col min="42" max="42" width="16" hidden="0" customWidth="1"/>
-    <x:col min="43" max="43" width="16" hidden="0" customWidth="1"/>
-    <x:col min="44" max="44" width="16" hidden="0" customWidth="1"/>
-    <x:col min="45" max="45" width="16" hidden="0" customWidth="1"/>
-    <x:col min="46" max="46" width="16" hidden="0" customWidth="1"/>
-    <x:col min="47" max="47" width="16" hidden="0" customWidth="1"/>
-    <x:col min="48" max="48" width="16" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="14" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="20" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="18" hidden="0" customWidth="1"/>
+    <x:col min="37" max="37" width="18" hidden="0" customWidth="1"/>
+    <x:col min="38" max="38" width="18" hidden="0" customWidth="1"/>
+    <x:col min="39" max="39" width="18" hidden="0" customWidth="1"/>
+    <x:col min="40" max="40" width="18" hidden="0" customWidth="1"/>
+    <x:col min="41" max="41" width="18" hidden="0" customWidth="1"/>
+    <x:col min="42" max="42" width="18" hidden="0" customWidth="1"/>
+    <x:col min="43" max="43" width="18" hidden="0" customWidth="1"/>
+    <x:col min="44" max="44" width="18" hidden="0" customWidth="1"/>
+    <x:col min="45" max="45" width="18" hidden="0" customWidth="1"/>
+    <x:col min="46" max="46" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -1386,8 +1325,6 @@
       <x:c r="AR1" s="3"/>
       <x:c r="AS1" s="3"/>
       <x:c r="AT1" s="3"/>
-      <x:c r="AU1" s="3"/>
-      <x:c r="AV1" s="3"/>
     </x:row>
     <x:row r="2" ht="31" customHeight="1">
       <x:c r="A2" s="4" t="str">
@@ -1438,8 +1375,6 @@
       <x:c r="AR2" s="3"/>
       <x:c r="AS2" s="3"/>
       <x:c r="AT2" s="3"/>
-      <x:c r="AU2" s="3"/>
-      <x:c r="AV2" s="3"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="5"/>
@@ -1488,12 +1423,10 @@
       <x:c r="AR3" s="5"/>
       <x:c r="AS3" s="5"/>
       <x:c r="AT3" s="5"/>
-      <x:c r="AU3" s="5"/>
-      <x:c r="AV3" s="5"/>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="6" t="str">
-        <x:v>每行对应员工、直播间、月份；前33列保留原始统计。金额为元，时长为小时。</x:v>
+        <x:v>每行对应员工、直播间、月份；前35列保留原始统计。金额为元，时长为小时。</x:v>
       </x:c>
       <x:c r="B4" s="3"/>
       <x:c r="C4" s="3"/>
@@ -1540,8 +1473,6 @@
       <x:c r="AR4" s="3"/>
       <x:c r="AS4" s="3"/>
       <x:c r="AT4" s="3"/>
-      <x:c r="AU4" s="3"/>
-      <x:c r="AV4" s="3"/>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
       <x:c r="A5" s="18" t="str">
@@ -1643,23 +1574,23 @@
       <x:c r="AG5" s="18" t="str">
         <x:v>直播数据统计</x:v>
       </x:c>
-      <x:c r="AH5" s="30" t="str">
-        <x:v>基础核算指标</x:v>
-      </x:c>
-      <x:c r="AI5" s="30" t="str">
-        <x:v>基础核算指标</x:v>
+      <x:c r="AH5" s="18" t="str">
+        <x:v>直播数据统计</x:v>
+      </x:c>
+      <x:c r="AI5" s="18" t="str">
+        <x:v>直播数据统计</x:v>
       </x:c>
       <x:c r="AJ5" s="30" t="str">
-        <x:v>基础核算指标</x:v>
+        <x:v>全局核算指标</x:v>
       </x:c>
       <x:c r="AK5" s="30" t="str">
-        <x:v>基础核算指标</x:v>
-      </x:c>
-      <x:c r="AL5" s="42" t="str">
-        <x:v>直播间核算指标</x:v>
-      </x:c>
-      <x:c r="AM5" s="42" t="str">
-        <x:v>直播间核算指标</x:v>
+        <x:v>全局核算指标</x:v>
+      </x:c>
+      <x:c r="AL5" s="30" t="str">
+        <x:v>全局核算指标</x:v>
+      </x:c>
+      <x:c r="AM5" s="30" t="str">
+        <x:v>全局核算指标</x:v>
       </x:c>
       <x:c r="AN5" s="42" t="str">
         <x:v>直播间核算指标</x:v>
@@ -1667,25 +1598,19 @@
       <x:c r="AO5" s="42" t="str">
         <x:v>直播间核算指标</x:v>
       </x:c>
-      <x:c r="AP5" s="54" t="str">
-        <x:v>员工核算指标</x:v>
-      </x:c>
-      <x:c r="AQ5" s="54" t="str">
-        <x:v>员工核算指标</x:v>
+      <x:c r="AP5" s="42" t="str">
+        <x:v>直播间核算指标</x:v>
+      </x:c>
+      <x:c r="AQ5" s="42" t="str">
+        <x:v>直播间核算指标</x:v>
       </x:c>
       <x:c r="AR5" s="54" t="str">
-        <x:v>员工核算指标</x:v>
+        <x:v>结果指标</x:v>
       </x:c>
       <x:c r="AS5" s="54" t="str">
-        <x:v>员工核算指标</x:v>
-      </x:c>
-      <x:c r="AT5" s="66" t="str">
         <x:v>结果指标</x:v>
       </x:c>
-      <x:c r="AU5" s="66" t="str">
-        <x:v>结果指标</x:v>
-      </x:c>
-      <x:c r="AV5" s="66" t="str">
+      <x:c r="AT5" s="54" t="str">
         <x:v>结果指标</x:v>
       </x:c>
     </x:row>
@@ -1786,817 +1711,705 @@
       <x:c r="AF6" s="16" t="str">
         <x:v>ROI排名</x:v>
       </x:c>
-      <x:c r="AG6" s="17" t="str">
+      <x:c r="AG6" s="16" t="str">
         <x:v>消耗排名</x:v>
       </x:c>
-      <x:c r="AH6" s="27" t="str">
-        <x:v>补贴</x:v>
-      </x:c>
-      <x:c r="AI6" s="28" t="str">
-        <x:v>保底</x:v>
-      </x:c>
-      <x:c r="AJ6" s="28" t="str">
-        <x:v>加成</x:v>
-      </x:c>
-      <x:c r="AK6" s="29" t="str">
-        <x:v>系数后保费</x:v>
-      </x:c>
-      <x:c r="AL6" s="39" t="str">
-        <x:v>补贴</x:v>
-      </x:c>
-      <x:c r="AM6" s="40" t="str">
-        <x:v>保底</x:v>
-      </x:c>
-      <x:c r="AN6" s="40" t="str">
-        <x:v>加成</x:v>
-      </x:c>
-      <x:c r="AO6" s="41" t="str">
-        <x:v>系数后保费</x:v>
-      </x:c>
-      <x:c r="AP6" s="51" t="str">
-        <x:v>补贴</x:v>
-      </x:c>
-      <x:c r="AQ6" s="52" t="str">
-        <x:v>保底</x:v>
-      </x:c>
-      <x:c r="AR6" s="52" t="str">
-        <x:v>加成</x:v>
-      </x:c>
-      <x:c r="AS6" s="53" t="str">
-        <x:v>系数后保费</x:v>
-      </x:c>
-      <x:c r="AT6" s="63" t="str">
-        <x:v>总补贴</x:v>
-      </x:c>
-      <x:c r="AU6" s="64" t="str">
-        <x:v>系数后总保费</x:v>
-      </x:c>
-      <x:c r="AV6" s="65" t="str">
+      <x:c r="AH6" s="16" t="str">
+        <x:v>等待薪资天数</x:v>
+      </x:c>
+      <x:c r="AI6" s="17" t="str">
+        <x:v>过去3个月的平均时薪</x:v>
+      </x:c>
+      <x:c r="AJ6" s="27" t="str">
+        <x:v>补贴金额</x:v>
+      </x:c>
+      <x:c r="AK6" s="28" t="str">
+        <x:v>保底金额</x:v>
+      </x:c>
+      <x:c r="AL6" s="28" t="str">
+        <x:v>加成金额</x:v>
+      </x:c>
+      <x:c r="AM6" s="29" t="str">
+        <x:v>系数加成后保费</x:v>
+      </x:c>
+      <x:c r="AN6" s="39" t="str">
+        <x:v>补贴金额</x:v>
+      </x:c>
+      <x:c r="AO6" s="40" t="str">
+        <x:v>保底金额</x:v>
+      </x:c>
+      <x:c r="AP6" s="40" t="str">
+        <x:v>加成金额</x:v>
+      </x:c>
+      <x:c r="AQ6" s="41" t="str">
+        <x:v>系数加成后保费</x:v>
+      </x:c>
+      <x:c r="AR6" s="51" t="str">
+        <x:v>总计补贴</x:v>
+      </x:c>
+      <x:c r="AS6" s="52" t="str">
+        <x:v>系数加成后总计保费</x:v>
+      </x:c>
+      <x:c r="AT6" s="53" t="str">
         <x:v>总计月薪</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
-      <x:c r="A7" s="68" t="str">
+      <x:c r="A7" s="56" t="str">
         <x:v>example-lin</x:v>
       </x:c>
-      <x:c r="B7" s="68" t="str">
+      <x:c r="B7" s="56" t="str">
         <x:v>林晓</x:v>
       </x:c>
-      <x:c r="C7" s="68" t="str">
+      <x:c r="C7" s="56" t="str">
         <x:v>example-live</x:v>
       </x:c>
-      <x:c r="D7" s="68" t="str">
+      <x:c r="D7" s="56" t="str">
         <x:v>示例直播部</x:v>
       </x:c>
-      <x:c r="E7" s="70" t="d">
+      <x:c r="E7" s="58" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F7" s="68" t="str">
+      <x:c r="F7" s="56" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="G7" s="68" t="str">
+      <x:c r="G7" s="56" t="str">
         <x:v>example-product</x:v>
       </x:c>
-      <x:c r="H7" s="68" t="str">
+      <x:c r="H7" s="56" t="str">
         <x:v>示例产品</x:v>
       </x:c>
-      <x:c r="I7" s="68" t="str">
+      <x:c r="I7" s="56" t="str">
         <x:v>example-room-a</x:v>
       </x:c>
-      <x:c r="J7" s="68" t="str">
+      <x:c r="J7" s="56" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="K7" s="70" t="d">
+      <x:c r="K7" s="58" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="L7" s="80" t="n">
+      <x:c r="L7" s="68" t="n">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="M7" s="81" t="d">
+      <x:c r="M7" s="69" t="d">
         <x:v>2026-10-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="N7" s="82" t="n">
+      <x:c r="N7" s="70" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="O7" s="82" t="n">
+      <x:c r="O7" s="70" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P7" s="82" t="n">
+      <x:c r="P7" s="70" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="Q7" s="82" t="n">
+      <x:c r="Q7" s="70" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="R7" s="80" t="n">
+      <x:c r="R7" s="68" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="S7" s="80" t="n">
+      <x:c r="S7" s="68" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="T7" s="82" t="n">
+      <x:c r="T7" s="70" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="U7" s="82" t="n">
+      <x:c r="U7" s="70" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="V7" s="82" t="n">
+      <x:c r="V7" s="70" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="W7" s="82" t="n">
+      <x:c r="W7" s="70" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="X7" s="82" t="n">
+      <x:c r="X7" s="70" t="n">
         <x:v>24000</x:v>
       </x:c>
-      <x:c r="Y7" s="82" t="n">
+      <x:c r="Y7" s="70" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="Z7" s="82" t="n">
+      <x:c r="Z7" s="70" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="AA7" s="82" t="n">
+      <x:c r="AA7" s="70" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="AB7" s="82" t="n">
+      <x:c r="AB7" s="70" t="n">
         <x:v>2.4</x:v>
       </x:c>
-      <x:c r="AC7" s="82" t="n">
+      <x:c r="AC7" s="70" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="AD7" s="82" t="str">
+      <x:c r="AD7" s="70" t="str">
         <x:v>待定义</x:v>
       </x:c>
-      <x:c r="AE7" s="82" t="str">
+      <x:c r="AE7" s="70" t="str">
         <x:v>待定义</x:v>
       </x:c>
-      <x:c r="AF7" s="80" t="n">
+      <x:c r="AF7" s="68" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AG7" s="80" t="n">
+      <x:c r="AG7" s="68" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH7" s="83" t="n">
-        <x:f>SUM('逐规则计算'!J7,'逐规则计算'!J8)</x:f>
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="AI7" s="83" t="n">
-        <x:f>MAX('逐规则计算'!J13,'逐规则计算'!J14)</x:f>
-        <x:v>5000</x:v>
-      </x:c>
-      <x:c r="AJ7" s="83" t="n">
-        <x:f>SUM('逐规则计算'!J15,'逐规则计算'!J16)</x:f>
-        <x:v>5500</x:v>
-      </x:c>
-      <x:c r="AK7" s="83" t="n">
-        <x:f>MAX('逐规则计算'!J9,'逐规则计算'!J10)</x:f>
-        <x:v>30000</x:v>
-      </x:c>
-      <x:c r="AL7" s="83" t="n">
+      <x:c r="AH7" s="68" t="str">
+        <x:v>未定义</x:v>
+      </x:c>
+      <x:c r="AI7" s="70" t="str">
+        <x:v>未定义</x:v>
+      </x:c>
+      <x:c r="AJ7" s="71" t="n">
+        <x:f>SUM('逐规则计算'!J7,'逐规则计算'!J8,'逐规则计算'!J11)</x:f>
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="AK7" s="71" t="n">
+        <x:f>MAX('逐规则计算'!J13,'逐规则计算'!J14,'逐规则计算'!J18,'逐规则计算'!J19)</x:f>
+        <x:v>6600</x:v>
+      </x:c>
+      <x:c r="AL7" s="71" t="n">
+        <x:f>SUM('逐规则计算'!J15,'逐规则计算'!J16,'逐规则计算'!J20)</x:f>
+        <x:v>5800</x:v>
+      </x:c>
+      <x:c r="AM7" s="71" t="n">
+        <x:f>MAX('逐规则计算'!J9,'逐规则计算'!J10,'逐规则计算'!J12)</x:f>
+        <x:v>40000</x:v>
+      </x:c>
+      <x:c r="AN7" s="71" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AM7" s="83" t="n">
+      <x:c r="AO7" s="71" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AN7" s="83" t="n">
+      <x:c r="AP7" s="71" t="n">
         <x:f>SUM('逐规则计算'!J17)</x:f>
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="AO7" s="83" t="n">
+      <x:c r="AQ7" s="71" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AP7" s="83" t="n">
-        <x:f>SUM('逐规则计算'!J11)</x:f>
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="AQ7" s="83" t="n">
-        <x:f>MAX('逐规则计算'!J18,'逐规则计算'!J19)</x:f>
-        <x:v>6600</x:v>
-      </x:c>
-      <x:c r="AR7" s="83" t="n">
-        <x:f>SUM('逐规则计算'!J20)</x:f>
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="AS7" s="83" t="n">
-        <x:f>MAX('逐规则计算'!J12)</x:f>
+      <x:c r="AR7" s="76" t="n">
+        <x:f>SUM(AJ7,AN7)</x:f>
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="AS7" s="76" t="n">
+        <x:f>MAX(AM7,AQ7)</x:f>
         <x:v>40000</x:v>
       </x:c>
-      <x:c r="AT7" s="88" t="n">
-        <x:f>SUM(AH7,AL7,AP7)</x:f>
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="AU7" s="88" t="n">
-        <x:f>MAX(AK7,AO7,AS7)</x:f>
-        <x:v>40000</x:v>
-      </x:c>
-      <x:c r="AV7" s="89" t="n">
-        <x:f>ROUND(MAX(AI7,AM7,AQ7,SUM(AJ7,AN7,AR7))+AT7,2)</x:f>
+      <x:c r="AT7" s="77" t="n">
+        <x:f>ROUND(MAX(AK7,AO7,SUM(AL7,AP7))+AR7,2)</x:f>
         <x:v>7250</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
-      <x:c r="A8" s="69" t="str">
+      <x:c r="A8" s="57" t="str">
         <x:v>example-zhou</x:v>
       </x:c>
-      <x:c r="B8" s="69" t="str">
+      <x:c r="B8" s="57" t="str">
         <x:v>周宁</x:v>
       </x:c>
-      <x:c r="C8" s="69" t="str">
+      <x:c r="C8" s="57" t="str">
         <x:v>example-live</x:v>
       </x:c>
-      <x:c r="D8" s="69" t="str">
+      <x:c r="D8" s="57" t="str">
         <x:v>示例直播部</x:v>
       </x:c>
-      <x:c r="E8" s="71" t="d">
+      <x:c r="E8" s="59" t="d">
         <x:v>2026-02-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F8" s="69" t="str">
+      <x:c r="F8" s="57" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="G8" s="69" t="str">
+      <x:c r="G8" s="57" t="str">
         <x:v>example-product</x:v>
       </x:c>
-      <x:c r="H8" s="69" t="str">
+      <x:c r="H8" s="57" t="str">
         <x:v>示例产品</x:v>
       </x:c>
-      <x:c r="I8" s="69" t="str">
+      <x:c r="I8" s="57" t="str">
         <x:v>example-room-a</x:v>
       </x:c>
-      <x:c r="J8" s="69" t="str">
+      <x:c r="J8" s="57" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="K8" s="71" t="d">
+      <x:c r="K8" s="59" t="d">
         <x:v>2026-01-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="L8" s="84" t="n">
+      <x:c r="L8" s="72" t="n">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="M8" s="85" t="d">
+      <x:c r="M8" s="73" t="d">
         <x:v>2026-10-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="N8" s="86" t="n">
+      <x:c r="N8" s="74" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="O8" s="86" t="n">
+      <x:c r="O8" s="74" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P8" s="86" t="n">
+      <x:c r="P8" s="74" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="Q8" s="86" t="n">
+      <x:c r="Q8" s="74" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="R8" s="84" t="n">
+      <x:c r="R8" s="72" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="S8" s="84" t="n">
+      <x:c r="S8" s="72" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="T8" s="86" t="n">
+      <x:c r="T8" s="74" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="U8" s="86" t="n">
+      <x:c r="U8" s="74" t="n">
         <x:v>2500</x:v>
       </x:c>
-      <x:c r="V8" s="86" t="n">
+      <x:c r="V8" s="74" t="n">
         <x:v>1250</x:v>
       </x:c>
-      <x:c r="W8" s="86" t="n">
+      <x:c r="W8" s="74" t="n">
         <x:v>6250</x:v>
       </x:c>
-      <x:c r="X8" s="86" t="n">
+      <x:c r="X8" s="74" t="n">
         <x:v>30000</x:v>
       </x:c>
-      <x:c r="Y8" s="86" t="n">
+      <x:c r="Y8" s="74" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="Z8" s="86" t="n">
+      <x:c r="Z8" s="74" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="AA8" s="86" t="n">
+      <x:c r="AA8" s="74" t="n">
         <x:v>24000</x:v>
       </x:c>
-      <x:c r="AB8" s="86" t="n">
+      <x:c r="AB8" s="74" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AC8" s="86" t="n">
+      <x:c r="AC8" s="74" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="AD8" s="86" t="str">
+      <x:c r="AD8" s="74" t="str">
         <x:v>待定义</x:v>
       </x:c>
-      <x:c r="AE8" s="86" t="str">
+      <x:c r="AE8" s="74" t="str">
         <x:v>待定义</x:v>
       </x:c>
-      <x:c r="AF8" s="84" t="n">
+      <x:c r="AF8" s="72" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AG8" s="84" t="n">
+      <x:c r="AG8" s="72" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AH8" s="87" t="n">
-        <x:f>SUM('逐规则计算'!J21,'逐规则计算'!J22)</x:f>
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="AI8" s="87" t="n">
-        <x:f>MAX('逐规则计算'!J25,'逐规则计算'!J26)</x:f>
+      <x:c r="AH8" s="72" t="str">
+        <x:v>未定义</x:v>
+      </x:c>
+      <x:c r="AI8" s="74" t="str">
+        <x:v>未定义</x:v>
+      </x:c>
+      <x:c r="AJ8" s="75" t="n">
+        <x:f>SUM('逐规则计算'!J21,'逐规则计算'!J22,'逐规则计算'!J25)</x:f>
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="AK8" s="75" t="n">
+        <x:f>MAX('逐规则计算'!J27,'逐规则计算'!J28,'逐规则计算'!J32,'逐规则计算'!J33)</x:f>
+        <x:v>4400</x:v>
+      </x:c>
+      <x:c r="AL8" s="75" t="n">
+        <x:f>SUM('逐规则计算'!J29,'逐规则计算'!J30,'逐规则计算'!J34)</x:f>
+        <x:v>2100</x:v>
+      </x:c>
+      <x:c r="AM8" s="75" t="n">
+        <x:f>MAX('逐规则计算'!J23,'逐规则计算'!J24,'逐规则计算'!J26)</x:f>
+        <x:v>28000</x:v>
+      </x:c>
+      <x:c r="AN8" s="75" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO8" s="75" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP8" s="75" t="n">
+        <x:f>SUM('逐规则计算'!J31)</x:f>
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="AQ8" s="75" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AR8" s="76" t="n">
+        <x:f>SUM(AJ8,AN8)</x:f>
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="AS8" s="76" t="n">
+        <x:f>MAX(AM8,AQ8)</x:f>
+        <x:v>28000</x:v>
+      </x:c>
+      <x:c r="AT8" s="77" t="n">
+        <x:f>ROUND(MAX(AK8,AO8,SUM(AL8,AP8))+AR8,2)</x:f>
+        <x:v>4595</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="56" t="str">
+        <x:v>example-chen</x:v>
+      </x:c>
+      <x:c r="B9" s="56" t="str">
+        <x:v>陈雨</x:v>
+      </x:c>
+      <x:c r="C9" s="56" t="str">
+        <x:v>example-live</x:v>
+      </x:c>
+      <x:c r="D9" s="56" t="str">
+        <x:v>示例直播部</x:v>
+      </x:c>
+      <x:c r="E9" s="58" t="d">
+        <x:v>2026-03-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F9" s="56" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G9" s="56" t="str">
+        <x:v>example-product</x:v>
+      </x:c>
+      <x:c r="H9" s="56" t="str">
+        <x:v>示例产品</x:v>
+      </x:c>
+      <x:c r="I9" s="56" t="str">
+        <x:v>example-room-a</x:v>
+      </x:c>
+      <x:c r="J9" s="56" t="str">
+        <x:v>示例一号房</x:v>
+      </x:c>
+      <x:c r="K9" s="58" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="L9" s="68" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M9" s="69" t="d">
+        <x:v>2026-10-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="N9" s="70" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="O9" s="70" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P9" s="70" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q9" s="70" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R9" s="68" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S9" s="68" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="T9" s="70" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="U9" s="70" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="V9" s="70" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="W9" s="70" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="X9" s="70" t="n">
+        <x:v>26000</x:v>
+      </x:c>
+      <x:c r="Y9" s="70" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="Z9" s="70" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="AA9" s="70" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="AB9" s="70" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="AC9" s="70" t="n">
+        <x:v>166.66666666666666</x:v>
+      </x:c>
+      <x:c r="AD9" s="70" t="str">
+        <x:v>待定义</x:v>
+      </x:c>
+      <x:c r="AE9" s="70" t="str">
+        <x:v>待定义</x:v>
+      </x:c>
+      <x:c r="AF9" s="68" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AG9" s="68" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH9" s="68" t="str">
+        <x:v>未定义</x:v>
+      </x:c>
+      <x:c r="AI9" s="70" t="str">
+        <x:v>未定义</x:v>
+      </x:c>
+      <x:c r="AJ9" s="71" t="n">
+        <x:f>SUM('逐规则计算'!J35,'逐规则计算'!J36,'逐规则计算'!J39)</x:f>
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="AK9" s="71" t="n">
+        <x:f>MAX('逐规则计算'!J41,'逐规则计算'!J42,'逐规则计算'!J46,'逐规则计算'!J47)</x:f>
+        <x:v>4400</x:v>
+      </x:c>
+      <x:c r="AL9" s="71" t="n">
+        <x:f>SUM('逐规则计算'!J43,'逐规则计算'!J44,'逐规则计算'!J48)</x:f>
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="AM9" s="71" t="n">
+        <x:f>MAX('逐规则计算'!J37,'逐规则计算'!J38,'逐规则计算'!J40)</x:f>
+        <x:v>36000</x:v>
+      </x:c>
+      <x:c r="AN9" s="71" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO9" s="71" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP9" s="71" t="n">
+        <x:f>SUM('逐规则计算'!J45)</x:f>
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="AQ9" s="71" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AR9" s="76" t="n">
+        <x:f>SUM(AJ9,AN9)</x:f>
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="AS9" s="76" t="n">
+        <x:f>MAX(AM9,AQ9)</x:f>
+        <x:v>36000</x:v>
+      </x:c>
+      <x:c r="AT9" s="77" t="n">
+        <x:f>ROUND(MAX(AK9,AO9,SUM(AL9,AP9))+AR9,2)</x:f>
+        <x:v>4565</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="57" t="str">
+        <x:v>example-lin</x:v>
+      </x:c>
+      <x:c r="B10" s="57" t="str">
+        <x:v>林晓</x:v>
+      </x:c>
+      <x:c r="C10" s="57" t="str">
+        <x:v>example-live</x:v>
+      </x:c>
+      <x:c r="D10" s="57" t="str">
+        <x:v>示例直播部</x:v>
+      </x:c>
+      <x:c r="E10" s="59" t="d">
+        <x:v>2026-01-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F10" s="57" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G10" s="57" t="str">
+        <x:v>example-product</x:v>
+      </x:c>
+      <x:c r="H10" s="57" t="str">
+        <x:v>示例产品</x:v>
+      </x:c>
+      <x:c r="I10" s="57" t="str">
+        <x:v>example-room-b</x:v>
+      </x:c>
+      <x:c r="J10" s="57" t="str">
+        <x:v>示例二号房</x:v>
+      </x:c>
+      <x:c r="K10" s="59" t="d">
+        <x:v>2026-02-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="L10" s="72" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="M10" s="73" t="d">
+        <x:v>2026-10-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="N10" s="74" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="O10" s="74" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P10" s="74" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Q10" s="74" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R10" s="72" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S10" s="72" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T10" s="74" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="AJ8" s="87" t="n">
-        <x:f>SUM('逐规则计算'!J27,'逐规则计算'!J28)</x:f>
+      <x:c r="U10" s="74" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="V10" s="74" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="W10" s="74" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="X10" s="74" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="Y10" s="74" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="Z10" s="74" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="AK8" s="87" t="n">
-        <x:f>MAX('逐规则计算'!J23,'逐规则计算'!J24)</x:f>
-        <x:v>28000</x:v>
-      </x:c>
-      <x:c r="AL8" s="87" t="n">
+      <x:c r="AA10" s="74" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="AB10" s="74" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="AC10" s="74" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="AD10" s="74" t="str">
+        <x:v>待定义</x:v>
+      </x:c>
+      <x:c r="AE10" s="74" t="str">
+        <x:v>待定义</x:v>
+      </x:c>
+      <x:c r="AF10" s="72" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG10" s="72" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH10" s="72" t="str">
+        <x:v>未定义</x:v>
+      </x:c>
+      <x:c r="AI10" s="74" t="str">
+        <x:v>未定义</x:v>
+      </x:c>
+      <x:c r="AJ10" s="75" t="n">
+        <x:f>SUM('逐规则计算'!J49,'逐规则计算'!J50,'逐规则计算'!J53)</x:f>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="AK10" s="75" t="n">
+        <x:f>MAX('逐规则计算'!J55,'逐规则计算'!J56,'逐规则计算'!J60,'逐规则计算'!J61)</x:f>
+        <x:v>2200</x:v>
+      </x:c>
+      <x:c r="AL10" s="75" t="n">
+        <x:f>SUM('逐规则计算'!J57,'逐规则计算'!J58,'逐规则计算'!J62)</x:f>
+        <x:v>1250</x:v>
+      </x:c>
+      <x:c r="AM10" s="75" t="n">
+        <x:f>MAX('逐规则计算'!J51,'逐规则计算'!J52,'逐规则计算'!J54)</x:f>
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="AN10" s="75" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AM8" s="87" t="n">
+      <x:c r="AO10" s="75" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AN8" s="87" t="n">
-        <x:f>SUM('逐规则计算'!J29)</x:f>
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="AO8" s="87" t="n">
+      <x:c r="AP10" s="75" t="n">
+        <x:f>SUM('逐规则计算'!J59)</x:f>
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="AQ10" s="75" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AP8" s="87" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AQ8" s="87" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AR8" s="87" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS8" s="87" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT8" s="88" t="n">
-        <x:f>SUM(AH8,AL8,AP8)</x:f>
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="AU8" s="88" t="n">
-        <x:f>MAX(AK8,AO8,AS8)</x:f>
-        <x:v>28000</x:v>
-      </x:c>
-      <x:c r="AV8" s="89" t="n">
-        <x:f>ROUND(MAX(AI8,AM8,AQ8,SUM(AJ8,AN8,AR8))+AT8,2)</x:f>
-        <x:v>4120</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="24" customHeight="1">
-      <x:c r="A9" s="68" t="str">
-        <x:v>example-chen</x:v>
-      </x:c>
-      <x:c r="B9" s="68" t="str">
-        <x:v>陈雨</x:v>
-      </x:c>
-      <x:c r="C9" s="68" t="str">
-        <x:v>example-live</x:v>
-      </x:c>
-      <x:c r="D9" s="68" t="str">
-        <x:v>示例直播部</x:v>
-      </x:c>
-      <x:c r="E9" s="70" t="d">
-        <x:v>2026-03-01T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="F9" s="68" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="G9" s="68" t="str">
-        <x:v>example-product</x:v>
-      </x:c>
-      <x:c r="H9" s="68" t="str">
-        <x:v>示例产品</x:v>
-      </x:c>
-      <x:c r="I9" s="68" t="str">
-        <x:v>example-room-a</x:v>
-      </x:c>
-      <x:c r="J9" s="68" t="str">
-        <x:v>示例一号房</x:v>
-      </x:c>
-      <x:c r="K9" s="70" t="d">
-        <x:v>2026-01-01T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="L9" s="80" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="M9" s="81" t="d">
-        <x:v>2026-10-01T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="N9" s="82" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="O9" s="82" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="P9" s="82" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="Q9" s="82" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R9" s="80" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S9" s="80" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="T9" s="82" t="n">
-        <x:v>10000</x:v>
-      </x:c>
-      <x:c r="U9" s="82" t="n">
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="V9" s="82" t="n">
-        <x:v>3000</x:v>
-      </x:c>
-      <x:c r="W9" s="82" t="n">
-        <x:v>5000</x:v>
-      </x:c>
-      <x:c r="X9" s="82" t="n">
-        <x:v>26000</x:v>
-      </x:c>
-      <x:c r="Y9" s="82" t="n">
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="Z9" s="82" t="n">
-        <x:v>6000</x:v>
-      </x:c>
-      <x:c r="AA9" s="82" t="n">
-        <x:v>18000</x:v>
-      </x:c>
-      <x:c r="AB9" s="82" t="n">
-        <x:v>2.6</x:v>
-      </x:c>
-      <x:c r="AC9" s="82" t="n">
-        <x:v>166.66666666666666</x:v>
-      </x:c>
-      <x:c r="AD9" s="82" t="str">
-        <x:v>待定义</x:v>
-      </x:c>
-      <x:c r="AE9" s="82" t="str">
-        <x:v>待定义</x:v>
-      </x:c>
-      <x:c r="AF9" s="80" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AG9" s="80" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH9" s="83" t="n">
-        <x:f>SUM('逐规则计算'!J30,'逐规则计算'!J31)</x:f>
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="AI9" s="83" t="n">
-        <x:f>MAX('逐规则计算'!J36,'逐规则计算'!J37)</x:f>
-        <x:v>3000</x:v>
-      </x:c>
-      <x:c r="AJ9" s="83" t="n">
-        <x:f>SUM('逐规则计算'!J38,'逐规则计算'!J39)</x:f>
-        <x:v>3000</x:v>
-      </x:c>
-      <x:c r="AK9" s="83" t="n">
-        <x:f>MAX('逐规则计算'!J32,'逐规则计算'!J33)</x:f>
-        <x:v>30000</x:v>
-      </x:c>
-      <x:c r="AL9" s="83" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AM9" s="83" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AN9" s="83" t="n">
-        <x:f>SUM('逐规则计算'!J40)</x:f>
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="AO9" s="83" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AP9" s="83" t="n">
-        <x:f>SUM('逐规则计算'!J34)</x:f>
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="AQ9" s="83" t="n">
-        <x:f>MAX('逐规则计算'!J41,'逐规则计算'!J42)</x:f>
-        <x:v>4400</x:v>
-      </x:c>
-      <x:c r="AR9" s="83" t="n">
-        <x:f>SUM('逐规则计算'!J43)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="AS9" s="83" t="n">
-        <x:f>MAX('逐规则计算'!J35)</x:f>
-        <x:v>36000</x:v>
-      </x:c>
-      <x:c r="AT9" s="88" t="n">
-        <x:f>SUM(AH9,AL9,AP9)</x:f>
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="AU9" s="88" t="n">
-        <x:f>MAX(AK9,AO9,AS9)</x:f>
-        <x:v>36000</x:v>
-      </x:c>
-      <x:c r="AV9" s="89" t="n">
-        <x:f>ROUND(MAX(AI9,AM9,AQ9,SUM(AJ9,AN9,AR9))+AT9,2)</x:f>
-        <x:v>4565</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="69" t="str">
-        <x:v>example-lin</x:v>
-      </x:c>
-      <x:c r="B10" s="69" t="str">
-        <x:v>林晓</x:v>
-      </x:c>
-      <x:c r="C10" s="69" t="str">
-        <x:v>example-live</x:v>
-      </x:c>
-      <x:c r="D10" s="69" t="str">
-        <x:v>示例直播部</x:v>
-      </x:c>
-      <x:c r="E10" s="71" t="d">
-        <x:v>2026-01-01T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="F10" s="69" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="G10" s="69" t="str">
-        <x:v>example-product</x:v>
-      </x:c>
-      <x:c r="H10" s="69" t="str">
-        <x:v>示例产品</x:v>
-      </x:c>
-      <x:c r="I10" s="69" t="str">
-        <x:v>example-room-b</x:v>
-      </x:c>
-      <x:c r="J10" s="69" t="str">
-        <x:v>示例二号房</x:v>
-      </x:c>
-      <x:c r="K10" s="71" t="d">
-        <x:v>2026-02-01T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="L10" s="84" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="M10" s="85" t="d">
-        <x:v>2026-10-01T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="N10" s="86" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="O10" s="86" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="P10" s="86" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="Q10" s="86" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R10" s="84" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S10" s="84" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T10" s="86" t="n">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="U10" s="86" t="n">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="V10" s="86" t="n">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="W10" s="86" t="n">
-        <x:v>3000</x:v>
-      </x:c>
-      <x:c r="X10" s="86" t="n">
-        <x:v>10000</x:v>
-      </x:c>
-      <x:c r="Y10" s="86" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="Z10" s="86" t="n">
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="AA10" s="86" t="n">
-        <x:v>7000</x:v>
-      </x:c>
-      <x:c r="AB10" s="86" t="n">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="AC10" s="86" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AD10" s="86" t="str">
-        <x:v>待定义</x:v>
-      </x:c>
-      <x:c r="AE10" s="86" t="str">
-        <x:v>待定义</x:v>
-      </x:c>
-      <x:c r="AF10" s="84" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG10" s="84" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH10" s="87" t="n">
-        <x:f>SUM('逐规则计算'!J44,'逐规则计算'!J45)</x:f>
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="AI10" s="87" t="n">
-        <x:f>MAX('逐规则计算'!J50,'逐规则计算'!J51)</x:f>
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="AJ10" s="87" t="n">
-        <x:f>SUM('逐规则计算'!J52,'逐规则计算'!J53)</x:f>
-        <x:v>1200</x:v>
-      </x:c>
-      <x:c r="AK10" s="87" t="n">
-        <x:f>MAX('逐规则计算'!J46,'逐规则计算'!J47)</x:f>
+      <x:c r="AR10" s="76" t="n">
+        <x:f>SUM(AJ10,AN10)</x:f>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="AS10" s="76" t="n">
+        <x:f>MAX(AM10,AQ10)</x:f>
         <x:v>9000</x:v>
       </x:c>
-      <x:c r="AL10" s="87" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AM10" s="87" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AN10" s="87" t="n">
-        <x:f>SUM('逐规则计算'!J54)</x:f>
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="AO10" s="87" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AP10" s="87" t="n">
-        <x:f>SUM('逐规则计算'!J48)</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="AQ10" s="87" t="n">
-        <x:f>MAX('逐规则计算'!J55,'逐规则计算'!J56)</x:f>
-        <x:v>2200</x:v>
-      </x:c>
-      <x:c r="AR10" s="87" t="n">
-        <x:f>SUM('逐规则计算'!J57)</x:f>
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="AS10" s="87" t="n">
-        <x:f>MAX('逐规则计算'!J49)</x:f>
-        <x:v>9000</x:v>
-      </x:c>
-      <x:c r="AT10" s="88" t="n">
-        <x:f>SUM(AH10,AL10,AP10)</x:f>
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="AU10" s="88" t="n">
-        <x:f>MAX(AK10,AO10,AS10)</x:f>
-        <x:v>9000</x:v>
-      </x:c>
-      <x:c r="AV10" s="89" t="n">
-        <x:f>ROUND(MAX(AI10,AM10,AQ10,SUM(AJ10,AN10,AR10))+AT10,2)</x:f>
+      <x:c r="AT10" s="77" t="n">
+        <x:f>ROUND(MAX(AK10,AO10,SUM(AL10,AP10))+AR10,2)</x:f>
         <x:v>2280</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
-      <x:c r="A11" s="90" t="str">
-        <x:v>example-wu</x:v>
-      </x:c>
-      <x:c r="B11" s="90" t="str">
-        <x:v>吴策</x:v>
-      </x:c>
-      <x:c r="C11" s="90" t="str">
-        <x:v>example-live</x:v>
-      </x:c>
-      <x:c r="D11" s="90" t="str">
-        <x:v>示例直播部</x:v>
-      </x:c>
-      <x:c r="E11" s="91" t="d">
-        <x:v>2026-02-01T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="F11" s="90" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="G11" s="90" t="str">
-        <x:v>example-product</x:v>
-      </x:c>
-      <x:c r="H11" s="90" t="str">
-        <x:v>示例产品</x:v>
-      </x:c>
-      <x:c r="I11" s="90" t="str">
-        <x:v>example-room-a</x:v>
-      </x:c>
-      <x:c r="J11" s="90" t="str">
-        <x:v>示例一号房</x:v>
-      </x:c>
-      <x:c r="K11" s="91" t="d">
-        <x:v>2026-01-01T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="L11" s="92" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="M11" s="93" t="d">
-        <x:v>2026-10-01T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="N11" s="94" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="O11" s="94" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="P11" s="94" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="Q11" s="94" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="R11" s="92" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="S11" s="92" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="T11" s="94" t="n">
-        <x:v>30000</x:v>
-      </x:c>
-      <x:c r="U11" s="94" t="n">
-        <x:v>6500</x:v>
-      </x:c>
-      <x:c r="V11" s="94" t="n">
-        <x:v>7250</x:v>
-      </x:c>
-      <x:c r="W11" s="94" t="n">
-        <x:v>16250</x:v>
-      </x:c>
-      <x:c r="X11" s="94" t="n">
-        <x:v>80000</x:v>
-      </x:c>
-      <x:c r="Y11" s="94" t="n">
-        <x:v>8000</x:v>
-      </x:c>
-      <x:c r="Z11" s="94" t="n">
-        <x:v>20000</x:v>
-      </x:c>
-      <x:c r="AA11" s="94" t="n">
-        <x:v>52000</x:v>
-      </x:c>
-      <x:c r="AB11" s="94" t="n">
-        <x:v>2.6666666666666665</x:v>
-      </x:c>
-      <x:c r="AC11" s="94" t="n">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="AD11" s="94" t="str">
-        <x:v>待定义</x:v>
-      </x:c>
-      <x:c r="AE11" s="94" t="str">
-        <x:v>待定义</x:v>
-      </x:c>
-      <x:c r="AF11" s="92" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG11" s="92" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH11" s="94"/>
-      <x:c r="AI11" s="94"/>
-      <x:c r="AJ11" s="94"/>
-      <x:c r="AK11" s="94"/>
-      <x:c r="AL11" s="94"/>
-      <x:c r="AM11" s="94"/>
-      <x:c r="AN11" s="94"/>
-      <x:c r="AO11" s="94"/>
-      <x:c r="AP11" s="94"/>
-      <x:c r="AQ11" s="94"/>
-      <x:c r="AR11" s="94"/>
-      <x:c r="AS11" s="94"/>
-      <x:c r="AT11" s="94"/>
-      <x:c r="AU11" s="94"/>
-      <x:c r="AV11" s="94"/>
+      <x:c r="A11" s="3"/>
+      <x:c r="B11" s="3"/>
+      <x:c r="C11" s="3"/>
+      <x:c r="D11" s="3"/>
+      <x:c r="E11" s="3"/>
+      <x:c r="F11" s="3"/>
+      <x:c r="G11" s="3"/>
+      <x:c r="H11" s="3"/>
+      <x:c r="I11" s="3"/>
+      <x:c r="J11" s="3"/>
+      <x:c r="K11" s="3"/>
+      <x:c r="L11" s="3"/>
+      <x:c r="M11" s="3"/>
+      <x:c r="N11" s="3"/>
+      <x:c r="O11" s="3"/>
+      <x:c r="P11" s="3"/>
+      <x:c r="Q11" s="3"/>
+      <x:c r="R11" s="3"/>
+      <x:c r="S11" s="3"/>
+      <x:c r="T11" s="3"/>
+      <x:c r="U11" s="3"/>
+      <x:c r="V11" s="3"/>
+      <x:c r="W11" s="3"/>
+      <x:c r="X11" s="3"/>
+      <x:c r="Y11" s="3"/>
+      <x:c r="Z11" s="3"/>
+      <x:c r="AA11" s="3"/>
+      <x:c r="AB11" s="3"/>
+      <x:c r="AC11" s="3"/>
+      <x:c r="AD11" s="3"/>
+      <x:c r="AE11" s="3"/>
+      <x:c r="AF11" s="3"/>
+      <x:c r="AG11" s="3"/>
+      <x:c r="AH11" s="3"/>
+      <x:c r="AI11" s="3"/>
+      <x:c r="AJ11" s="3"/>
+      <x:c r="AK11" s="3"/>
+      <x:c r="AL11" s="3"/>
+      <x:c r="AM11" s="3"/>
+      <x:c r="AN11" s="3"/>
+      <x:c r="AO11" s="3"/>
+      <x:c r="AP11" s="3"/>
+      <x:c r="AQ11" s="3"/>
+      <x:c r="AR11" s="3"/>
+      <x:c r="AS11" s="3"/>
+      <x:c r="AT11" s="3"/>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="3"/>
+      <x:c r="A12" s="6" t="str">
+        <x:v>5行来源数据筛选为4行主播核算。吴策仅具备投手身份，已排除。</x:v>
+      </x:c>
       <x:c r="B12" s="3"/>
       <x:c r="C12" s="3"/>
       <x:c r="D12" s="3"/>
@@ -2642,12 +2455,10 @@
       <x:c r="AR12" s="3"/>
       <x:c r="AS12" s="3"/>
       <x:c r="AT12" s="3"/>
-      <x:c r="AU12" s="3"/>
-      <x:c r="AV12" s="3"/>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="6" t="str">
-        <x:v>吴策仅具备投手身份，保留其输入以展示筛选口径，核算栏留空。AD成本、保单成本尚未定义。</x:v>
+        <x:v>等待薪资天数、过去3个月平均时薪未提供；AD成本、保单成本待定义。</x:v>
       </x:c>
       <x:c r="B13" s="3"/>
       <x:c r="C13" s="3"/>
@@ -2694,8 +2505,6 @@
       <x:c r="AR13" s="3"/>
       <x:c r="AS13" s="3"/>
       <x:c r="AT13" s="3"/>
-      <x:c r="AU13" s="3"/>
-      <x:c r="AV13" s="3"/>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="6" t="str">
@@ -2746,8 +2555,6 @@
       <x:c r="AR14" s="3"/>
       <x:c r="AS14" s="3"/>
       <x:c r="AT14" s="3"/>
-      <x:c r="AU14" s="3"/>
-      <x:c r="AV14" s="3"/>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="3"/>
@@ -2796,16 +2603,13 @@
       <x:c r="AR15" s="3"/>
       <x:c r="AS15" s="3"/>
       <x:c r="AT15" s="3"/>
-      <x:c r="AU15" s="3"/>
-      <x:c r="AV15" s="3"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A5:AG5"/>
-    <x:mergeCell ref="AH5:AK5"/>
-    <x:mergeCell ref="AL5:AO5"/>
-    <x:mergeCell ref="AP5:AS5"/>
-    <x:mergeCell ref="AT5:AV5"/>
+    <x:mergeCell ref="A5:AI5"/>
+    <x:mergeCell ref="AJ5:AM5"/>
+    <x:mergeCell ref="AN5:AQ5"/>
+    <x:mergeCell ref="AR5:AT5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2962,7 +2766,7 @@
         <x:v>规则金额</x:v>
       </x:c>
       <x:c r="K6" s="3"/>
-      <x:c r="L6" s="104" t="str">
+      <x:c r="L6" s="87" t="str">
         <x:v>命中说明</x:v>
       </x:c>
       <x:c r="M6" s="27" t="str">
@@ -2986,7 +2790,7 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C7" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D7" s="3" t="str">
         <x:v>基础·夜班补贴</x:v>
@@ -2997,17 +2801,17 @@
       <x:c r="F7" s="3" t="str">
         <x:v>夜班场次</x:v>
       </x:c>
-      <x:c r="G7" s="75" t="n">
+      <x:c r="G7" s="63" t="n">
         <x:f>'月度核算明细'!R7</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H7" s="118" t="n">
+      <x:c r="H7" s="101" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I7" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7" s="102" t="n">
+      <x:c r="I7" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J7" s="85" t="n">
         <x:f>ROUND(G7*H7+I7,2)</x:f>
         <x:v>200</x:v>
       </x:c>
@@ -3015,43 +2819,43 @@
       <x:c r="L7" s="3" t="str">
         <x:v>场次 × 每场补贴</x:v>
       </x:c>
-      <x:c r="M7" s="119"/>
-      <x:c r="N7" s="120"/>
-      <x:c r="O7" s="121"/>
+      <x:c r="M7" s="102"/>
+      <x:c r="N7" s="103"/>
+      <x:c r="O7" s="104"/>
       <x:c r="P7" s="3" t="str">
         <x:v>g-night-allowance</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
-      <x:c r="A8" s="67" t="str">
+      <x:c r="A8" s="55" t="str">
         <x:v>林晓</x:v>
       </x:c>
-      <x:c r="B8" s="67" t="str">
+      <x:c r="B8" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C8" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D8" s="67" t="str">
+      <x:c r="C8" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D8" s="55" t="str">
         <x:v>基础·早班补贴</x:v>
       </x:c>
-      <x:c r="E8" s="67" t="str">
+      <x:c r="E8" s="55" t="str">
         <x:v>补贴</x:v>
       </x:c>
-      <x:c r="F8" s="67" t="str">
+      <x:c r="F8" s="55" t="str">
         <x:v>早班场次</x:v>
       </x:c>
-      <x:c r="G8" s="77" t="n">
+      <x:c r="G8" s="65" t="n">
         <x:f>'月度核算明细'!S7</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H8" s="118" t="n">
+      <x:c r="H8" s="101" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I8" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J8" s="103" t="n">
+      <x:c r="I8" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="86" t="n">
         <x:f>ROUND(G8*H8+I8,2)</x:f>
         <x:v>100</x:v>
       </x:c>
@@ -3059,10 +2863,10 @@
       <x:c r="L8" s="3" t="str">
         <x:v>场次 × 每场补贴</x:v>
       </x:c>
-      <x:c r="M8" s="119"/>
-      <x:c r="N8" s="120"/>
-      <x:c r="O8" s="121"/>
-      <x:c r="P8" s="67" t="str">
+      <x:c r="M8" s="102"/>
+      <x:c r="N8" s="103"/>
+      <x:c r="O8" s="104"/>
+      <x:c r="P8" s="55" t="str">
         <x:v>g-early-allowance</x:v>
       </x:c>
     </x:row>
@@ -3074,7 +2878,7 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C9" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D9" s="3" t="str">
         <x:v>基础·早班系数</x:v>
@@ -3085,19 +2889,19 @@
       <x:c r="F9" s="3" t="str">
         <x:v>早班保费</x:v>
       </x:c>
-      <x:c r="G9" s="75" t="n">
+      <x:c r="G9" s="63" t="n">
         <x:f>'月度核算明细'!Z7</x:f>
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H9" s="118" t="n">
+      <x:c r="H9" s="101" t="n">
         <x:f>IF('月度核算明细'!S7&gt;=O9,M9,1)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I9" s="75" t="n">
+      <x:c r="I9" s="63" t="n">
         <x:f>'月度核算明细'!AA7</x:f>
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="J9" s="102" t="n">
+      <x:c r="J9" s="85" t="n">
         <x:f>ROUND(G9*H9+I9,2)</x:f>
         <x:v>30000</x:v>
       </x:c>
@@ -3105,13 +2909,13 @@
       <x:c r="L9" s="3" t="str">
         <x:v>达阈值用设定系数，否则用1</x:v>
       </x:c>
-      <x:c r="M9" s="119" t="n">
+      <x:c r="M9" s="102" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N9" s="120" t="str">
+      <x:c r="N9" s="103" t="str">
         <x:v>早班场次 ≥</x:v>
       </x:c>
-      <x:c r="O9" s="121" t="n">
+      <x:c r="O9" s="104" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P9" s="3" t="str">
@@ -3119,37 +2923,37 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="67" t="str">
+      <x:c r="A10" s="55" t="str">
         <x:v>林晓</x:v>
       </x:c>
-      <x:c r="B10" s="67" t="str">
+      <x:c r="B10" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C10" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D10" s="67" t="str">
+      <x:c r="C10" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D10" s="55" t="str">
         <x:v>基础·早班系数备选</x:v>
       </x:c>
-      <x:c r="E10" s="67" t="str">
+      <x:c r="E10" s="55" t="str">
         <x:v>系数保费</x:v>
       </x:c>
-      <x:c r="F10" s="67" t="str">
+      <x:c r="F10" s="55" t="str">
         <x:v>早班保费</x:v>
       </x:c>
-      <x:c r="G10" s="77" t="n">
+      <x:c r="G10" s="65" t="n">
         <x:f>'月度核算明细'!Z7</x:f>
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H10" s="118" t="n">
+      <x:c r="H10" s="101" t="n">
         <x:f>IF('月度核算明细'!S7&gt;=O10,M10,1)</x:f>
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="I10" s="77" t="n">
+      <x:c r="I10" s="65" t="n">
         <x:f>'月度核算明细'!AA7</x:f>
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="J10" s="103" t="n">
+      <x:c r="J10" s="86" t="n">
         <x:f>ROUND(G10*H10+I10,2)</x:f>
         <x:v>25000</x:v>
       </x:c>
@@ -3157,16 +2961,16 @@
       <x:c r="L10" s="3" t="str">
         <x:v>达阈值用设定系数，否则用1</x:v>
       </x:c>
-      <x:c r="M10" s="119" t="n">
+      <x:c r="M10" s="102" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="N10" s="120" t="str">
+      <x:c r="N10" s="103" t="str">
         <x:v>早班场次 ≥</x:v>
       </x:c>
-      <x:c r="O10" s="121" t="n">
+      <x:c r="O10" s="104" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P10" s="67" t="str">
+      <x:c r="P10" s="55" t="str">
         <x:v>g-premium-alternative</x:v>
       </x:c>
     </x:row>
@@ -3178,10 +2982,10 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C11" s="3" t="str">
-        <x:v>员工</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D11" s="3" t="str">
-        <x:v>签约员工·夜班补贴</x:v>
+        <x:v>全局补充·夜班补贴</x:v>
       </x:c>
       <x:c r="E11" s="3" t="str">
         <x:v>补贴</x:v>
@@ -3189,17 +2993,17 @@
       <x:c r="F11" s="3" t="str">
         <x:v>夜班场次</x:v>
       </x:c>
-      <x:c r="G11" s="75" t="n">
+      <x:c r="G11" s="63" t="n">
         <x:f>'月度核算明细'!R7</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H11" s="118" t="n">
+      <x:c r="H11" s="101" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I11" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="102" t="n">
+      <x:c r="I11" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="85" t="n">
         <x:f>ROUND(G11*H11+I11,2)</x:f>
         <x:v>150</x:v>
       </x:c>
@@ -3207,45 +3011,45 @@
       <x:c r="L11" s="3" t="str">
         <x:v>场次 × 每场补贴</x:v>
       </x:c>
-      <x:c r="M11" s="119"/>
-      <x:c r="N11" s="120"/>
-      <x:c r="O11" s="121"/>
+      <x:c r="M11" s="102"/>
+      <x:c r="N11" s="103"/>
+      <x:c r="O11" s="104"/>
       <x:c r="P11" s="3" t="str">
-        <x:v>e-night-allowance</x:v>
+        <x:v>g-extra-night-allowance</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="67" t="str">
+      <x:c r="A12" s="55" t="str">
         <x:v>林晓</x:v>
       </x:c>
-      <x:c r="B12" s="67" t="str">
+      <x:c r="B12" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C12" s="67" t="str">
-        <x:v>员工</x:v>
-      </x:c>
-      <x:c r="D12" s="67" t="str">
-        <x:v>签约员工·早班系数</x:v>
-      </x:c>
-      <x:c r="E12" s="67" t="str">
+      <x:c r="C12" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D12" s="55" t="str">
+        <x:v>全局补充·早班系数</x:v>
+      </x:c>
+      <x:c r="E12" s="55" t="str">
         <x:v>系数保费</x:v>
       </x:c>
-      <x:c r="F12" s="67" t="str">
+      <x:c r="F12" s="55" t="str">
         <x:v>早班保费</x:v>
       </x:c>
-      <x:c r="G12" s="77" t="n">
+      <x:c r="G12" s="65" t="n">
         <x:f>'月度核算明细'!Z7</x:f>
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H12" s="118" t="n">
+      <x:c r="H12" s="101" t="n">
         <x:f>IF('月度核算明细'!S7&gt;=O12,M12,1)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I12" s="77" t="n">
+      <x:c r="I12" s="65" t="n">
         <x:f>'月度核算明细'!AA7</x:f>
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="J12" s="103" t="n">
+      <x:c r="J12" s="86" t="n">
         <x:f>ROUND(G12*H12+I12,2)</x:f>
         <x:v>40000</x:v>
       </x:c>
@@ -3253,17 +3057,17 @@
       <x:c r="L12" s="3" t="str">
         <x:v>达阈值用设定系数，否则用1</x:v>
       </x:c>
-      <x:c r="M12" s="119" t="n">
+      <x:c r="M12" s="102" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="N12" s="120" t="str">
+      <x:c r="N12" s="103" t="str">
         <x:v>早班场次 ≥</x:v>
       </x:c>
-      <x:c r="O12" s="121" t="n">
+      <x:c r="O12" s="104" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P12" s="67" t="str">
-        <x:v>e-premium</x:v>
+      <x:c r="P12" s="55" t="str">
+        <x:v>g-extra-premium</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
@@ -3274,7 +3078,7 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C13" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D13" s="3" t="str">
         <x:v>基础·总时长保底</x:v>
@@ -3285,17 +3089,17 @@
       <x:c r="F13" s="3" t="str">
         <x:v>总直播时长</x:v>
       </x:c>
-      <x:c r="G13" s="75" t="n">
+      <x:c r="G13" s="63" t="n">
         <x:f>'月度核算明细'!N7</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H13" s="118" t="n">
+      <x:c r="H13" s="101" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="I13" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="102" t="n">
+      <x:c r="I13" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="85" t="n">
         <x:f>ROUND(G13*H13+I13,2)</x:f>
         <x:v>5000</x:v>
       </x:c>
@@ -3303,43 +3107,43 @@
       <x:c r="L13" s="3" t="str">
         <x:v>所选时长 × 规则时薪</x:v>
       </x:c>
-      <x:c r="M13" s="119"/>
-      <x:c r="N13" s="120"/>
-      <x:c r="O13" s="121"/>
+      <x:c r="M13" s="102"/>
+      <x:c r="N13" s="103"/>
+      <x:c r="O13" s="104"/>
       <x:c r="P13" s="3" t="str">
         <x:v>g-floor-total</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="67" t="str">
+      <x:c r="A14" s="55" t="str">
         <x:v>林晓</x:v>
       </x:c>
-      <x:c r="B14" s="67" t="str">
+      <x:c r="B14" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C14" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D14" s="67" t="str">
+      <x:c r="C14" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D14" s="55" t="str">
         <x:v>基础·夜班保底</x:v>
       </x:c>
-      <x:c r="E14" s="67" t="str">
+      <x:c r="E14" s="55" t="str">
         <x:v>保底</x:v>
       </x:c>
-      <x:c r="F14" s="67" t="str">
+      <x:c r="F14" s="55" t="str">
         <x:v>夜班直播时长</x:v>
       </x:c>
-      <x:c r="G14" s="77" t="n">
+      <x:c r="G14" s="65" t="n">
         <x:f>'月度核算明细'!O7</x:f>
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H14" s="118" t="n">
+      <x:c r="H14" s="101" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="I14" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J14" s="103" t="n">
+      <x:c r="I14" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="86" t="n">
         <x:f>ROUND(G14*H14+I14,2)</x:f>
         <x:v>4000</x:v>
       </x:c>
@@ -3347,10 +3151,10 @@
       <x:c r="L14" s="3" t="str">
         <x:v>所选时长 × 规则时薪</x:v>
       </x:c>
-      <x:c r="M14" s="119"/>
-      <x:c r="N14" s="120"/>
-      <x:c r="O14" s="121"/>
-      <x:c r="P14" s="67" t="str">
+      <x:c r="M14" s="102"/>
+      <x:c r="N14" s="103"/>
+      <x:c r="O14" s="104"/>
+      <x:c r="P14" s="55" t="str">
         <x:v>g-floor-night</x:v>
       </x:c>
     </x:row>
@@ -3362,7 +3166,7 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C15" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D15" s="3" t="str">
         <x:v>基础·ROI加成</x:v>
@@ -3373,18 +3177,18 @@
       <x:c r="F15" s="3" t="str">
         <x:v>总直播时长</x:v>
       </x:c>
-      <x:c r="G15" s="75" t="n">
+      <x:c r="G15" s="63" t="n">
         <x:f>'月度核算明细'!N7</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H15" s="118" t="n">
+      <x:c r="H15" s="101" t="n">
         <x:f>IF(AND('员工月薪汇总'!H17&gt;=0,'员工月薪汇总'!H17&lt;3),20,IF('员工月薪汇总'!H17&gt;=3,45,NA()))</x:f>
         <x:v>45</x:v>
       </x:c>
-      <x:c r="I15" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="102" t="n">
+      <x:c r="I15" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="85" t="n">
         <x:f>ROUND(G15*H15+I15,2)</x:f>
         <x:v>4500</x:v>
       </x:c>
@@ -3392,44 +3196,44 @@
       <x:c r="L15" s="3" t="str">
         <x:v>有效ROI：低于3为20；≥3为45</x:v>
       </x:c>
-      <x:c r="M15" s="119"/>
-      <x:c r="N15" s="120"/>
-      <x:c r="O15" s="121"/>
+      <x:c r="M15" s="102"/>
+      <x:c r="N15" s="103"/>
+      <x:c r="O15" s="104"/>
       <x:c r="P15" s="3" t="str">
         <x:v>g-roi-addition</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="67" t="str">
+      <x:c r="A16" s="55" t="str">
         <x:v>林晓</x:v>
       </x:c>
-      <x:c r="B16" s="67" t="str">
+      <x:c r="B16" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C16" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D16" s="67" t="str">
+      <x:c r="C16" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D16" s="55" t="str">
         <x:v>基础·排名加成</x:v>
       </x:c>
-      <x:c r="E16" s="67" t="str">
+      <x:c r="E16" s="55" t="str">
         <x:v>加成</x:v>
       </x:c>
-      <x:c r="F16" s="67" t="str">
+      <x:c r="F16" s="55" t="str">
         <x:v>总直播时长</x:v>
       </x:c>
-      <x:c r="G16" s="77" t="n">
+      <x:c r="G16" s="65" t="n">
         <x:f>'月度核算明细'!N7</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H16" s="118" t="n">
-        <x:f>IF('员工月薪汇总'!I17=1,10,IF('员工月薪汇总'!I17&gt;=2,5,NA()))</x:f>
+      <x:c r="H16" s="101" t="n">
+        <x:f>IF(AND('员工月薪汇总'!I17&gt;=1,'员工月薪汇总'!I17&lt;=1),10,IF('员工月薪汇总'!I17&gt;=2,5,NA()))</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I16" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J16" s="103" t="n">
+      <x:c r="I16" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="86" t="n">
         <x:f>ROUND(G16*H16+I16,2)</x:f>
         <x:v>1000</x:v>
       </x:c>
@@ -3437,10 +3241,10 @@
       <x:c r="L16" s="3" t="str">
         <x:v>有效排名：第1为10；其余为5</x:v>
       </x:c>
-      <x:c r="M16" s="119"/>
-      <x:c r="N16" s="120"/>
-      <x:c r="O16" s="121"/>
-      <x:c r="P16" s="67" t="str">
+      <x:c r="M16" s="102"/>
+      <x:c r="N16" s="103"/>
+      <x:c r="O16" s="104"/>
+      <x:c r="P16" s="55" t="str">
         <x:v>g-rank-addition</x:v>
       </x:c>
     </x:row>
@@ -3463,17 +3267,17 @@
       <x:c r="F17" s="3" t="str">
         <x:v>正常直播时长</x:v>
       </x:c>
-      <x:c r="G17" s="75" t="n">
+      <x:c r="G17" s="63" t="n">
         <x:f>'月度核算明细'!Q7</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H17" s="118" t="n">
+      <x:c r="H17" s="101" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I17" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="102" t="n">
+      <x:c r="I17" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="85" t="n">
         <x:f>ROUND(G17*H17+I17,2)</x:f>
         <x:v>1000</x:v>
       </x:c>
@@ -3481,43 +3285,43 @@
       <x:c r="L17" s="3" t="str">
         <x:v>所选时长 × 规则时薪</x:v>
       </x:c>
-      <x:c r="M17" s="119"/>
-      <x:c r="N17" s="120"/>
-      <x:c r="O17" s="121"/>
+      <x:c r="M17" s="102"/>
+      <x:c r="N17" s="103"/>
+      <x:c r="O17" s="104"/>
       <x:c r="P17" s="3" t="str">
         <x:v>r-regular-addition</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
-      <x:c r="A18" s="67" t="str">
+      <x:c r="A18" s="55" t="str">
         <x:v>林晓</x:v>
       </x:c>
-      <x:c r="B18" s="67" t="str">
+      <x:c r="B18" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C18" s="67" t="str">
-        <x:v>员工</x:v>
-      </x:c>
-      <x:c r="D18" s="67" t="str">
-        <x:v>签约员工·早班保底</x:v>
-      </x:c>
-      <x:c r="E18" s="67" t="str">
+      <x:c r="C18" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D18" s="55" t="str">
+        <x:v>全局补充·早班保底</x:v>
+      </x:c>
+      <x:c r="E18" s="55" t="str">
         <x:v>保底</x:v>
       </x:c>
-      <x:c r="F18" s="67" t="str">
+      <x:c r="F18" s="55" t="str">
         <x:v>早班直播时长</x:v>
       </x:c>
-      <x:c r="G18" s="77" t="n">
+      <x:c r="G18" s="65" t="n">
         <x:f>'月度核算明细'!P7</x:f>
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H18" s="118" t="n">
+      <x:c r="H18" s="101" t="n">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="I18" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J18" s="103" t="n">
+      <x:c r="I18" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="86" t="n">
         <x:f>ROUND(G18*H18+I18,2)</x:f>
         <x:v>6600</x:v>
       </x:c>
@@ -3525,11 +3329,11 @@
       <x:c r="L18" s="3" t="str">
         <x:v>所选时长 × 规则时薪</x:v>
       </x:c>
-      <x:c r="M18" s="119"/>
-      <x:c r="N18" s="120"/>
-      <x:c r="O18" s="121"/>
-      <x:c r="P18" s="67" t="str">
-        <x:v>e-floor-early</x:v>
+      <x:c r="M18" s="102"/>
+      <x:c r="N18" s="103"/>
+      <x:c r="O18" s="104"/>
+      <x:c r="P18" s="55" t="str">
+        <x:v>g-extra-floor-early</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
@@ -3540,10 +3344,10 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C19" s="3" t="str">
-        <x:v>员工</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D19" s="3" t="str">
-        <x:v>签约员工·总时长保底</x:v>
+        <x:v>全局补充·总时长保底</x:v>
       </x:c>
       <x:c r="E19" s="3" t="str">
         <x:v>保底</x:v>
@@ -3551,17 +3355,17 @@
       <x:c r="F19" s="3" t="str">
         <x:v>总直播时长</x:v>
       </x:c>
-      <x:c r="G19" s="75" t="n">
+      <x:c r="G19" s="63" t="n">
         <x:f>'月度核算明细'!N7</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H19" s="118" t="n">
+      <x:c r="H19" s="101" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="I19" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J19" s="102" t="n">
+      <x:c r="I19" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="85" t="n">
         <x:f>ROUND(G19*H19+I19,2)</x:f>
         <x:v>5500</x:v>
       </x:c>
@@ -3569,43 +3373,43 @@
       <x:c r="L19" s="3" t="str">
         <x:v>所选时长 × 规则时薪</x:v>
       </x:c>
-      <x:c r="M19" s="119"/>
-      <x:c r="N19" s="120"/>
-      <x:c r="O19" s="121"/>
+      <x:c r="M19" s="102"/>
+      <x:c r="N19" s="103"/>
+      <x:c r="O19" s="104"/>
       <x:c r="P19" s="3" t="str">
-        <x:v>e-floor-total</x:v>
+        <x:v>g-extra-floor-total</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
-      <x:c r="A20" s="67" t="str">
+      <x:c r="A20" s="55" t="str">
         <x:v>林晓</x:v>
       </x:c>
-      <x:c r="B20" s="67" t="str">
+      <x:c r="B20" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C20" s="67" t="str">
-        <x:v>员工</x:v>
-      </x:c>
-      <x:c r="D20" s="67" t="str">
-        <x:v>签约员工·早班加成</x:v>
-      </x:c>
-      <x:c r="E20" s="67" t="str">
+      <x:c r="C20" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D20" s="55" t="str">
+        <x:v>全局补充·早班加成</x:v>
+      </x:c>
+      <x:c r="E20" s="55" t="str">
         <x:v>加成</x:v>
       </x:c>
-      <x:c r="F20" s="67" t="str">
+      <x:c r="F20" s="55" t="str">
         <x:v>早班直播时长</x:v>
       </x:c>
-      <x:c r="G20" s="77" t="n">
+      <x:c r="G20" s="65" t="n">
         <x:f>'月度核算明细'!P7</x:f>
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H20" s="118" t="n">
+      <x:c r="H20" s="101" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I20" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J20" s="103" t="n">
+      <x:c r="I20" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J20" s="86" t="n">
         <x:f>ROUND(G20*H20+I20,2)</x:f>
         <x:v>300</x:v>
       </x:c>
@@ -3613,11 +3417,11 @@
       <x:c r="L20" s="3" t="str">
         <x:v>所选时长 × 规则时薪</x:v>
       </x:c>
-      <x:c r="M20" s="119"/>
-      <x:c r="N20" s="120"/>
-      <x:c r="O20" s="121"/>
-      <x:c r="P20" s="67" t="str">
-        <x:v>e-early-addition</x:v>
+      <x:c r="M20" s="102"/>
+      <x:c r="N20" s="103"/>
+      <x:c r="O20" s="104"/>
+      <x:c r="P20" s="55" t="str">
+        <x:v>g-extra-early-addition</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
@@ -3628,7 +3432,7 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C21" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D21" s="3" t="str">
         <x:v>基础·夜班补贴</x:v>
@@ -3639,17 +3443,17 @@
       <x:c r="F21" s="3" t="str">
         <x:v>夜班场次</x:v>
       </x:c>
-      <x:c r="G21" s="75" t="n">
+      <x:c r="G21" s="63" t="n">
         <x:f>'月度核算明细'!R8</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H21" s="118" t="n">
+      <x:c r="H21" s="101" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I21" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J21" s="102" t="n">
+      <x:c r="I21" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J21" s="85" t="n">
         <x:f>ROUND(G21*H21+I21,2)</x:f>
         <x:v>100</x:v>
       </x:c>
@@ -3657,43 +3461,43 @@
       <x:c r="L21" s="3" t="str">
         <x:v>场次 × 每场补贴</x:v>
       </x:c>
-      <x:c r="M21" s="119"/>
-      <x:c r="N21" s="120"/>
-      <x:c r="O21" s="121"/>
+      <x:c r="M21" s="102"/>
+      <x:c r="N21" s="103"/>
+      <x:c r="O21" s="104"/>
       <x:c r="P21" s="3" t="str">
         <x:v>g-night-allowance</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
-      <x:c r="A22" s="67" t="str">
+      <x:c r="A22" s="55" t="str">
         <x:v>周宁</x:v>
       </x:c>
-      <x:c r="B22" s="67" t="str">
+      <x:c r="B22" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C22" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D22" s="67" t="str">
+      <x:c r="C22" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D22" s="55" t="str">
         <x:v>基础·早班补贴</x:v>
       </x:c>
-      <x:c r="E22" s="67" t="str">
+      <x:c r="E22" s="55" t="str">
         <x:v>补贴</x:v>
       </x:c>
-      <x:c r="F22" s="67" t="str">
+      <x:c r="F22" s="55" t="str">
         <x:v>早班场次</x:v>
       </x:c>
-      <x:c r="G22" s="77" t="n">
+      <x:c r="G22" s="65" t="n">
         <x:f>'月度核算明细'!S8</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H22" s="118" t="n">
+      <x:c r="H22" s="101" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I22" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J22" s="103" t="n">
+      <x:c r="I22" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J22" s="86" t="n">
         <x:f>ROUND(G22*H22+I22,2)</x:f>
         <x:v>20</x:v>
       </x:c>
@@ -3701,10 +3505,10 @@
       <x:c r="L22" s="3" t="str">
         <x:v>场次 × 每场补贴</x:v>
       </x:c>
-      <x:c r="M22" s="119"/>
-      <x:c r="N22" s="120"/>
-      <x:c r="O22" s="121"/>
-      <x:c r="P22" s="67" t="str">
+      <x:c r="M22" s="102"/>
+      <x:c r="N22" s="103"/>
+      <x:c r="O22" s="104"/>
+      <x:c r="P22" s="55" t="str">
         <x:v>g-early-allowance</x:v>
       </x:c>
     </x:row>
@@ -3716,7 +3520,7 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C23" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D23" s="3" t="str">
         <x:v>基础·早班系数</x:v>
@@ -3727,19 +3531,19 @@
       <x:c r="F23" s="3" t="str">
         <x:v>早班保费</x:v>
       </x:c>
-      <x:c r="G23" s="75" t="n">
+      <x:c r="G23" s="63" t="n">
         <x:f>'月度核算明细'!Z8</x:f>
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="H23" s="118" t="n">
+      <x:c r="H23" s="101" t="n">
         <x:f>IF('月度核算明细'!S8&gt;=O23,M23,1)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I23" s="75" t="n">
+      <x:c r="I23" s="63" t="n">
         <x:f>'月度核算明细'!AA8</x:f>
         <x:v>24000</x:v>
       </x:c>
-      <x:c r="J23" s="102" t="n">
+      <x:c r="J23" s="85" t="n">
         <x:f>ROUND(G23*H23+I23,2)</x:f>
         <x:v>28000</x:v>
       </x:c>
@@ -3747,13 +3551,13 @@
       <x:c r="L23" s="3" t="str">
         <x:v>达阈值用设定系数，否则用1</x:v>
       </x:c>
-      <x:c r="M23" s="119" t="n">
+      <x:c r="M23" s="102" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N23" s="120" t="str">
+      <x:c r="N23" s="103" t="str">
         <x:v>早班场次 ≥</x:v>
       </x:c>
-      <x:c r="O23" s="121" t="n">
+      <x:c r="O23" s="104" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P23" s="3" t="str">
@@ -3761,37 +3565,37 @@
       </x:c>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
-      <x:c r="A24" s="67" t="str">
+      <x:c r="A24" s="55" t="str">
         <x:v>周宁</x:v>
       </x:c>
-      <x:c r="B24" s="67" t="str">
+      <x:c r="B24" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C24" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D24" s="67" t="str">
+      <x:c r="C24" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D24" s="55" t="str">
         <x:v>基础·早班系数备选</x:v>
       </x:c>
-      <x:c r="E24" s="67" t="str">
+      <x:c r="E24" s="55" t="str">
         <x:v>系数保费</x:v>
       </x:c>
-      <x:c r="F24" s="67" t="str">
+      <x:c r="F24" s="55" t="str">
         <x:v>早班保费</x:v>
       </x:c>
-      <x:c r="G24" s="77" t="n">
+      <x:c r="G24" s="65" t="n">
         <x:f>'月度核算明细'!Z8</x:f>
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="H24" s="118" t="n">
+      <x:c r="H24" s="101" t="n">
         <x:f>IF('月度核算明细'!S8&gt;=O24,M24,1)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I24" s="77" t="n">
+      <x:c r="I24" s="65" t="n">
         <x:f>'月度核算明细'!AA8</x:f>
         <x:v>24000</x:v>
       </x:c>
-      <x:c r="J24" s="103" t="n">
+      <x:c r="J24" s="86" t="n">
         <x:f>ROUND(G24*H24+I24,2)</x:f>
         <x:v>28000</x:v>
       </x:c>
@@ -3799,16 +3603,16 @@
       <x:c r="L24" s="3" t="str">
         <x:v>达阈值用设定系数，否则用1</x:v>
       </x:c>
-      <x:c r="M24" s="119" t="n">
+      <x:c r="M24" s="102" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="N24" s="120" t="str">
+      <x:c r="N24" s="103" t="str">
         <x:v>早班场次 ≥</x:v>
       </x:c>
-      <x:c r="O24" s="121" t="n">
+      <x:c r="O24" s="104" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P24" s="67" t="str">
+      <x:c r="P24" s="55" t="str">
         <x:v>g-premium-alternative</x:v>
       </x:c>
     </x:row>
@@ -3820,84 +3624,92 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C25" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D25" s="3" t="str">
-        <x:v>基础·总时长保底</x:v>
+        <x:v>全局补充·夜班补贴</x:v>
       </x:c>
       <x:c r="E25" s="3" t="str">
-        <x:v>保底</x:v>
+        <x:v>补贴</x:v>
       </x:c>
       <x:c r="F25" s="3" t="str">
-        <x:v>总直播时长</x:v>
-      </x:c>
-      <x:c r="G25" s="75" t="n">
-        <x:f>'月度核算明细'!N8</x:f>
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H25" s="118" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I25" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J25" s="102" t="n">
+        <x:v>夜班场次</x:v>
+      </x:c>
+      <x:c r="G25" s="63" t="n">
+        <x:f>'月度核算明细'!R8</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H25" s="101" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I25" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J25" s="85" t="n">
         <x:f>ROUND(G25*H25+I25,2)</x:f>
-        <x:v>4000</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K25" s="3"/>
       <x:c r="L25" s="3" t="str">
-        <x:v>所选时长 × 规则时薪</x:v>
-      </x:c>
-      <x:c r="M25" s="119"/>
-      <x:c r="N25" s="120"/>
-      <x:c r="O25" s="121"/>
+        <x:v>场次 × 每场补贴</x:v>
+      </x:c>
+      <x:c r="M25" s="102"/>
+      <x:c r="N25" s="103"/>
+      <x:c r="O25" s="104"/>
       <x:c r="P25" s="3" t="str">
-        <x:v>g-floor-total</x:v>
+        <x:v>g-extra-night-allowance</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
-      <x:c r="A26" s="67" t="str">
+      <x:c r="A26" s="55" t="str">
         <x:v>周宁</x:v>
       </x:c>
-      <x:c r="B26" s="67" t="str">
+      <x:c r="B26" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C26" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D26" s="67" t="str">
-        <x:v>基础·夜班保底</x:v>
-      </x:c>
-      <x:c r="E26" s="67" t="str">
-        <x:v>保底</x:v>
-      </x:c>
-      <x:c r="F26" s="67" t="str">
-        <x:v>夜班直播时长</x:v>
-      </x:c>
-      <x:c r="G26" s="77" t="n">
-        <x:f>'月度核算明细'!O8</x:f>
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H26" s="118" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="I26" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J26" s="103" t="n">
+      <x:c r="C26" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D26" s="55" t="str">
+        <x:v>全局补充·早班系数</x:v>
+      </x:c>
+      <x:c r="E26" s="55" t="str">
+        <x:v>系数保费</x:v>
+      </x:c>
+      <x:c r="F26" s="55" t="str">
+        <x:v>早班保费</x:v>
+      </x:c>
+      <x:c r="G26" s="65" t="n">
+        <x:f>'月度核算明细'!Z8</x:f>
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="H26" s="101" t="n">
+        <x:f>IF('月度核算明细'!S8&gt;=O26,M26,1)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I26" s="65" t="n">
+        <x:f>'月度核算明细'!AA8</x:f>
+        <x:v>24000</x:v>
+      </x:c>
+      <x:c r="J26" s="86" t="n">
         <x:f>ROUND(G26*H26+I26,2)</x:f>
-        <x:v>4000</x:v>
+        <x:v>28000</x:v>
       </x:c>
       <x:c r="K26" s="3"/>
       <x:c r="L26" s="3" t="str">
-        <x:v>所选时长 × 规则时薪</x:v>
-      </x:c>
-      <x:c r="M26" s="119"/>
-      <x:c r="N26" s="120"/>
-      <x:c r="O26" s="121"/>
-      <x:c r="P26" s="67" t="str">
-        <x:v>g-floor-night</x:v>
+        <x:v>达阈值用设定系数，否则用1</x:v>
+      </x:c>
+      <x:c r="M26" s="102" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N26" s="103" t="str">
+        <x:v>早班场次 ≥</x:v>
+      </x:c>
+      <x:c r="O26" s="104" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P26" s="55" t="str">
+        <x:v>g-extra-premium</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
@@ -3908,86 +3720,84 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C27" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D27" s="3" t="str">
-        <x:v>基础·ROI加成</x:v>
+        <x:v>基础·总时长保底</x:v>
       </x:c>
       <x:c r="E27" s="3" t="str">
-        <x:v>加成</x:v>
+        <x:v>保底</x:v>
       </x:c>
       <x:c r="F27" s="3" t="str">
         <x:v>总直播时长</x:v>
       </x:c>
-      <x:c r="G27" s="75" t="n">
+      <x:c r="G27" s="63" t="n">
         <x:f>'月度核算明细'!N8</x:f>
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H27" s="118" t="n">
-        <x:f>IF(AND('员工月薪汇总'!H18&gt;=0,'员工月薪汇总'!H18&lt;3),20,IF('员工月薪汇总'!H18&gt;=3,45,NA()))</x:f>
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I27" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J27" s="102" t="n">
+      <x:c r="H27" s="101" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I27" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27" s="85" t="n">
         <x:f>ROUND(G27*H27+I27,2)</x:f>
-        <x:v>1600</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="K27" s="3"/>
       <x:c r="L27" s="3" t="str">
-        <x:v>有效ROI：低于3为20；≥3为45</x:v>
-      </x:c>
-      <x:c r="M27" s="119"/>
-      <x:c r="N27" s="120"/>
-      <x:c r="O27" s="121"/>
+        <x:v>所选时长 × 规则时薪</x:v>
+      </x:c>
+      <x:c r="M27" s="102"/>
+      <x:c r="N27" s="103"/>
+      <x:c r="O27" s="104"/>
       <x:c r="P27" s="3" t="str">
-        <x:v>g-roi-addition</x:v>
+        <x:v>g-floor-total</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
-      <x:c r="A28" s="67" t="str">
+      <x:c r="A28" s="55" t="str">
         <x:v>周宁</x:v>
       </x:c>
-      <x:c r="B28" s="67" t="str">
+      <x:c r="B28" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C28" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D28" s="67" t="str">
-        <x:v>基础·排名加成</x:v>
-      </x:c>
-      <x:c r="E28" s="67" t="str">
-        <x:v>加成</x:v>
-      </x:c>
-      <x:c r="F28" s="67" t="str">
-        <x:v>总直播时长</x:v>
-      </x:c>
-      <x:c r="G28" s="77" t="n">
-        <x:f>'月度核算明细'!N8</x:f>
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H28" s="118" t="n">
-        <x:f>IF('员工月薪汇总'!I18=1,10,IF('员工月薪汇总'!I18&gt;=2,5,NA()))</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I28" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J28" s="103" t="n">
+      <x:c r="C28" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D28" s="55" t="str">
+        <x:v>基础·夜班保底</x:v>
+      </x:c>
+      <x:c r="E28" s="55" t="str">
+        <x:v>保底</x:v>
+      </x:c>
+      <x:c r="F28" s="55" t="str">
+        <x:v>夜班直播时长</x:v>
+      </x:c>
+      <x:c r="G28" s="65" t="n">
+        <x:f>'月度核算明细'!O8</x:f>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H28" s="101" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="I28" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28" s="86" t="n">
         <x:f>ROUND(G28*H28+I28,2)</x:f>
-        <x:v>400</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="K28" s="3"/>
       <x:c r="L28" s="3" t="str">
-        <x:v>有效排名：第1为10；其余为5</x:v>
-      </x:c>
-      <x:c r="M28" s="119"/>
-      <x:c r="N28" s="120"/>
-      <x:c r="O28" s="121"/>
-      <x:c r="P28" s="67" t="str">
-        <x:v>g-rank-addition</x:v>
+        <x:v>所选时长 × 规则时薪</x:v>
+      </x:c>
+      <x:c r="M28" s="102"/>
+      <x:c r="N28" s="103"/>
+      <x:c r="O28" s="104"/>
+      <x:c r="P28" s="55" t="str">
+        <x:v>g-floor-night</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
@@ -3998,276 +3808,262 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C29" s="3" t="str">
-        <x:v>直播间</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D29" s="3" t="str">
-        <x:v>双房共用·正常时段加成</x:v>
+        <x:v>基础·ROI加成</x:v>
       </x:c>
       <x:c r="E29" s="3" t="str">
         <x:v>加成</x:v>
       </x:c>
       <x:c r="F29" s="3" t="str">
+        <x:v>总直播时长</x:v>
+      </x:c>
+      <x:c r="G29" s="63" t="n">
+        <x:f>'月度核算明细'!N8</x:f>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H29" s="101" t="n">
+        <x:f>IF(AND('员工月薪汇总'!H18&gt;=0,'员工月薪汇总'!H18&lt;3),20,IF('员工月薪汇总'!H18&gt;=3,45,NA()))</x:f>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I29" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J29" s="85" t="n">
+        <x:f>ROUND(G29*H29+I29,2)</x:f>
+        <x:v>1600</x:v>
+      </x:c>
+      <x:c r="K29" s="3"/>
+      <x:c r="L29" s="3" t="str">
+        <x:v>有效ROI：低于3为20；≥3为45</x:v>
+      </x:c>
+      <x:c r="M29" s="102"/>
+      <x:c r="N29" s="103"/>
+      <x:c r="O29" s="104"/>
+      <x:c r="P29" s="3" t="str">
+        <x:v>g-roi-addition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="55" t="str">
+        <x:v>周宁</x:v>
+      </x:c>
+      <x:c r="B30" s="55" t="str">
+        <x:v>示例一号房</x:v>
+      </x:c>
+      <x:c r="C30" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D30" s="55" t="str">
+        <x:v>基础·排名加成</x:v>
+      </x:c>
+      <x:c r="E30" s="55" t="str">
+        <x:v>加成</x:v>
+      </x:c>
+      <x:c r="F30" s="55" t="str">
+        <x:v>总直播时长</x:v>
+      </x:c>
+      <x:c r="G30" s="65" t="n">
+        <x:f>'月度核算明细'!N8</x:f>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H30" s="101" t="n">
+        <x:f>IF(AND('员工月薪汇总'!I18&gt;=1,'员工月薪汇总'!I18&lt;=1),10,IF('员工月薪汇总'!I18&gt;=2,5,NA()))</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I30" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J30" s="86" t="n">
+        <x:f>ROUND(G30*H30+I30,2)</x:f>
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="K30" s="3"/>
+      <x:c r="L30" s="3" t="str">
+        <x:v>有效排名：第1为10；其余为5</x:v>
+      </x:c>
+      <x:c r="M30" s="102"/>
+      <x:c r="N30" s="103"/>
+      <x:c r="O30" s="104"/>
+      <x:c r="P30" s="55" t="str">
+        <x:v>g-rank-addition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="24" customHeight="1">
+      <x:c r="A31" s="3" t="str">
+        <x:v>周宁</x:v>
+      </x:c>
+      <x:c r="B31" s="3" t="str">
+        <x:v>示例一号房</x:v>
+      </x:c>
+      <x:c r="C31" s="3" t="str">
+        <x:v>直播间</x:v>
+      </x:c>
+      <x:c r="D31" s="3" t="str">
+        <x:v>双房共用·正常时段加成</x:v>
+      </x:c>
+      <x:c r="E31" s="3" t="str">
+        <x:v>加成</x:v>
+      </x:c>
+      <x:c r="F31" s="3" t="str">
         <x:v>正常直播时长</x:v>
       </x:c>
-      <x:c r="G29" s="75" t="n">
+      <x:c r="G31" s="63" t="n">
         <x:f>'月度核算明细'!Q8</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H29" s="118" t="n">
+      <x:c r="H31" s="101" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I29" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J29" s="102" t="n">
-        <x:f>ROUND(G29*H29+I29,2)</x:f>
+      <x:c r="I31" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J31" s="85" t="n">
+        <x:f>ROUND(G31*H31+I31,2)</x:f>
         <x:v>1000</x:v>
-      </x:c>
-      <x:c r="K29" s="3"/>
-      <x:c r="L29" s="3" t="str">
-        <x:v>所选时长 × 规则时薪</x:v>
-      </x:c>
-      <x:c r="M29" s="119"/>
-      <x:c r="N29" s="120"/>
-      <x:c r="O29" s="121"/>
-      <x:c r="P29" s="3" t="str">
-        <x:v>r-regular-addition</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="24" customHeight="1">
-      <x:c r="A30" s="67" t="str">
-        <x:v>陈雨</x:v>
-      </x:c>
-      <x:c r="B30" s="67" t="str">
-        <x:v>示例一号房</x:v>
-      </x:c>
-      <x:c r="C30" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D30" s="67" t="str">
-        <x:v>基础·夜班补贴</x:v>
-      </x:c>
-      <x:c r="E30" s="67" t="str">
-        <x:v>补贴</x:v>
-      </x:c>
-      <x:c r="F30" s="67" t="str">
-        <x:v>夜班场次</x:v>
-      </x:c>
-      <x:c r="G30" s="77" t="n">
-        <x:f>'月度核算明细'!R9</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H30" s="118" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I30" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J30" s="103" t="n">
-        <x:f>ROUND(G30*H30+I30,2)</x:f>
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="K30" s="3"/>
-      <x:c r="L30" s="3" t="str">
-        <x:v>场次 × 每场补贴</x:v>
-      </x:c>
-      <x:c r="M30" s="119"/>
-      <x:c r="N30" s="120"/>
-      <x:c r="O30" s="121"/>
-      <x:c r="P30" s="67" t="str">
-        <x:v>g-night-allowance</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="24" customHeight="1">
-      <x:c r="A31" s="3" t="str">
-        <x:v>陈雨</x:v>
-      </x:c>
-      <x:c r="B31" s="3" t="str">
-        <x:v>示例一号房</x:v>
-      </x:c>
-      <x:c r="C31" s="3" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D31" s="3" t="str">
-        <x:v>基础·早班补贴</x:v>
-      </x:c>
-      <x:c r="E31" s="3" t="str">
-        <x:v>补贴</x:v>
-      </x:c>
-      <x:c r="F31" s="3" t="str">
-        <x:v>早班场次</x:v>
-      </x:c>
-      <x:c r="G31" s="75" t="n">
-        <x:f>'月度核算明细'!S9</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H31" s="118" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I31" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J31" s="102" t="n">
-        <x:f>ROUND(G31*H31+I31,2)</x:f>
-        <x:v>60</x:v>
       </x:c>
       <x:c r="K31" s="3"/>
       <x:c r="L31" s="3" t="str">
-        <x:v>场次 × 每场补贴</x:v>
-      </x:c>
-      <x:c r="M31" s="119"/>
-      <x:c r="N31" s="120"/>
-      <x:c r="O31" s="121"/>
+        <x:v>所选时长 × 规则时薪</x:v>
+      </x:c>
+      <x:c r="M31" s="102"/>
+      <x:c r="N31" s="103"/>
+      <x:c r="O31" s="104"/>
       <x:c r="P31" s="3" t="str">
-        <x:v>g-early-allowance</x:v>
+        <x:v>r-regular-addition</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
-      <x:c r="A32" s="67" t="str">
-        <x:v>陈雨</x:v>
-      </x:c>
-      <x:c r="B32" s="67" t="str">
+      <x:c r="A32" s="55" t="str">
+        <x:v>周宁</x:v>
+      </x:c>
+      <x:c r="B32" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C32" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D32" s="67" t="str">
-        <x:v>基础·早班系数</x:v>
-      </x:c>
-      <x:c r="E32" s="67" t="str">
-        <x:v>系数保费</x:v>
-      </x:c>
-      <x:c r="F32" s="67" t="str">
-        <x:v>早班保费</x:v>
-      </x:c>
-      <x:c r="G32" s="77" t="n">
-        <x:f>'月度核算明细'!Z9</x:f>
-        <x:v>6000</x:v>
-      </x:c>
-      <x:c r="H32" s="118" t="n">
-        <x:f>IF('月度核算明细'!S9&gt;=O32,M32,1)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I32" s="77" t="n">
-        <x:f>'月度核算明细'!AA9</x:f>
-        <x:v>18000</x:v>
-      </x:c>
-      <x:c r="J32" s="103" t="n">
+      <x:c r="C32" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D32" s="55" t="str">
+        <x:v>全局补充·早班保底</x:v>
+      </x:c>
+      <x:c r="E32" s="55" t="str">
+        <x:v>保底</x:v>
+      </x:c>
+      <x:c r="F32" s="55" t="str">
+        <x:v>早班直播时长</x:v>
+      </x:c>
+      <x:c r="G32" s="65" t="n">
+        <x:f>'月度核算明细'!P8</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H32" s="101" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I32" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32" s="86" t="n">
         <x:f>ROUND(G32*H32+I32,2)</x:f>
-        <x:v>30000</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="K32" s="3"/>
       <x:c r="L32" s="3" t="str">
-        <x:v>达阈值用设定系数，否则用1</x:v>
-      </x:c>
-      <x:c r="M32" s="119" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N32" s="120" t="str">
-        <x:v>早班场次 ≥</x:v>
-      </x:c>
-      <x:c r="O32" s="121" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="P32" s="67" t="str">
-        <x:v>g-premium</x:v>
+        <x:v>所选时长 × 规则时薪</x:v>
+      </x:c>
+      <x:c r="M32" s="102"/>
+      <x:c r="N32" s="103"/>
+      <x:c r="O32" s="104"/>
+      <x:c r="P32" s="55" t="str">
+        <x:v>g-extra-floor-early</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="24" customHeight="1">
       <x:c r="A33" s="3" t="str">
-        <x:v>陈雨</x:v>
+        <x:v>周宁</x:v>
       </x:c>
       <x:c r="B33" s="3" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C33" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D33" s="3" t="str">
-        <x:v>基础·早班系数备选</x:v>
+        <x:v>全局补充·总时长保底</x:v>
       </x:c>
       <x:c r="E33" s="3" t="str">
-        <x:v>系数保费</x:v>
+        <x:v>保底</x:v>
       </x:c>
       <x:c r="F33" s="3" t="str">
-        <x:v>早班保费</x:v>
-      </x:c>
-      <x:c r="G33" s="75" t="n">
-        <x:f>'月度核算明细'!Z9</x:f>
-        <x:v>6000</x:v>
-      </x:c>
-      <x:c r="H33" s="118" t="n">
-        <x:f>IF('月度核算明细'!S9&gt;=O33,M33,1)</x:f>
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="I33" s="75" t="n">
-        <x:f>'月度核算明细'!AA9</x:f>
-        <x:v>18000</x:v>
-      </x:c>
-      <x:c r="J33" s="102" t="n">
+        <x:v>总直播时长</x:v>
+      </x:c>
+      <x:c r="G33" s="63" t="n">
+        <x:f>'月度核算明细'!N8</x:f>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H33" s="101" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I33" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J33" s="85" t="n">
         <x:f>ROUND(G33*H33+I33,2)</x:f>
-        <x:v>27000</x:v>
+        <x:v>4400</x:v>
       </x:c>
       <x:c r="K33" s="3"/>
       <x:c r="L33" s="3" t="str">
-        <x:v>达阈值用设定系数，否则用1</x:v>
-      </x:c>
-      <x:c r="M33" s="119" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="N33" s="120" t="str">
-        <x:v>早班场次 ≥</x:v>
-      </x:c>
-      <x:c r="O33" s="121" t="n">
-        <x:v>3</x:v>
-      </x:c>
+        <x:v>所选时长 × 规则时薪</x:v>
+      </x:c>
+      <x:c r="M33" s="102"/>
+      <x:c r="N33" s="103"/>
+      <x:c r="O33" s="104"/>
       <x:c r="P33" s="3" t="str">
-        <x:v>g-premium-alternative</x:v>
+        <x:v>g-extra-floor-total</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
-      <x:c r="A34" s="67" t="str">
-        <x:v>陈雨</x:v>
-      </x:c>
-      <x:c r="B34" s="67" t="str">
+      <x:c r="A34" s="55" t="str">
+        <x:v>周宁</x:v>
+      </x:c>
+      <x:c r="B34" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C34" s="67" t="str">
-        <x:v>员工</x:v>
-      </x:c>
-      <x:c r="D34" s="67" t="str">
-        <x:v>签约员工·夜班补贴</x:v>
-      </x:c>
-      <x:c r="E34" s="67" t="str">
-        <x:v>补贴</x:v>
-      </x:c>
-      <x:c r="F34" s="67" t="str">
-        <x:v>夜班场次</x:v>
-      </x:c>
-      <x:c r="G34" s="77" t="n">
-        <x:f>'月度核算明细'!R9</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H34" s="118" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I34" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J34" s="103" t="n">
+      <x:c r="C34" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D34" s="55" t="str">
+        <x:v>全局补充·早班加成</x:v>
+      </x:c>
+      <x:c r="E34" s="55" t="str">
+        <x:v>加成</x:v>
+      </x:c>
+      <x:c r="F34" s="55" t="str">
+        <x:v>早班直播时长</x:v>
+      </x:c>
+      <x:c r="G34" s="65" t="n">
+        <x:f>'月度核算明细'!P8</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H34" s="101" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I34" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J34" s="86" t="n">
         <x:f>ROUND(G34*H34+I34,2)</x:f>
-        <x:v>45</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K34" s="3"/>
       <x:c r="L34" s="3" t="str">
-        <x:v>场次 × 每场补贴</x:v>
-      </x:c>
-      <x:c r="M34" s="119"/>
-      <x:c r="N34" s="120"/>
-      <x:c r="O34" s="121"/>
-      <x:c r="P34" s="67" t="str">
-        <x:v>e-night-allowance</x:v>
+        <x:v>所选时长 × 规则时薪</x:v>
+      </x:c>
+      <x:c r="M34" s="102"/>
+      <x:c r="N34" s="103"/>
+      <x:c r="O34" s="104"/>
+      <x:c r="P34" s="55" t="str">
+        <x:v>g-extra-early-addition</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="24" customHeight="1">
@@ -4278,92 +4074,84 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C35" s="3" t="str">
-        <x:v>员工</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D35" s="3" t="str">
-        <x:v>签约员工·早班系数</x:v>
+        <x:v>基础·夜班补贴</x:v>
       </x:c>
       <x:c r="E35" s="3" t="str">
-        <x:v>系数保费</x:v>
+        <x:v>补贴</x:v>
       </x:c>
       <x:c r="F35" s="3" t="str">
-        <x:v>早班保费</x:v>
-      </x:c>
-      <x:c r="G35" s="75" t="n">
-        <x:f>'月度核算明细'!Z9</x:f>
-        <x:v>6000</x:v>
-      </x:c>
-      <x:c r="H35" s="118" t="n">
-        <x:f>IF('月度核算明细'!S9&gt;=O35,M35,1)</x:f>
+        <x:v>夜班场次</x:v>
+      </x:c>
+      <x:c r="G35" s="63" t="n">
+        <x:f>'月度核算明细'!R9</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I35" s="75" t="n">
-        <x:f>'月度核算明细'!AA9</x:f>
-        <x:v>18000</x:v>
-      </x:c>
-      <x:c r="J35" s="102" t="n">
+      <x:c r="H35" s="101" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I35" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J35" s="85" t="n">
         <x:f>ROUND(G35*H35+I35,2)</x:f>
-        <x:v>36000</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K35" s="3"/>
       <x:c r="L35" s="3" t="str">
-        <x:v>达阈值用设定系数，否则用1</x:v>
-      </x:c>
-      <x:c r="M35" s="119" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="N35" s="120" t="str">
-        <x:v>早班场次 ≥</x:v>
-      </x:c>
-      <x:c r="O35" s="121" t="n">
-        <x:v>5</x:v>
-      </x:c>
+        <x:v>场次 × 每场补贴</x:v>
+      </x:c>
+      <x:c r="M35" s="102"/>
+      <x:c r="N35" s="103"/>
+      <x:c r="O35" s="104"/>
       <x:c r="P35" s="3" t="str">
-        <x:v>e-premium</x:v>
+        <x:v>g-night-allowance</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="24" customHeight="1">
-      <x:c r="A36" s="67" t="str">
+      <x:c r="A36" s="55" t="str">
         <x:v>陈雨</x:v>
       </x:c>
-      <x:c r="B36" s="67" t="str">
+      <x:c r="B36" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C36" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D36" s="67" t="str">
-        <x:v>基础·总时长保底</x:v>
-      </x:c>
-      <x:c r="E36" s="67" t="str">
-        <x:v>保底</x:v>
-      </x:c>
-      <x:c r="F36" s="67" t="str">
-        <x:v>总直播时长</x:v>
-      </x:c>
-      <x:c r="G36" s="77" t="n">
-        <x:f>'月度核算明细'!N9</x:f>
+      <x:c r="C36" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D36" s="55" t="str">
+        <x:v>基础·早班补贴</x:v>
+      </x:c>
+      <x:c r="E36" s="55" t="str">
+        <x:v>补贴</x:v>
+      </x:c>
+      <x:c r="F36" s="55" t="str">
+        <x:v>早班场次</x:v>
+      </x:c>
+      <x:c r="G36" s="65" t="n">
+        <x:f>'月度核算明细'!S9</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H36" s="101" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I36" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36" s="86" t="n">
+        <x:f>ROUND(G36*H36+I36,2)</x:f>
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="H36" s="118" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I36" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J36" s="103" t="n">
-        <x:f>ROUND(G36*H36+I36,2)</x:f>
-        <x:v>3000</x:v>
       </x:c>
       <x:c r="K36" s="3"/>
       <x:c r="L36" s="3" t="str">
-        <x:v>所选时长 × 规则时薪</x:v>
-      </x:c>
-      <x:c r="M36" s="119"/>
-      <x:c r="N36" s="120"/>
-      <x:c r="O36" s="121"/>
-      <x:c r="P36" s="67" t="str">
-        <x:v>g-floor-total</x:v>
+        <x:v>场次 × 每场补贴</x:v>
+      </x:c>
+      <x:c r="M36" s="102"/>
+      <x:c r="N36" s="103"/>
+      <x:c r="O36" s="104"/>
+      <x:c r="P36" s="55" t="str">
+        <x:v>g-early-allowance</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="24" customHeight="1">
@@ -4374,85 +4162,100 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C37" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D37" s="3" t="str">
-        <x:v>基础·夜班保底</x:v>
+        <x:v>基础·早班系数</x:v>
       </x:c>
       <x:c r="E37" s="3" t="str">
-        <x:v>保底</x:v>
+        <x:v>系数保费</x:v>
       </x:c>
       <x:c r="F37" s="3" t="str">
-        <x:v>夜班直播时长</x:v>
-      </x:c>
-      <x:c r="G37" s="75" t="n">
-        <x:f>'月度核算明细'!O9</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H37" s="118" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="I37" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J37" s="102" t="n">
+        <x:v>早班保费</x:v>
+      </x:c>
+      <x:c r="G37" s="63" t="n">
+        <x:f>'月度核算明细'!Z9</x:f>
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="H37" s="101" t="n">
+        <x:f>IF('月度核算明细'!S9&gt;=O37,M37,1)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I37" s="63" t="n">
+        <x:f>'月度核算明细'!AA9</x:f>
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="J37" s="85" t="n">
         <x:f>ROUND(G37*H37+I37,2)</x:f>
-        <x:v>2000</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="K37" s="3"/>
       <x:c r="L37" s="3" t="str">
-        <x:v>所选时长 × 规则时薪</x:v>
-      </x:c>
-      <x:c r="M37" s="119"/>
-      <x:c r="N37" s="120"/>
-      <x:c r="O37" s="121"/>
+        <x:v>达阈值用设定系数，否则用1</x:v>
+      </x:c>
+      <x:c r="M37" s="102" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N37" s="103" t="str">
+        <x:v>早班场次 ≥</x:v>
+      </x:c>
+      <x:c r="O37" s="104" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="P37" s="3" t="str">
-        <x:v>g-floor-night</x:v>
+        <x:v>g-premium</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="24" customHeight="1">
-      <x:c r="A38" s="67" t="str">
+      <x:c r="A38" s="55" t="str">
         <x:v>陈雨</x:v>
       </x:c>
-      <x:c r="B38" s="67" t="str">
+      <x:c r="B38" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C38" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D38" s="67" t="str">
-        <x:v>基础·ROI加成</x:v>
-      </x:c>
-      <x:c r="E38" s="67" t="str">
-        <x:v>加成</x:v>
-      </x:c>
-      <x:c r="F38" s="67" t="str">
-        <x:v>总直播时长</x:v>
-      </x:c>
-      <x:c r="G38" s="77" t="n">
-        <x:f>'月度核算明细'!N9</x:f>
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H38" s="118" t="n">
-        <x:f>IF(AND('员工月薪汇总'!H19&gt;=0,'员工月薪汇总'!H19&lt;3),20,IF('员工月薪汇总'!H19&gt;=3,45,NA()))</x:f>
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="I38" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J38" s="103" t="n">
+      <x:c r="C38" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D38" s="55" t="str">
+        <x:v>基础·早班系数备选</x:v>
+      </x:c>
+      <x:c r="E38" s="55" t="str">
+        <x:v>系数保费</x:v>
+      </x:c>
+      <x:c r="F38" s="55" t="str">
+        <x:v>早班保费</x:v>
+      </x:c>
+      <x:c r="G38" s="65" t="n">
+        <x:f>'月度核算明细'!Z9</x:f>
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="H38" s="101" t="n">
+        <x:f>IF('月度核算明细'!S9&gt;=O38,M38,1)</x:f>
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="I38" s="65" t="n">
+        <x:f>'月度核算明细'!AA9</x:f>
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="J38" s="86" t="n">
         <x:f>ROUND(G38*H38+I38,2)</x:f>
-        <x:v>2700</x:v>
+        <x:v>27000</x:v>
       </x:c>
       <x:c r="K38" s="3"/>
       <x:c r="L38" s="3" t="str">
-        <x:v>有效ROI：低于3为20；≥3为45</x:v>
-      </x:c>
-      <x:c r="M38" s="119"/>
-      <x:c r="N38" s="120"/>
-      <x:c r="O38" s="121"/>
-      <x:c r="P38" s="67" t="str">
-        <x:v>g-roi-addition</x:v>
+        <x:v>达阈值用设定系数，否则用1</x:v>
+      </x:c>
+      <x:c r="M38" s="102" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="N38" s="103" t="str">
+        <x:v>早班场次 ≥</x:v>
+      </x:c>
+      <x:c r="O38" s="104" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P38" s="55" t="str">
+        <x:v>g-premium-alternative</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="24" customHeight="1">
@@ -4463,85 +4266,92 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C39" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D39" s="3" t="str">
-        <x:v>基础·排名加成</x:v>
+        <x:v>全局补充·夜班补贴</x:v>
       </x:c>
       <x:c r="E39" s="3" t="str">
-        <x:v>加成</x:v>
+        <x:v>补贴</x:v>
       </x:c>
       <x:c r="F39" s="3" t="str">
-        <x:v>总直播时长</x:v>
-      </x:c>
-      <x:c r="G39" s="75" t="n">
-        <x:f>'月度核算明细'!N9</x:f>
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H39" s="118" t="n">
-        <x:f>IF('员工月薪汇总'!I19=1,10,IF('员工月薪汇总'!I19&gt;=2,5,NA()))</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I39" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J39" s="102" t="n">
+        <x:v>夜班场次</x:v>
+      </x:c>
+      <x:c r="G39" s="63" t="n">
+        <x:f>'月度核算明细'!R9</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H39" s="101" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I39" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J39" s="85" t="n">
         <x:f>ROUND(G39*H39+I39,2)</x:f>
-        <x:v>300</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K39" s="3"/>
       <x:c r="L39" s="3" t="str">
-        <x:v>有效排名：第1为10；其余为5</x:v>
-      </x:c>
-      <x:c r="M39" s="119"/>
-      <x:c r="N39" s="120"/>
-      <x:c r="O39" s="121"/>
+        <x:v>场次 × 每场补贴</x:v>
+      </x:c>
+      <x:c r="M39" s="102"/>
+      <x:c r="N39" s="103"/>
+      <x:c r="O39" s="104"/>
       <x:c r="P39" s="3" t="str">
-        <x:v>g-rank-addition</x:v>
+        <x:v>g-extra-night-allowance</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="24" customHeight="1">
-      <x:c r="A40" s="67" t="str">
+      <x:c r="A40" s="55" t="str">
         <x:v>陈雨</x:v>
       </x:c>
-      <x:c r="B40" s="67" t="str">
+      <x:c r="B40" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C40" s="67" t="str">
-        <x:v>直播间</x:v>
-      </x:c>
-      <x:c r="D40" s="67" t="str">
-        <x:v>双房共用·正常时段加成</x:v>
-      </x:c>
-      <x:c r="E40" s="67" t="str">
-        <x:v>加成</x:v>
-      </x:c>
-      <x:c r="F40" s="67" t="str">
-        <x:v>正常直播时长</x:v>
-      </x:c>
-      <x:c r="G40" s="77" t="n">
-        <x:f>'月度核算明细'!Q9</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H40" s="118" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I40" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J40" s="103" t="n">
+      <x:c r="C40" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D40" s="55" t="str">
+        <x:v>全局补充·早班系数</x:v>
+      </x:c>
+      <x:c r="E40" s="55" t="str">
+        <x:v>系数保费</x:v>
+      </x:c>
+      <x:c r="F40" s="55" t="str">
+        <x:v>早班保费</x:v>
+      </x:c>
+      <x:c r="G40" s="65" t="n">
+        <x:f>'月度核算明细'!Z9</x:f>
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="H40" s="101" t="n">
+        <x:f>IF('月度核算明细'!S9&gt;=O40,M40,1)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I40" s="65" t="n">
+        <x:f>'月度核算明细'!AA9</x:f>
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="J40" s="86" t="n">
         <x:f>ROUND(G40*H40+I40,2)</x:f>
-        <x:v>600</x:v>
+        <x:v>36000</x:v>
       </x:c>
       <x:c r="K40" s="3"/>
       <x:c r="L40" s="3" t="str">
-        <x:v>所选时长 × 规则时薪</x:v>
-      </x:c>
-      <x:c r="M40" s="119"/>
-      <x:c r="N40" s="120"/>
-      <x:c r="O40" s="121"/>
-      <x:c r="P40" s="67" t="str">
-        <x:v>r-regular-addition</x:v>
+        <x:v>达阈值用设定系数，否则用1</x:v>
+      </x:c>
+      <x:c r="M40" s="102" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N40" s="103" t="str">
+        <x:v>早班场次 ≥</x:v>
+      </x:c>
+      <x:c r="O40" s="104" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P40" s="55" t="str">
+        <x:v>g-extra-premium</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="24" customHeight="1">
@@ -4552,84 +4362,84 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C41" s="3" t="str">
-        <x:v>员工</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D41" s="3" t="str">
-        <x:v>签约员工·早班保底</x:v>
+        <x:v>基础·总时长保底</x:v>
       </x:c>
       <x:c r="E41" s="3" t="str">
         <x:v>保底</x:v>
       </x:c>
       <x:c r="F41" s="3" t="str">
-        <x:v>早班直播时长</x:v>
-      </x:c>
-      <x:c r="G41" s="75" t="n">
-        <x:f>'月度核算明细'!P9</x:f>
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H41" s="118" t="n">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="I41" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J41" s="102" t="n">
+        <x:v>总直播时长</x:v>
+      </x:c>
+      <x:c r="G41" s="63" t="n">
+        <x:f>'月度核算明细'!N9</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H41" s="101" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I41" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J41" s="85" t="n">
         <x:f>ROUND(G41*H41+I41,2)</x:f>
-        <x:v>4400</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="K41" s="3"/>
       <x:c r="L41" s="3" t="str">
         <x:v>所选时长 × 规则时薪</x:v>
       </x:c>
-      <x:c r="M41" s="119"/>
-      <x:c r="N41" s="120"/>
-      <x:c r="O41" s="121"/>
+      <x:c r="M41" s="102"/>
+      <x:c r="N41" s="103"/>
+      <x:c r="O41" s="104"/>
       <x:c r="P41" s="3" t="str">
-        <x:v>e-floor-early</x:v>
+        <x:v>g-floor-total</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="24" customHeight="1">
-      <x:c r="A42" s="67" t="str">
+      <x:c r="A42" s="55" t="str">
         <x:v>陈雨</x:v>
       </x:c>
-      <x:c r="B42" s="67" t="str">
+      <x:c r="B42" s="55" t="str">
         <x:v>示例一号房</x:v>
       </x:c>
-      <x:c r="C42" s="67" t="str">
-        <x:v>员工</x:v>
-      </x:c>
-      <x:c r="D42" s="67" t="str">
-        <x:v>签约员工·总时长保底</x:v>
-      </x:c>
-      <x:c r="E42" s="67" t="str">
+      <x:c r="C42" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D42" s="55" t="str">
+        <x:v>基础·夜班保底</x:v>
+      </x:c>
+      <x:c r="E42" s="55" t="str">
         <x:v>保底</x:v>
       </x:c>
-      <x:c r="F42" s="67" t="str">
-        <x:v>总直播时长</x:v>
-      </x:c>
-      <x:c r="G42" s="77" t="n">
-        <x:f>'月度核算明细'!N9</x:f>
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H42" s="118" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="I42" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J42" s="103" t="n">
+      <x:c r="F42" s="55" t="str">
+        <x:v>夜班直播时长</x:v>
+      </x:c>
+      <x:c r="G42" s="65" t="n">
+        <x:f>'月度核算明细'!O9</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H42" s="101" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="I42" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J42" s="86" t="n">
         <x:f>ROUND(G42*H42+I42,2)</x:f>
-        <x:v>3300</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="K42" s="3"/>
       <x:c r="L42" s="3" t="str">
         <x:v>所选时长 × 规则时薪</x:v>
       </x:c>
-      <x:c r="M42" s="119"/>
-      <x:c r="N42" s="120"/>
-      <x:c r="O42" s="121"/>
-      <x:c r="P42" s="67" t="str">
-        <x:v>e-floor-total</x:v>
+      <x:c r="M42" s="102"/>
+      <x:c r="N42" s="103"/>
+      <x:c r="O42" s="104"/>
+      <x:c r="P42" s="55" t="str">
+        <x:v>g-floor-night</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="24" customHeight="1">
@@ -4640,276 +4450,262 @@
         <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C43" s="3" t="str">
-        <x:v>员工</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D43" s="3" t="str">
-        <x:v>签约员工·早班加成</x:v>
+        <x:v>基础·ROI加成</x:v>
       </x:c>
       <x:c r="E43" s="3" t="str">
         <x:v>加成</x:v>
       </x:c>
       <x:c r="F43" s="3" t="str">
+        <x:v>总直播时长</x:v>
+      </x:c>
+      <x:c r="G43" s="63" t="n">
+        <x:f>'月度核算明细'!N9</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H43" s="101" t="n">
+        <x:f>IF(AND('员工月薪汇总'!H19&gt;=0,'员工月薪汇总'!H19&lt;3),20,IF('员工月薪汇总'!H19&gt;=3,45,NA()))</x:f>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I43" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J43" s="85" t="n">
+        <x:f>ROUND(G43*H43+I43,2)</x:f>
+        <x:v>2700</x:v>
+      </x:c>
+      <x:c r="K43" s="3"/>
+      <x:c r="L43" s="3" t="str">
+        <x:v>有效ROI：低于3为20；≥3为45</x:v>
+      </x:c>
+      <x:c r="M43" s="102"/>
+      <x:c r="N43" s="103"/>
+      <x:c r="O43" s="104"/>
+      <x:c r="P43" s="3" t="str">
+        <x:v>g-roi-addition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="24" customHeight="1">
+      <x:c r="A44" s="55" t="str">
+        <x:v>陈雨</x:v>
+      </x:c>
+      <x:c r="B44" s="55" t="str">
+        <x:v>示例一号房</x:v>
+      </x:c>
+      <x:c r="C44" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D44" s="55" t="str">
+        <x:v>基础·排名加成</x:v>
+      </x:c>
+      <x:c r="E44" s="55" t="str">
+        <x:v>加成</x:v>
+      </x:c>
+      <x:c r="F44" s="55" t="str">
+        <x:v>总直播时长</x:v>
+      </x:c>
+      <x:c r="G44" s="65" t="n">
+        <x:f>'月度核算明细'!N9</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H44" s="101" t="n">
+        <x:f>IF(AND('员工月薪汇总'!I19&gt;=1,'员工月薪汇总'!I19&lt;=1),10,IF('员工月薪汇总'!I19&gt;=2,5,NA()))</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I44" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J44" s="86" t="n">
+        <x:f>ROUND(G44*H44+I44,2)</x:f>
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="K44" s="3"/>
+      <x:c r="L44" s="3" t="str">
+        <x:v>有效排名：第1为10；其余为5</x:v>
+      </x:c>
+      <x:c r="M44" s="102"/>
+      <x:c r="N44" s="103"/>
+      <x:c r="O44" s="104"/>
+      <x:c r="P44" s="55" t="str">
+        <x:v>g-rank-addition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="24" customHeight="1">
+      <x:c r="A45" s="3" t="str">
+        <x:v>陈雨</x:v>
+      </x:c>
+      <x:c r="B45" s="3" t="str">
+        <x:v>示例一号房</x:v>
+      </x:c>
+      <x:c r="C45" s="3" t="str">
+        <x:v>直播间</x:v>
+      </x:c>
+      <x:c r="D45" s="3" t="str">
+        <x:v>双房共用·正常时段加成</x:v>
+      </x:c>
+      <x:c r="E45" s="3" t="str">
+        <x:v>加成</x:v>
+      </x:c>
+      <x:c r="F45" s="3" t="str">
+        <x:v>正常直播时长</x:v>
+      </x:c>
+      <x:c r="G45" s="63" t="n">
+        <x:f>'月度核算明细'!Q9</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H45" s="101" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I45" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J45" s="85" t="n">
+        <x:f>ROUND(G45*H45+I45,2)</x:f>
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="K45" s="3"/>
+      <x:c r="L45" s="3" t="str">
+        <x:v>所选时长 × 规则时薪</x:v>
+      </x:c>
+      <x:c r="M45" s="102"/>
+      <x:c r="N45" s="103"/>
+      <x:c r="O45" s="104"/>
+      <x:c r="P45" s="3" t="str">
+        <x:v>r-regular-addition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="24" customHeight="1">
+      <x:c r="A46" s="55" t="str">
+        <x:v>陈雨</x:v>
+      </x:c>
+      <x:c r="B46" s="55" t="str">
+        <x:v>示例一号房</x:v>
+      </x:c>
+      <x:c r="C46" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D46" s="55" t="str">
+        <x:v>全局补充·早班保底</x:v>
+      </x:c>
+      <x:c r="E46" s="55" t="str">
+        <x:v>保底</x:v>
+      </x:c>
+      <x:c r="F46" s="55" t="str">
         <x:v>早班直播时长</x:v>
       </x:c>
-      <x:c r="G43" s="75" t="n">
+      <x:c r="G46" s="65" t="n">
         <x:f>'月度核算明细'!P9</x:f>
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H43" s="118" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I43" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J43" s="102" t="n">
-        <x:f>ROUND(G43*H43+I43,2)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="K43" s="3"/>
-      <x:c r="L43" s="3" t="str">
-        <x:v>所选时长 × 规则时薪</x:v>
-      </x:c>
-      <x:c r="M43" s="119"/>
-      <x:c r="N43" s="120"/>
-      <x:c r="O43" s="121"/>
-      <x:c r="P43" s="3" t="str">
-        <x:v>e-early-addition</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="24" customHeight="1">
-      <x:c r="A44" s="67" t="str">
-        <x:v>林晓</x:v>
-      </x:c>
-      <x:c r="B44" s="67" t="str">
-        <x:v>示例二号房</x:v>
-      </x:c>
-      <x:c r="C44" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D44" s="67" t="str">
-        <x:v>基础·夜班补贴</x:v>
-      </x:c>
-      <x:c r="E44" s="67" t="str">
-        <x:v>补贴</x:v>
-      </x:c>
-      <x:c r="F44" s="67" t="str">
-        <x:v>夜班场次</x:v>
-      </x:c>
-      <x:c r="G44" s="77" t="n">
-        <x:f>'月度核算明细'!R10</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H44" s="118" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I44" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J44" s="103" t="n">
-        <x:f>ROUND(G44*H44+I44,2)</x:f>
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="K44" s="3"/>
-      <x:c r="L44" s="3" t="str">
-        <x:v>场次 × 每场补贴</x:v>
-      </x:c>
-      <x:c r="M44" s="119"/>
-      <x:c r="N44" s="120"/>
-      <x:c r="O44" s="121"/>
-      <x:c r="P44" s="67" t="str">
-        <x:v>g-night-allowance</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="24" customHeight="1">
-      <x:c r="A45" s="3" t="str">
-        <x:v>林晓</x:v>
-      </x:c>
-      <x:c r="B45" s="3" t="str">
-        <x:v>示例二号房</x:v>
-      </x:c>
-      <x:c r="C45" s="3" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D45" s="3" t="str">
-        <x:v>基础·早班补贴</x:v>
-      </x:c>
-      <x:c r="E45" s="3" t="str">
-        <x:v>补贴</x:v>
-      </x:c>
-      <x:c r="F45" s="3" t="str">
-        <x:v>早班场次</x:v>
-      </x:c>
-      <x:c r="G45" s="75" t="n">
-        <x:f>'月度核算明细'!S10</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H45" s="118" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I45" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J45" s="102" t="n">
-        <x:f>ROUND(G45*H45+I45,2)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K45" s="3"/>
-      <x:c r="L45" s="3" t="str">
-        <x:v>场次 × 每场补贴</x:v>
-      </x:c>
-      <x:c r="M45" s="119"/>
-      <x:c r="N45" s="120"/>
-      <x:c r="O45" s="121"/>
-      <x:c r="P45" s="3" t="str">
-        <x:v>g-early-allowance</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="24" customHeight="1">
-      <x:c r="A46" s="67" t="str">
-        <x:v>林晓</x:v>
-      </x:c>
-      <x:c r="B46" s="67" t="str">
-        <x:v>示例二号房</x:v>
-      </x:c>
-      <x:c r="C46" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D46" s="67" t="str">
-        <x:v>基础·早班系数</x:v>
-      </x:c>
-      <x:c r="E46" s="67" t="str">
-        <x:v>系数保费</x:v>
-      </x:c>
-      <x:c r="F46" s="67" t="str">
-        <x:v>早班保费</x:v>
-      </x:c>
-      <x:c r="G46" s="77" t="n">
-        <x:f>'月度核算明细'!Z10</x:f>
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="H46" s="118" t="n">
-        <x:f>IF('月度核算明细'!S10&gt;=O46,M46,1)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I46" s="77" t="n">
-        <x:f>'月度核算明细'!AA10</x:f>
-        <x:v>7000</x:v>
-      </x:c>
-      <x:c r="J46" s="103" t="n">
+      <x:c r="H46" s="101" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I46" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J46" s="86" t="n">
         <x:f>ROUND(G46*H46+I46,2)</x:f>
-        <x:v>9000</x:v>
+        <x:v>4400</x:v>
       </x:c>
       <x:c r="K46" s="3"/>
       <x:c r="L46" s="3" t="str">
-        <x:v>达阈值用设定系数，否则用1</x:v>
-      </x:c>
-      <x:c r="M46" s="119" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N46" s="120" t="str">
-        <x:v>早班场次 ≥</x:v>
-      </x:c>
-      <x:c r="O46" s="121" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="P46" s="67" t="str">
-        <x:v>g-premium</x:v>
+        <x:v>所选时长 × 规则时薪</x:v>
+      </x:c>
+      <x:c r="M46" s="102"/>
+      <x:c r="N46" s="103"/>
+      <x:c r="O46" s="104"/>
+      <x:c r="P46" s="55" t="str">
+        <x:v>g-extra-floor-early</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="24" customHeight="1">
       <x:c r="A47" s="3" t="str">
-        <x:v>林晓</x:v>
+        <x:v>陈雨</x:v>
       </x:c>
       <x:c r="B47" s="3" t="str">
-        <x:v>示例二号房</x:v>
+        <x:v>示例一号房</x:v>
       </x:c>
       <x:c r="C47" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D47" s="3" t="str">
-        <x:v>基础·早班系数备选</x:v>
+        <x:v>全局补充·总时长保底</x:v>
       </x:c>
       <x:c r="E47" s="3" t="str">
-        <x:v>系数保费</x:v>
+        <x:v>保底</x:v>
       </x:c>
       <x:c r="F47" s="3" t="str">
-        <x:v>早班保费</x:v>
-      </x:c>
-      <x:c r="G47" s="75" t="n">
-        <x:f>'月度核算明细'!Z10</x:f>
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="H47" s="118" t="n">
-        <x:f>IF('月度核算明细'!S10&gt;=O47,M47,1)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I47" s="75" t="n">
-        <x:f>'月度核算明细'!AA10</x:f>
-        <x:v>7000</x:v>
-      </x:c>
-      <x:c r="J47" s="102" t="n">
+        <x:v>总直播时长</x:v>
+      </x:c>
+      <x:c r="G47" s="63" t="n">
+        <x:f>'月度核算明细'!N9</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H47" s="101" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I47" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J47" s="85" t="n">
         <x:f>ROUND(G47*H47+I47,2)</x:f>
-        <x:v>9000</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="K47" s="3"/>
       <x:c r="L47" s="3" t="str">
-        <x:v>达阈值用设定系数，否则用1</x:v>
-      </x:c>
-      <x:c r="M47" s="119" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="N47" s="120" t="str">
-        <x:v>早班场次 ≥</x:v>
-      </x:c>
-      <x:c r="O47" s="121" t="n">
-        <x:v>3</x:v>
-      </x:c>
+        <x:v>所选时长 × 规则时薪</x:v>
+      </x:c>
+      <x:c r="M47" s="102"/>
+      <x:c r="N47" s="103"/>
+      <x:c r="O47" s="104"/>
       <x:c r="P47" s="3" t="str">
-        <x:v>g-premium-alternative</x:v>
+        <x:v>g-extra-floor-total</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="24" customHeight="1">
-      <x:c r="A48" s="67" t="str">
-        <x:v>林晓</x:v>
-      </x:c>
-      <x:c r="B48" s="67" t="str">
-        <x:v>示例二号房</x:v>
-      </x:c>
-      <x:c r="C48" s="67" t="str">
-        <x:v>员工</x:v>
-      </x:c>
-      <x:c r="D48" s="67" t="str">
-        <x:v>签约员工·夜班补贴</x:v>
-      </x:c>
-      <x:c r="E48" s="67" t="str">
-        <x:v>补贴</x:v>
-      </x:c>
-      <x:c r="F48" s="67" t="str">
-        <x:v>夜班场次</x:v>
-      </x:c>
-      <x:c r="G48" s="77" t="n">
-        <x:f>'月度核算明细'!R10</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H48" s="118" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I48" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J48" s="103" t="n">
+      <x:c r="A48" s="55" t="str">
+        <x:v>陈雨</x:v>
+      </x:c>
+      <x:c r="B48" s="55" t="str">
+        <x:v>示例一号房</x:v>
+      </x:c>
+      <x:c r="C48" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D48" s="55" t="str">
+        <x:v>全局补充·早班加成</x:v>
+      </x:c>
+      <x:c r="E48" s="55" t="str">
+        <x:v>加成</x:v>
+      </x:c>
+      <x:c r="F48" s="55" t="str">
+        <x:v>早班直播时长</x:v>
+      </x:c>
+      <x:c r="G48" s="65" t="n">
+        <x:f>'月度核算明细'!P9</x:f>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H48" s="101" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I48" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J48" s="86" t="n">
         <x:f>ROUND(G48*H48+I48,2)</x:f>
-        <x:v>30</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="K48" s="3"/>
       <x:c r="L48" s="3" t="str">
-        <x:v>场次 × 每场补贴</x:v>
-      </x:c>
-      <x:c r="M48" s="119"/>
-      <x:c r="N48" s="120"/>
-      <x:c r="O48" s="121"/>
-      <x:c r="P48" s="67" t="str">
-        <x:v>e-night-allowance</x:v>
+        <x:v>所选时长 × 规则时薪</x:v>
+      </x:c>
+      <x:c r="M48" s="102"/>
+      <x:c r="N48" s="103"/>
+      <x:c r="O48" s="104"/>
+      <x:c r="P48" s="55" t="str">
+        <x:v>g-extra-early-addition</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="24" customHeight="1">
@@ -4920,92 +4716,84 @@
         <x:v>示例二号房</x:v>
       </x:c>
       <x:c r="C49" s="3" t="str">
-        <x:v>员工</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D49" s="3" t="str">
-        <x:v>签约员工·早班系数</x:v>
+        <x:v>基础·夜班补贴</x:v>
       </x:c>
       <x:c r="E49" s="3" t="str">
-        <x:v>系数保费</x:v>
+        <x:v>补贴</x:v>
       </x:c>
       <x:c r="F49" s="3" t="str">
-        <x:v>早班保费</x:v>
-      </x:c>
-      <x:c r="G49" s="75" t="n">
-        <x:f>'月度核算明细'!Z10</x:f>
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="H49" s="118" t="n">
-        <x:f>IF('月度核算明细'!S10&gt;=O49,M49,1)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I49" s="75" t="n">
-        <x:f>'月度核算明细'!AA10</x:f>
-        <x:v>7000</x:v>
-      </x:c>
-      <x:c r="J49" s="102" t="n">
+        <x:v>夜班场次</x:v>
+      </x:c>
+      <x:c r="G49" s="63" t="n">
+        <x:f>'月度核算明细'!R10</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H49" s="101" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I49" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J49" s="85" t="n">
         <x:f>ROUND(G49*H49+I49,2)</x:f>
-        <x:v>9000</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K49" s="3"/>
       <x:c r="L49" s="3" t="str">
-        <x:v>达阈值用设定系数，否则用1</x:v>
-      </x:c>
-      <x:c r="M49" s="119" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="N49" s="120" t="str">
-        <x:v>早班场次 ≥</x:v>
-      </x:c>
-      <x:c r="O49" s="121" t="n">
-        <x:v>5</x:v>
-      </x:c>
+        <x:v>场次 × 每场补贴</x:v>
+      </x:c>
+      <x:c r="M49" s="102"/>
+      <x:c r="N49" s="103"/>
+      <x:c r="O49" s="104"/>
       <x:c r="P49" s="3" t="str">
-        <x:v>e-premium</x:v>
+        <x:v>g-night-allowance</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="24" customHeight="1">
-      <x:c r="A50" s="67" t="str">
+      <x:c r="A50" s="55" t="str">
         <x:v>林晓</x:v>
       </x:c>
-      <x:c r="B50" s="67" t="str">
+      <x:c r="B50" s="55" t="str">
         <x:v>示例二号房</x:v>
       </x:c>
-      <x:c r="C50" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D50" s="67" t="str">
-        <x:v>基础·总时长保底</x:v>
-      </x:c>
-      <x:c r="E50" s="67" t="str">
-        <x:v>保底</x:v>
-      </x:c>
-      <x:c r="F50" s="67" t="str">
-        <x:v>总直播时长</x:v>
-      </x:c>
-      <x:c r="G50" s="77" t="n">
-        <x:f>'月度核算明细'!N10</x:f>
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H50" s="118" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I50" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J50" s="103" t="n">
+      <x:c r="C50" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D50" s="55" t="str">
+        <x:v>基础·早班补贴</x:v>
+      </x:c>
+      <x:c r="E50" s="55" t="str">
+        <x:v>补贴</x:v>
+      </x:c>
+      <x:c r="F50" s="55" t="str">
+        <x:v>早班场次</x:v>
+      </x:c>
+      <x:c r="G50" s="65" t="n">
+        <x:f>'月度核算明细'!S10</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H50" s="101" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I50" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J50" s="86" t="n">
         <x:f>ROUND(G50*H50+I50,2)</x:f>
-        <x:v>2000</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K50" s="3"/>
       <x:c r="L50" s="3" t="str">
-        <x:v>所选时长 × 规则时薪</x:v>
-      </x:c>
-      <x:c r="M50" s="119"/>
-      <x:c r="N50" s="120"/>
-      <x:c r="O50" s="121"/>
-      <x:c r="P50" s="67" t="str">
-        <x:v>g-floor-total</x:v>
+        <x:v>场次 × 每场补贴</x:v>
+      </x:c>
+      <x:c r="M50" s="102"/>
+      <x:c r="N50" s="103"/>
+      <x:c r="O50" s="104"/>
+      <x:c r="P50" s="55" t="str">
+        <x:v>g-early-allowance</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="24" customHeight="1">
@@ -5016,85 +4804,100 @@
         <x:v>示例二号房</x:v>
       </x:c>
       <x:c r="C51" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D51" s="3" t="str">
-        <x:v>基础·夜班保底</x:v>
+        <x:v>基础·早班系数</x:v>
       </x:c>
       <x:c r="E51" s="3" t="str">
-        <x:v>保底</x:v>
+        <x:v>系数保费</x:v>
       </x:c>
       <x:c r="F51" s="3" t="str">
-        <x:v>夜班直播时长</x:v>
-      </x:c>
-      <x:c r="G51" s="75" t="n">
-        <x:f>'月度核算明细'!O10</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H51" s="118" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="I51" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J51" s="102" t="n">
+        <x:v>早班保费</x:v>
+      </x:c>
+      <x:c r="G51" s="63" t="n">
+        <x:f>'月度核算明细'!Z10</x:f>
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="H51" s="101" t="n">
+        <x:f>IF('月度核算明细'!S10&gt;=O51,M51,1)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I51" s="63" t="n">
+        <x:f>'月度核算明细'!AA10</x:f>
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="J51" s="85" t="n">
         <x:f>ROUND(G51*H51+I51,2)</x:f>
-        <x:v>1000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="K51" s="3"/>
       <x:c r="L51" s="3" t="str">
-        <x:v>所选时长 × 规则时薪</x:v>
-      </x:c>
-      <x:c r="M51" s="119"/>
-      <x:c r="N51" s="120"/>
-      <x:c r="O51" s="121"/>
+        <x:v>达阈值用设定系数，否则用1</x:v>
+      </x:c>
+      <x:c r="M51" s="102" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N51" s="103" t="str">
+        <x:v>早班场次 ≥</x:v>
+      </x:c>
+      <x:c r="O51" s="104" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="P51" s="3" t="str">
-        <x:v>g-floor-night</x:v>
+        <x:v>g-premium</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="24" customHeight="1">
-      <x:c r="A52" s="67" t="str">
+      <x:c r="A52" s="55" t="str">
         <x:v>林晓</x:v>
       </x:c>
-      <x:c r="B52" s="67" t="str">
+      <x:c r="B52" s="55" t="str">
         <x:v>示例二号房</x:v>
       </x:c>
-      <x:c r="C52" s="67" t="str">
-        <x:v>基础</x:v>
-      </x:c>
-      <x:c r="D52" s="67" t="str">
-        <x:v>基础·ROI加成</x:v>
-      </x:c>
-      <x:c r="E52" s="67" t="str">
-        <x:v>加成</x:v>
-      </x:c>
-      <x:c r="F52" s="67" t="str">
-        <x:v>总直播时长</x:v>
-      </x:c>
-      <x:c r="G52" s="77" t="n">
-        <x:f>'月度核算明细'!N10</x:f>
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H52" s="118" t="n">
-        <x:f>IF(AND('员工月薪汇总'!H20&gt;=0,'员工月薪汇总'!H20&lt;3),20,IF('员工月薪汇总'!H20&gt;=3,45,NA()))</x:f>
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I52" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J52" s="103" t="n">
+      <x:c r="C52" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D52" s="55" t="str">
+        <x:v>基础·早班系数备选</x:v>
+      </x:c>
+      <x:c r="E52" s="55" t="str">
+        <x:v>系数保费</x:v>
+      </x:c>
+      <x:c r="F52" s="55" t="str">
+        <x:v>早班保费</x:v>
+      </x:c>
+      <x:c r="G52" s="65" t="n">
+        <x:f>'月度核算明细'!Z10</x:f>
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="H52" s="101" t="n">
+        <x:f>IF('月度核算明细'!S10&gt;=O52,M52,1)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I52" s="65" t="n">
+        <x:f>'月度核算明细'!AA10</x:f>
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="J52" s="86" t="n">
         <x:f>ROUND(G52*H52+I52,2)</x:f>
-        <x:v>800</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="K52" s="3"/>
       <x:c r="L52" s="3" t="str">
-        <x:v>有效ROI：低于3为20；≥3为45</x:v>
-      </x:c>
-      <x:c r="M52" s="119"/>
-      <x:c r="N52" s="120"/>
-      <x:c r="O52" s="121"/>
-      <x:c r="P52" s="67" t="str">
-        <x:v>g-roi-addition</x:v>
+        <x:v>达阈值用设定系数，否则用1</x:v>
+      </x:c>
+      <x:c r="M52" s="102" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="N52" s="103" t="str">
+        <x:v>早班场次 ≥</x:v>
+      </x:c>
+      <x:c r="O52" s="104" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P52" s="55" t="str">
+        <x:v>g-premium-alternative</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="24" customHeight="1">
@@ -5105,85 +4908,92 @@
         <x:v>示例二号房</x:v>
       </x:c>
       <x:c r="C53" s="3" t="str">
-        <x:v>基础</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D53" s="3" t="str">
-        <x:v>基础·排名加成</x:v>
+        <x:v>全局补充·夜班补贴</x:v>
       </x:c>
       <x:c r="E53" s="3" t="str">
-        <x:v>加成</x:v>
+        <x:v>补贴</x:v>
       </x:c>
       <x:c r="F53" s="3" t="str">
-        <x:v>总直播时长</x:v>
-      </x:c>
-      <x:c r="G53" s="75" t="n">
-        <x:f>'月度核算明细'!N10</x:f>
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H53" s="118" t="n">
-        <x:f>IF('员工月薪汇总'!I20=1,10,IF('员工月薪汇总'!I20&gt;=2,5,NA()))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I53" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J53" s="102" t="n">
+        <x:v>夜班场次</x:v>
+      </x:c>
+      <x:c r="G53" s="63" t="n">
+        <x:f>'月度核算明细'!R10</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H53" s="101" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I53" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J53" s="85" t="n">
         <x:f>ROUND(G53*H53+I53,2)</x:f>
-        <x:v>400</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K53" s="3"/>
       <x:c r="L53" s="3" t="str">
-        <x:v>有效排名：第1为10；其余为5</x:v>
-      </x:c>
-      <x:c r="M53" s="119"/>
-      <x:c r="N53" s="120"/>
-      <x:c r="O53" s="121"/>
+        <x:v>场次 × 每场补贴</x:v>
+      </x:c>
+      <x:c r="M53" s="102"/>
+      <x:c r="N53" s="103"/>
+      <x:c r="O53" s="104"/>
       <x:c r="P53" s="3" t="str">
-        <x:v>g-rank-addition</x:v>
+        <x:v>g-extra-night-allowance</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="24" customHeight="1">
-      <x:c r="A54" s="67" t="str">
+      <x:c r="A54" s="55" t="str">
         <x:v>林晓</x:v>
       </x:c>
-      <x:c r="B54" s="67" t="str">
+      <x:c r="B54" s="55" t="str">
         <x:v>示例二号房</x:v>
       </x:c>
-      <x:c r="C54" s="67" t="str">
-        <x:v>直播间</x:v>
-      </x:c>
-      <x:c r="D54" s="67" t="str">
-        <x:v>双房共用·正常时段加成</x:v>
-      </x:c>
-      <x:c r="E54" s="67" t="str">
-        <x:v>加成</x:v>
-      </x:c>
-      <x:c r="F54" s="67" t="str">
-        <x:v>正常直播时长</x:v>
-      </x:c>
-      <x:c r="G54" s="77" t="n">
-        <x:f>'月度核算明细'!Q10</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H54" s="118" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I54" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J54" s="103" t="n">
+      <x:c r="C54" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D54" s="55" t="str">
+        <x:v>全局补充·早班系数</x:v>
+      </x:c>
+      <x:c r="E54" s="55" t="str">
+        <x:v>系数保费</x:v>
+      </x:c>
+      <x:c r="F54" s="55" t="str">
+        <x:v>早班保费</x:v>
+      </x:c>
+      <x:c r="G54" s="65" t="n">
+        <x:f>'月度核算明细'!Z10</x:f>
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="H54" s="101" t="n">
+        <x:f>IF('月度核算明细'!S10&gt;=O54,M54,1)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I54" s="65" t="n">
+        <x:f>'月度核算明细'!AA10</x:f>
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="J54" s="86" t="n">
         <x:f>ROUND(G54*H54+I54,2)</x:f>
-        <x:v>600</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="K54" s="3"/>
       <x:c r="L54" s="3" t="str">
-        <x:v>所选时长 × 规则时薪</x:v>
-      </x:c>
-      <x:c r="M54" s="119"/>
-      <x:c r="N54" s="120"/>
-      <x:c r="O54" s="121"/>
-      <x:c r="P54" s="67" t="str">
-        <x:v>r-regular-addition</x:v>
+        <x:v>达阈值用设定系数，否则用1</x:v>
+      </x:c>
+      <x:c r="M54" s="102" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N54" s="103" t="str">
+        <x:v>早班场次 ≥</x:v>
+      </x:c>
+      <x:c r="O54" s="104" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P54" s="55" t="str">
+        <x:v>g-extra-premium</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="24" customHeight="1">
@@ -5194,84 +5004,84 @@
         <x:v>示例二号房</x:v>
       </x:c>
       <x:c r="C55" s="3" t="str">
-        <x:v>员工</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D55" s="3" t="str">
-        <x:v>签约员工·早班保底</x:v>
+        <x:v>基础·总时长保底</x:v>
       </x:c>
       <x:c r="E55" s="3" t="str">
         <x:v>保底</x:v>
       </x:c>
       <x:c r="F55" s="3" t="str">
-        <x:v>早班直播时长</x:v>
-      </x:c>
-      <x:c r="G55" s="75" t="n">
-        <x:f>'月度核算明细'!P10</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H55" s="118" t="n">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="I55" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J55" s="102" t="n">
+        <x:v>总直播时长</x:v>
+      </x:c>
+      <x:c r="G55" s="63" t="n">
+        <x:f>'月度核算明细'!N10</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H55" s="101" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I55" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J55" s="85" t="n">
         <x:f>ROUND(G55*H55+I55,2)</x:f>
-        <x:v>1100</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="K55" s="3"/>
       <x:c r="L55" s="3" t="str">
         <x:v>所选时长 × 规则时薪</x:v>
       </x:c>
-      <x:c r="M55" s="119"/>
-      <x:c r="N55" s="120"/>
-      <x:c r="O55" s="121"/>
+      <x:c r="M55" s="102"/>
+      <x:c r="N55" s="103"/>
+      <x:c r="O55" s="104"/>
       <x:c r="P55" s="3" t="str">
-        <x:v>e-floor-early</x:v>
+        <x:v>g-floor-total</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="24" customHeight="1">
-      <x:c r="A56" s="67" t="str">
+      <x:c r="A56" s="55" t="str">
         <x:v>林晓</x:v>
       </x:c>
-      <x:c r="B56" s="67" t="str">
+      <x:c r="B56" s="55" t="str">
         <x:v>示例二号房</x:v>
       </x:c>
-      <x:c r="C56" s="67" t="str">
-        <x:v>员工</x:v>
-      </x:c>
-      <x:c r="D56" s="67" t="str">
-        <x:v>签约员工·总时长保底</x:v>
-      </x:c>
-      <x:c r="E56" s="67" t="str">
+      <x:c r="C56" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D56" s="55" t="str">
+        <x:v>基础·夜班保底</x:v>
+      </x:c>
+      <x:c r="E56" s="55" t="str">
         <x:v>保底</x:v>
       </x:c>
-      <x:c r="F56" s="67" t="str">
-        <x:v>总直播时长</x:v>
-      </x:c>
-      <x:c r="G56" s="77" t="n">
-        <x:f>'月度核算明细'!N10</x:f>
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H56" s="118" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="I56" s="77" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J56" s="103" t="n">
+      <x:c r="F56" s="55" t="str">
+        <x:v>夜班直播时长</x:v>
+      </x:c>
+      <x:c r="G56" s="65" t="n">
+        <x:f>'月度核算明细'!O10</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H56" s="101" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="I56" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J56" s="86" t="n">
         <x:f>ROUND(G56*H56+I56,2)</x:f>
-        <x:v>2200</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="K56" s="3"/>
       <x:c r="L56" s="3" t="str">
         <x:v>所选时长 × 规则时薪</x:v>
       </x:c>
-      <x:c r="M56" s="119"/>
-      <x:c r="N56" s="120"/>
-      <x:c r="O56" s="121"/>
-      <x:c r="P56" s="67" t="str">
-        <x:v>e-floor-total</x:v>
+      <x:c r="M56" s="102"/>
+      <x:c r="N56" s="103"/>
+      <x:c r="O56" s="104"/>
+      <x:c r="P56" s="55" t="str">
+        <x:v>g-floor-night</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="24" customHeight="1">
@@ -5282,95 +5092,317 @@
         <x:v>示例二号房</x:v>
       </x:c>
       <x:c r="C57" s="3" t="str">
-        <x:v>员工</x:v>
+        <x:v>全局</x:v>
       </x:c>
       <x:c r="D57" s="3" t="str">
-        <x:v>签约员工·早班加成</x:v>
+        <x:v>基础·ROI加成</x:v>
       </x:c>
       <x:c r="E57" s="3" t="str">
         <x:v>加成</x:v>
       </x:c>
       <x:c r="F57" s="3" t="str">
+        <x:v>总直播时长</x:v>
+      </x:c>
+      <x:c r="G57" s="63" t="n">
+        <x:f>'月度核算明细'!N10</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H57" s="101" t="n">
+        <x:f>IF(AND('员工月薪汇总'!H20&gt;=0,'员工月薪汇总'!H20&lt;3),20,IF('员工月薪汇总'!H20&gt;=3,45,NA()))</x:f>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I57" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J57" s="85" t="n">
+        <x:f>ROUND(G57*H57+I57,2)</x:f>
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="K57" s="3"/>
+      <x:c r="L57" s="3" t="str">
+        <x:v>有效ROI：低于3为20；≥3为45</x:v>
+      </x:c>
+      <x:c r="M57" s="102"/>
+      <x:c r="N57" s="103"/>
+      <x:c r="O57" s="104"/>
+      <x:c r="P57" s="3" t="str">
+        <x:v>g-roi-addition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="24" customHeight="1">
+      <x:c r="A58" s="55" t="str">
+        <x:v>林晓</x:v>
+      </x:c>
+      <x:c r="B58" s="55" t="str">
+        <x:v>示例二号房</x:v>
+      </x:c>
+      <x:c r="C58" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D58" s="55" t="str">
+        <x:v>基础·排名加成</x:v>
+      </x:c>
+      <x:c r="E58" s="55" t="str">
+        <x:v>加成</x:v>
+      </x:c>
+      <x:c r="F58" s="55" t="str">
+        <x:v>总直播时长</x:v>
+      </x:c>
+      <x:c r="G58" s="65" t="n">
+        <x:f>'月度核算明细'!N10</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H58" s="101" t="n">
+        <x:f>IF(AND('员工月薪汇总'!I20&gt;=1,'员工月薪汇总'!I20&lt;=1),10,IF('员工月薪汇总'!I20&gt;=2,5,NA()))</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I58" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J58" s="86" t="n">
+        <x:f>ROUND(G58*H58+I58,2)</x:f>
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="K58" s="3"/>
+      <x:c r="L58" s="3" t="str">
+        <x:v>有效排名：第1为10；其余为5</x:v>
+      </x:c>
+      <x:c r="M58" s="102"/>
+      <x:c r="N58" s="103"/>
+      <x:c r="O58" s="104"/>
+      <x:c r="P58" s="55" t="str">
+        <x:v>g-rank-addition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="24" customHeight="1">
+      <x:c r="A59" s="3" t="str">
+        <x:v>林晓</x:v>
+      </x:c>
+      <x:c r="B59" s="3" t="str">
+        <x:v>示例二号房</x:v>
+      </x:c>
+      <x:c r="C59" s="3" t="str">
+        <x:v>直播间</x:v>
+      </x:c>
+      <x:c r="D59" s="3" t="str">
+        <x:v>双房共用·正常时段加成</x:v>
+      </x:c>
+      <x:c r="E59" s="3" t="str">
+        <x:v>加成</x:v>
+      </x:c>
+      <x:c r="F59" s="3" t="str">
+        <x:v>正常直播时长</x:v>
+      </x:c>
+      <x:c r="G59" s="63" t="n">
+        <x:f>'月度核算明细'!Q10</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H59" s="101" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I59" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J59" s="85" t="n">
+        <x:f>ROUND(G59*H59+I59,2)</x:f>
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="K59" s="3"/>
+      <x:c r="L59" s="3" t="str">
+        <x:v>所选时长 × 规则时薪</x:v>
+      </x:c>
+      <x:c r="M59" s="102"/>
+      <x:c r="N59" s="103"/>
+      <x:c r="O59" s="104"/>
+      <x:c r="P59" s="3" t="str">
+        <x:v>r-regular-addition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="24" customHeight="1">
+      <x:c r="A60" s="55" t="str">
+        <x:v>林晓</x:v>
+      </x:c>
+      <x:c r="B60" s="55" t="str">
+        <x:v>示例二号房</x:v>
+      </x:c>
+      <x:c r="C60" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D60" s="55" t="str">
+        <x:v>全局补充·早班保底</x:v>
+      </x:c>
+      <x:c r="E60" s="55" t="str">
+        <x:v>保底</x:v>
+      </x:c>
+      <x:c r="F60" s="55" t="str">
         <x:v>早班直播时长</x:v>
       </x:c>
-      <x:c r="G57" s="75" t="n">
+      <x:c r="G60" s="65" t="n">
         <x:f>'月度核算明细'!P10</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H57" s="118" t="n">
+      <x:c r="H60" s="101" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I60" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J60" s="86" t="n">
+        <x:f>ROUND(G60*H60+I60,2)</x:f>
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="K60" s="3"/>
+      <x:c r="L60" s="3" t="str">
+        <x:v>所选时长 × 规则时薪</x:v>
+      </x:c>
+      <x:c r="M60" s="102"/>
+      <x:c r="N60" s="103"/>
+      <x:c r="O60" s="104"/>
+      <x:c r="P60" s="55" t="str">
+        <x:v>g-extra-floor-early</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="24" customHeight="1">
+      <x:c r="A61" s="3" t="str">
+        <x:v>林晓</x:v>
+      </x:c>
+      <x:c r="B61" s="3" t="str">
+        <x:v>示例二号房</x:v>
+      </x:c>
+      <x:c r="C61" s="3" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D61" s="3" t="str">
+        <x:v>全局补充·总时长保底</x:v>
+      </x:c>
+      <x:c r="E61" s="3" t="str">
+        <x:v>保底</x:v>
+      </x:c>
+      <x:c r="F61" s="3" t="str">
+        <x:v>总直播时长</x:v>
+      </x:c>
+      <x:c r="G61" s="63" t="n">
+        <x:f>'月度核算明细'!N10</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H61" s="101" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I61" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J61" s="85" t="n">
+        <x:f>ROUND(G61*H61+I61,2)</x:f>
+        <x:v>2200</x:v>
+      </x:c>
+      <x:c r="K61" s="3"/>
+      <x:c r="L61" s="3" t="str">
+        <x:v>所选时长 × 规则时薪</x:v>
+      </x:c>
+      <x:c r="M61" s="102"/>
+      <x:c r="N61" s="103"/>
+      <x:c r="O61" s="104"/>
+      <x:c r="P61" s="3" t="str">
+        <x:v>g-extra-floor-total</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="24" customHeight="1">
+      <x:c r="A62" s="55" t="str">
+        <x:v>林晓</x:v>
+      </x:c>
+      <x:c r="B62" s="55" t="str">
+        <x:v>示例二号房</x:v>
+      </x:c>
+      <x:c r="C62" s="55" t="str">
+        <x:v>全局</x:v>
+      </x:c>
+      <x:c r="D62" s="55" t="str">
+        <x:v>全局补充·早班加成</x:v>
+      </x:c>
+      <x:c r="E62" s="55" t="str">
+        <x:v>加成</x:v>
+      </x:c>
+      <x:c r="F62" s="55" t="str">
+        <x:v>早班直播时长</x:v>
+      </x:c>
+      <x:c r="G62" s="65" t="n">
+        <x:f>'月度核算明细'!P10</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H62" s="101" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I57" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J57" s="102" t="n">
-        <x:f>ROUND(G57*H57+I57,2)</x:f>
+      <x:c r="I62" s="65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J62" s="86" t="n">
+        <x:f>ROUND(G62*H62+I62,2)</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K57" s="3"/>
-      <x:c r="L57" s="3" t="str">
+      <x:c r="K62" s="3"/>
+      <x:c r="L62" s="3" t="str">
         <x:v>所选时长 × 规则时薪</x:v>
       </x:c>
-      <x:c r="M57" s="119"/>
-      <x:c r="N57" s="120"/>
-      <x:c r="O57" s="121"/>
-      <x:c r="P57" s="3" t="str">
-        <x:v>e-early-addition</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" ht="24" customHeight="1">
-      <x:c r="A58" s="3"/>
-      <x:c r="B58" s="3"/>
-      <x:c r="C58" s="3"/>
-      <x:c r="D58" s="3"/>
-      <x:c r="E58" s="3"/>
-      <x:c r="F58" s="3"/>
-      <x:c r="G58" s="3"/>
-      <x:c r="H58" s="3"/>
-      <x:c r="I58" s="3"/>
-      <x:c r="J58" s="3"/>
-      <x:c r="K58" s="3"/>
-      <x:c r="L58" s="3"/>
-      <x:c r="M58" s="3"/>
-      <x:c r="N58" s="3"/>
-      <x:c r="O58" s="3"/>
-      <x:c r="P58" s="3"/>
-    </x:row>
-    <x:row r="59" ht="24" customHeight="1">
-      <x:c r="A59" s="3"/>
-      <x:c r="B59" s="3"/>
-      <x:c r="C59" s="3"/>
-      <x:c r="D59" s="3"/>
-      <x:c r="E59" s="3"/>
-      <x:c r="F59" s="3"/>
-      <x:c r="G59" s="3"/>
-      <x:c r="H59" s="3"/>
-      <x:c r="I59" s="3"/>
-      <x:c r="J59" s="3"/>
-      <x:c r="K59" s="3"/>
-      <x:c r="L59" s="3"/>
-      <x:c r="M59" s="3"/>
-      <x:c r="N59" s="3"/>
-      <x:c r="O59" s="3"/>
-      <x:c r="P59" s="3"/>
-    </x:row>
-    <x:row r="60" ht="24" customHeight="1">
-      <x:c r="A60" s="3"/>
-      <x:c r="B60" s="3"/>
-      <x:c r="C60" s="3"/>
-      <x:c r="D60" s="3"/>
-      <x:c r="E60" s="3"/>
-      <x:c r="F60" s="3"/>
-      <x:c r="G60" s="3"/>
-      <x:c r="H60" s="3"/>
-      <x:c r="I60" s="3"/>
-      <x:c r="J60" s="3"/>
-      <x:c r="K60" s="3"/>
-      <x:c r="L60" s="3"/>
-      <x:c r="M60" s="3"/>
-      <x:c r="N60" s="3"/>
-      <x:c r="O60" s="3"/>
-      <x:c r="P60" s="3"/>
+      <x:c r="M62" s="102"/>
+      <x:c r="N62" s="103"/>
+      <x:c r="O62" s="104"/>
+      <x:c r="P62" s="55" t="str">
+        <x:v>g-extra-early-addition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="24" customHeight="1">
+      <x:c r="A63" s="3"/>
+      <x:c r="B63" s="3"/>
+      <x:c r="C63" s="3"/>
+      <x:c r="D63" s="3"/>
+      <x:c r="E63" s="3"/>
+      <x:c r="F63" s="3"/>
+      <x:c r="G63" s="3"/>
+      <x:c r="H63" s="3"/>
+      <x:c r="I63" s="3"/>
+      <x:c r="J63" s="3"/>
+      <x:c r="K63" s="3"/>
+      <x:c r="L63" s="3"/>
+      <x:c r="M63" s="3"/>
+      <x:c r="N63" s="3"/>
+      <x:c r="O63" s="3"/>
+      <x:c r="P63" s="3"/>
+    </x:row>
+    <x:row r="64" ht="24" customHeight="1">
+      <x:c r="A64" s="3"/>
+      <x:c r="B64" s="3"/>
+      <x:c r="C64" s="3"/>
+      <x:c r="D64" s="3"/>
+      <x:c r="E64" s="3"/>
+      <x:c r="F64" s="3"/>
+      <x:c r="G64" s="3"/>
+      <x:c r="H64" s="3"/>
+      <x:c r="I64" s="3"/>
+      <x:c r="J64" s="3"/>
+      <x:c r="K64" s="3"/>
+      <x:c r="L64" s="3"/>
+      <x:c r="M64" s="3"/>
+      <x:c r="N64" s="3"/>
+      <x:c r="O64" s="3"/>
+      <x:c r="P64" s="3"/>
+    </x:row>
+    <x:row r="65" ht="24" customHeight="1">
+      <x:c r="A65" s="3"/>
+      <x:c r="B65" s="3"/>
+      <x:c r="C65" s="3"/>
+      <x:c r="D65" s="3"/>
+      <x:c r="E65" s="3"/>
+      <x:c r="F65" s="3"/>
+      <x:c r="G65" s="3"/>
+      <x:c r="H65" s="3"/>
+      <x:c r="I65" s="3"/>
+      <x:c r="J65" s="3"/>
+      <x:c r="K65" s="3"/>
+      <x:c r="L65" s="3"/>
+      <x:c r="M65" s="3"/>
+      <x:c r="N65" s="3"/>
+      <x:c r="O65" s="3"/>
+      <x:c r="P65" s="3"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/outputs/layered-payroll-20261016/主播月度薪酬核算示例.xlsx
+++ b/outputs/layered-payroll-20261016/主播月度薪酬核算示例.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工月薪汇总" sheetId="1" r:id="R1dae1ec5850040b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度核算明细" sheetId="2" r:id="R659c32a78bc341ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐规则计算" sheetId="3" r:id="Ra03d76b14aa24925"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工月薪汇总" sheetId="1" r:id="R935bdee531184d94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度核算明细" sheetId="2" r:id="R59493bec8922432e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐规则计算" sheetId="3" r:id="R26ce321c546147be"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -705,10 +705,11 @@
     <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -721,6 +722,7 @@
       <x:c r="G1" s="3"/>
       <x:c r="H1" s="3"/>
       <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
     </x:row>
     <x:row r="2" ht="31" customHeight="1">
       <x:c r="A2" s="4" t="str">
@@ -734,6 +736,7 @@
       <x:c r="G2" s="3"/>
       <x:c r="H2" s="3"/>
       <x:c r="I2" s="3"/>
+      <x:c r="J2" s="3"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="5"/>
@@ -745,6 +748,7 @@
       <x:c r="G3" s="5"/>
       <x:c r="H3" s="5"/>
       <x:c r="I3" s="5"/>
+      <x:c r="J3" s="5"/>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -758,6 +762,7 @@
       <x:c r="G4" s="3"/>
       <x:c r="H4" s="3"/>
       <x:c r="I4" s="3"/>
+      <x:c r="J4" s="3"/>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="3"/>
@@ -769,6 +774,7 @@
       <x:c r="G5" s="3"/>
       <x:c r="H5" s="3"/>
       <x:c r="I5" s="3"/>
+      <x:c r="J5" s="3"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
       <x:c r="A6" s="51" t="str">
@@ -786,12 +792,15 @@
       <x:c r="E6" s="52" t="str">
         <x:v>系数后总保费</x:v>
       </x:c>
-      <x:c r="F6" s="53" t="str">
+      <x:c r="F6" s="52" t="str">
+        <x:v>总计绩效金额</x:v>
+      </x:c>
+      <x:c r="G6" s="53" t="str">
         <x:v>总计月薪</x:v>
       </x:c>
-      <x:c r="G6" s="3"/>
       <x:c r="H6" s="3"/>
       <x:c r="I6" s="3"/>
+      <x:c r="J6" s="3"/>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
       <x:c r="A7" s="3" t="str">
@@ -812,13 +821,17 @@
         <x:f>SUMIFS('月度核算明细'!$AS$7:$AS$10,'月度核算明细'!$A$7:$A$10,B7)</x:f>
         <x:v>49000</x:v>
       </x:c>
-      <x:c r="F7" s="89" t="n">
+      <x:c r="F7" s="71" t="n">
         <x:f>SUMIFS('月度核算明细'!$AT$7:$AT$10,'月度核算明细'!$A$7:$A$10,B7)</x:f>
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="G7" s="89" t="n">
+        <x:f>SUMIFS('月度核算明细'!$AU$7:$AU$10,'月度核算明细'!$A$7:$A$10,B7)</x:f>
         <x:v>9530</x:v>
       </x:c>
-      <x:c r="G7" s="90"/>
       <x:c r="H7" s="90"/>
       <x:c r="I7" s="90"/>
+      <x:c r="J7" s="90"/>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
       <x:c r="A8" s="55" t="str">
@@ -839,13 +852,17 @@
         <x:f>SUMIFS('月度核算明细'!$AS$7:$AS$10,'月度核算明细'!$A$7:$A$10,B8)</x:f>
         <x:v>28000</x:v>
       </x:c>
-      <x:c r="F8" s="92" t="n">
+      <x:c r="F8" s="75" t="n">
         <x:f>SUMIFS('月度核算明细'!$AT$7:$AT$10,'月度核算明细'!$A$7:$A$10,B8)</x:f>
+        <x:v>4400</x:v>
+      </x:c>
+      <x:c r="G8" s="92" t="n">
+        <x:f>SUMIFS('月度核算明细'!$AU$7:$AU$10,'月度核算明细'!$A$7:$A$10,B8)</x:f>
         <x:v>4595</x:v>
       </x:c>
-      <x:c r="G8" s="90"/>
       <x:c r="H8" s="90"/>
       <x:c r="I8" s="90"/>
+      <x:c r="J8" s="90"/>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
       <x:c r="A9" s="3" t="str">
@@ -866,13 +883,17 @@
         <x:f>SUMIFS('月度核算明细'!$AS$7:$AS$10,'月度核算明细'!$A$7:$A$10,B9)</x:f>
         <x:v>36000</x:v>
       </x:c>
-      <x:c r="F9" s="89" t="n">
+      <x:c r="F9" s="71" t="n">
         <x:f>SUMIFS('月度核算明细'!$AT$7:$AT$10,'月度核算明细'!$A$7:$A$10,B9)</x:f>
+        <x:v>4400</x:v>
+      </x:c>
+      <x:c r="G9" s="89" t="n">
+        <x:f>SUMIFS('月度核算明细'!$AU$7:$AU$10,'月度核算明细'!$A$7:$A$10,B9)</x:f>
         <x:v>4565</x:v>
       </x:c>
-      <x:c r="G9" s="90"/>
       <x:c r="H9" s="90"/>
       <x:c r="I9" s="90"/>
+      <x:c r="J9" s="90"/>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
       <x:c r="A10" s="80" t="str">
@@ -893,11 +914,15 @@
       </x:c>
       <x:c r="F10" s="94" t="n">
         <x:f>SUM(F7:F9)</x:f>
+        <x:v>17800</x:v>
+      </x:c>
+      <x:c r="G10" s="94" t="n">
+        <x:f>SUM(G7:G9)</x:f>
         <x:v>18690</x:v>
       </x:c>
-      <x:c r="G10" s="90"/>
       <x:c r="H10" s="90"/>
       <x:c r="I10" s="90"/>
+      <x:c r="J10" s="90"/>
     </x:row>
     <x:row r="11" ht="12" customHeight="1">
       <x:c r="A11" s="3"/>
@@ -909,6 +934,7 @@
       <x:c r="G11" s="90"/>
       <x:c r="H11" s="90"/>
       <x:c r="I11" s="90"/>
+      <x:c r="J11" s="90"/>
     </x:row>
     <x:row r="12" ht="12" customHeight="1">
       <x:c r="A12" s="3"/>
@@ -920,6 +946,7 @@
       <x:c r="G12" s="90"/>
       <x:c r="H12" s="90"/>
       <x:c r="I12" s="90"/>
+      <x:c r="J12" s="90"/>
     </x:row>
     <x:row r="13" ht="12" customHeight="1">
       <x:c r="A13" s="3"/>
@@ -931,6 +958,7 @@
       <x:c r="G13" s="90"/>
       <x:c r="H13" s="90"/>
       <x:c r="I13" s="90"/>
+      <x:c r="J13" s="90"/>
     </x:row>
     <x:row r="14" ht="28" customHeight="1">
       <x:c r="A14" s="87" t="str">
@@ -944,6 +972,7 @@
       <x:c r="G14" s="90"/>
       <x:c r="H14" s="90"/>
       <x:c r="I14" s="90"/>
+      <x:c r="J14" s="90"/>
     </x:row>
     <x:row r="15" ht="28" customHeight="1">
       <x:c r="A15" s="6" t="str">
@@ -957,6 +986,7 @@
       <x:c r="G15" s="90"/>
       <x:c r="H15" s="90"/>
       <x:c r="I15" s="90"/>
+      <x:c r="J15" s="90"/>
     </x:row>
     <x:row r="16" ht="40" customHeight="1">
       <x:c r="A16" s="51" t="str">
@@ -975,15 +1005,18 @@
         <x:v>总补贴</x:v>
       </x:c>
       <x:c r="F16" s="52" t="str">
+        <x:v>总计绩效金额</x:v>
+      </x:c>
+      <x:c r="G16" s="52" t="str">
         <x:v>总计月薪</x:v>
       </x:c>
-      <x:c r="G16" s="52" t="str">
+      <x:c r="H16" s="52" t="str">
         <x:v>有效总保费</x:v>
       </x:c>
-      <x:c r="H16" s="52" t="str">
+      <x:c r="I16" s="52" t="str">
         <x:v>有效ROI</x:v>
       </x:c>
-      <x:c r="I16" s="53" t="str">
+      <x:c r="J16" s="53" t="str">
         <x:v>同房主播排名</x:v>
       </x:c>
     </x:row>
@@ -1006,20 +1039,24 @@
         <x:f>'月度核算明细'!AR7</x:f>
         <x:v>450</x:v>
       </x:c>
-      <x:c r="F17" s="89" t="n">
+      <x:c r="F17" s="71" t="n">
         <x:f>'月度核算明细'!AT7</x:f>
+        <x:v>6800</x:v>
+      </x:c>
+      <x:c r="G17" s="89" t="n">
+        <x:f>'月度核算明细'!AU7</x:f>
         <x:v>7250</x:v>
       </x:c>
-      <x:c r="G17" s="71" t="n">
+      <x:c r="H17" s="71" t="n">
         <x:f>'月度核算明细'!AS7</x:f>
         <x:v>40000</x:v>
       </x:c>
-      <x:c r="H17" s="71" t="n">
-        <x:f>IF('月度核算明细'!T7=0,"n.a.",G17/'月度核算明细'!T7)</x:f>
+      <x:c r="I17" s="71" t="n">
+        <x:f>IF('月度核算明细'!T7=0,"n.a.",H17/'月度核算明细'!T7)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I17" s="88" t="n">
-        <x:f>1+COUNTIFS($B$17:$B$20,B17,$H$17:$H$20,"&gt;"&amp;H17)</x:f>
+      <x:c r="J17" s="88" t="n">
+        <x:f>1+COUNTIFS($B$17:$B$20,B17,$I$17:$I$20,"&gt;"&amp;I17)</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1042,20 +1079,24 @@
         <x:f>'月度核算明细'!AR8</x:f>
         <x:v>195</x:v>
       </x:c>
-      <x:c r="F18" s="92" t="n">
+      <x:c r="F18" s="75" t="n">
         <x:f>'月度核算明细'!AT8</x:f>
+        <x:v>4400</x:v>
+      </x:c>
+      <x:c r="G18" s="92" t="n">
+        <x:f>'月度核算明细'!AU8</x:f>
         <x:v>4595</x:v>
       </x:c>
-      <x:c r="G18" s="75" t="n">
+      <x:c r="H18" s="75" t="n">
         <x:f>'月度核算明细'!AS8</x:f>
         <x:v>28000</x:v>
       </x:c>
-      <x:c r="H18" s="75" t="n">
-        <x:f>IF('月度核算明细'!T8=0,"n.a.",G18/'月度核算明细'!T8)</x:f>
+      <x:c r="I18" s="75" t="n">
+        <x:f>IF('月度核算明细'!T8=0,"n.a.",H18/'月度核算明细'!T8)</x:f>
         <x:v>2.8</x:v>
       </x:c>
-      <x:c r="I18" s="91" t="n">
-        <x:f>1+COUNTIFS($B$17:$B$20,B18,$H$17:$H$20,"&gt;"&amp;H18)</x:f>
+      <x:c r="J18" s="91" t="n">
+        <x:f>1+COUNTIFS($B$17:$B$20,B18,$I$17:$I$20,"&gt;"&amp;I18)</x:f>
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -1078,20 +1119,24 @@
         <x:f>'月度核算明细'!AR9</x:f>
         <x:v>165</x:v>
       </x:c>
-      <x:c r="F19" s="89" t="n">
+      <x:c r="F19" s="71" t="n">
         <x:f>'月度核算明细'!AT9</x:f>
+        <x:v>4400</x:v>
+      </x:c>
+      <x:c r="G19" s="89" t="n">
+        <x:f>'月度核算明细'!AU9</x:f>
         <x:v>4565</x:v>
       </x:c>
-      <x:c r="G19" s="71" t="n">
+      <x:c r="H19" s="71" t="n">
         <x:f>'月度核算明细'!AS9</x:f>
         <x:v>36000</x:v>
       </x:c>
-      <x:c r="H19" s="71" t="n">
-        <x:f>IF('月度核算明细'!T9=0,"n.a.",G19/'月度核算明细'!T9)</x:f>
+      <x:c r="I19" s="71" t="n">
+        <x:f>IF('月度核算明细'!T9=0,"n.a.",H19/'月度核算明细'!T9)</x:f>
         <x:v>3.6</x:v>
       </x:c>
-      <x:c r="I19" s="88" t="n">
-        <x:f>1+COUNTIFS($B$17:$B$20,B19,$H$17:$H$20,"&gt;"&amp;H19)</x:f>
+      <x:c r="J19" s="88" t="n">
+        <x:f>1+COUNTIFS($B$17:$B$20,B19,$I$17:$I$20,"&gt;"&amp;I19)</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -1114,20 +1159,24 @@
         <x:f>'月度核算明细'!AR10</x:f>
         <x:v>80</x:v>
       </x:c>
-      <x:c r="F20" s="92" t="n">
+      <x:c r="F20" s="75" t="n">
         <x:f>'月度核算明细'!AT10</x:f>
+        <x:v>2200</x:v>
+      </x:c>
+      <x:c r="G20" s="92" t="n">
+        <x:f>'月度核算明细'!AU10</x:f>
         <x:v>2280</x:v>
       </x:c>
-      <x:c r="G20" s="75" t="n">
+      <x:c r="H20" s="75" t="n">
         <x:f>'月度核算明细'!AS10</x:f>
         <x:v>9000</x:v>
       </x:c>
-      <x:c r="H20" s="75" t="n">
-        <x:f>IF('月度核算明细'!T10=0,"n.a.",G20/'月度核算明细'!T10)</x:f>
+      <x:c r="I20" s="75" t="n">
+        <x:f>IF('月度核算明细'!T10=0,"n.a.",H20/'月度核算明细'!T10)</x:f>
         <x:v>2.25</x:v>
       </x:c>
-      <x:c r="I20" s="91" t="n">
-        <x:f>1+COUNTIFS($B$17:$B$20,B20,$H$17:$H$20,"&gt;"&amp;H20)</x:f>
+      <x:c r="J20" s="91" t="n">
+        <x:f>1+COUNTIFS($B$17:$B$20,B20,$I$17:$I$20,"&gt;"&amp;I20)</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1141,6 +1190,7 @@
       <x:c r="G21" s="3"/>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
+      <x:c r="J21" s="3"/>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="3"/>
@@ -1152,10 +1202,11 @@
       <x:c r="G22" s="3"/>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
+      <x:c r="J22" s="3"/>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="6" t="str">
-        <x:v>每行月薪 = MAX（全局与直播间保底最大值，两类加成合计）+ 总补贴。系数后保费用于ROI与排名。</x:v>
+        <x:v>总计绩效金额 = MAX（全局与直播间保底最大值，两类加成合计）；总计月薪 = 总计绩效金额 + 总补贴。</x:v>
       </x:c>
       <x:c r="B23" s="3"/>
       <x:c r="C23" s="3"/>
@@ -1165,6 +1216,7 @@
       <x:c r="G23" s="3"/>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
+      <x:c r="J23" s="3"/>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="6" t="str">
@@ -1178,6 +1230,7 @@
       <x:c r="G24" s="3"/>
       <x:c r="H24" s="3"/>
       <x:c r="I24" s="3"/>
+      <x:c r="J24" s="3"/>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="6" t="str">
@@ -1191,6 +1244,7 @@
       <x:c r="G25" s="3"/>
       <x:c r="H25" s="3"/>
       <x:c r="I25" s="3"/>
+      <x:c r="J25" s="3"/>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="6" t="str">
@@ -1204,6 +1258,7 @@
       <x:c r="G26" s="3"/>
       <x:c r="H26" s="3"/>
       <x:c r="I26" s="3"/>
+      <x:c r="J26" s="3"/>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="6" t="str">
@@ -1217,6 +1272,7 @@
       <x:c r="G27" s="3"/>
       <x:c r="H27" s="3"/>
       <x:c r="I27" s="3"/>
+      <x:c r="J27" s="3"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1276,6 +1332,7 @@
     <x:col min="44" max="44" width="18" hidden="0" customWidth="1"/>
     <x:col min="45" max="45" width="18" hidden="0" customWidth="1"/>
     <x:col min="46" max="46" width="18" hidden="0" customWidth="1"/>
+    <x:col min="47" max="47" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -1325,6 +1382,7 @@
       <x:c r="AR1" s="3"/>
       <x:c r="AS1" s="3"/>
       <x:c r="AT1" s="3"/>
+      <x:c r="AU1" s="3"/>
     </x:row>
     <x:row r="2" ht="31" customHeight="1">
       <x:c r="A2" s="4" t="str">
@@ -1375,6 +1433,7 @@
       <x:c r="AR2" s="3"/>
       <x:c r="AS2" s="3"/>
       <x:c r="AT2" s="3"/>
+      <x:c r="AU2" s="3"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="5"/>
@@ -1423,6 +1482,7 @@
       <x:c r="AR3" s="5"/>
       <x:c r="AS3" s="5"/>
       <x:c r="AT3" s="5"/>
+      <x:c r="AU3" s="5"/>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -1473,6 +1533,7 @@
       <x:c r="AR4" s="3"/>
       <x:c r="AS4" s="3"/>
       <x:c r="AT4" s="3"/>
+      <x:c r="AU4" s="3"/>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
       <x:c r="A5" s="18" t="str">
@@ -1613,6 +1674,9 @@
       <x:c r="AT5" s="54" t="str">
         <x:v>结果指标</x:v>
       </x:c>
+      <x:c r="AU5" s="54" t="str">
+        <x:v>结果指标</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="15" t="str">
@@ -1750,7 +1814,10 @@
       <x:c r="AS6" s="52" t="str">
         <x:v>系数加成后总计保费</x:v>
       </x:c>
-      <x:c r="AT6" s="53" t="str">
+      <x:c r="AT6" s="52" t="str">
+        <x:v>总计绩效金额</x:v>
+      </x:c>
+      <x:c r="AU6" s="53" t="str">
         <x:v>总计月薪</x:v>
       </x:c>
     </x:row>
@@ -1900,8 +1967,12 @@
         <x:f>MAX(AM7,AQ7)</x:f>
         <x:v>40000</x:v>
       </x:c>
-      <x:c r="AT7" s="77" t="n">
-        <x:f>ROUND(MAX(AK7,AO7,SUM(AL7,AP7))+AR7,2)</x:f>
+      <x:c r="AT7" s="76" t="n">
+        <x:f>ROUND(MAX(AK7,AO7,SUM(AL7,AP7)),2)</x:f>
+        <x:v>6800</x:v>
+      </x:c>
+      <x:c r="AU7" s="77" t="n">
+        <x:f>ROUND(AT7+AR7,2)</x:f>
         <x:v>7250</x:v>
       </x:c>
     </x:row>
@@ -2051,8 +2122,12 @@
         <x:f>MAX(AM8,AQ8)</x:f>
         <x:v>28000</x:v>
       </x:c>
-      <x:c r="AT8" s="77" t="n">
-        <x:f>ROUND(MAX(AK8,AO8,SUM(AL8,AP8))+AR8,2)</x:f>
+      <x:c r="AT8" s="76" t="n">
+        <x:f>ROUND(MAX(AK8,AO8,SUM(AL8,AP8)),2)</x:f>
+        <x:v>4400</x:v>
+      </x:c>
+      <x:c r="AU8" s="77" t="n">
+        <x:f>ROUND(AT8+AR8,2)</x:f>
         <x:v>4595</x:v>
       </x:c>
     </x:row>
@@ -2202,8 +2277,12 @@
         <x:f>MAX(AM9,AQ9)</x:f>
         <x:v>36000</x:v>
       </x:c>
-      <x:c r="AT9" s="77" t="n">
-        <x:f>ROUND(MAX(AK9,AO9,SUM(AL9,AP9))+AR9,2)</x:f>
+      <x:c r="AT9" s="76" t="n">
+        <x:f>ROUND(MAX(AK9,AO9,SUM(AL9,AP9)),2)</x:f>
+        <x:v>4400</x:v>
+      </x:c>
+      <x:c r="AU9" s="77" t="n">
+        <x:f>ROUND(AT9+AR9,2)</x:f>
         <x:v>4565</x:v>
       </x:c>
     </x:row>
@@ -2353,8 +2432,12 @@
         <x:f>MAX(AM10,AQ10)</x:f>
         <x:v>9000</x:v>
       </x:c>
-      <x:c r="AT10" s="77" t="n">
-        <x:f>ROUND(MAX(AK10,AO10,SUM(AL10,AP10))+AR10,2)</x:f>
+      <x:c r="AT10" s="76" t="n">
+        <x:f>ROUND(MAX(AK10,AO10,SUM(AL10,AP10)),2)</x:f>
+        <x:v>2200</x:v>
+      </x:c>
+      <x:c r="AU10" s="77" t="n">
+        <x:f>ROUND(AT10+AR10,2)</x:f>
         <x:v>2280</x:v>
       </x:c>
     </x:row>
@@ -2405,6 +2488,7 @@
       <x:c r="AR11" s="3"/>
       <x:c r="AS11" s="3"/>
       <x:c r="AT11" s="3"/>
+      <x:c r="AU11" s="3"/>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="6" t="str">
@@ -2455,6 +2539,7 @@
       <x:c r="AR12" s="3"/>
       <x:c r="AS12" s="3"/>
       <x:c r="AT12" s="3"/>
+      <x:c r="AU12" s="3"/>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="6" t="str">
@@ -2505,6 +2590,7 @@
       <x:c r="AR13" s="3"/>
       <x:c r="AS13" s="3"/>
       <x:c r="AT13" s="3"/>
+      <x:c r="AU13" s="3"/>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="6" t="str">
@@ -2555,6 +2641,7 @@
       <x:c r="AR14" s="3"/>
       <x:c r="AS14" s="3"/>
       <x:c r="AT14" s="3"/>
+      <x:c r="AU14" s="3"/>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="3"/>
@@ -2603,13 +2690,14 @@
       <x:c r="AR15" s="3"/>
       <x:c r="AS15" s="3"/>
       <x:c r="AT15" s="3"/>
+      <x:c r="AU15" s="3"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A5:AI5"/>
     <x:mergeCell ref="AJ5:AM5"/>
     <x:mergeCell ref="AN5:AQ5"/>
-    <x:mergeCell ref="AR5:AT5"/>
+    <x:mergeCell ref="AR5:AU5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3182,7 +3270,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H15" s="101" t="n">
-        <x:f>IF(AND('员工月薪汇总'!H17&gt;=0,'员工月薪汇总'!H17&lt;3),20,IF('员工月薪汇总'!H17&gt;=3,45,NA()))</x:f>
+        <x:f>IF(AND('员工月薪汇总'!I17&gt;=0,'员工月薪汇总'!I17&lt;3),20,IF('员工月薪汇总'!I17&gt;=3,45,NA()))</x:f>
         <x:v>45</x:v>
       </x:c>
       <x:c r="I15" s="63" t="n">
@@ -3227,7 +3315,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H16" s="101" t="n">
-        <x:f>IF(AND('员工月薪汇总'!I17&gt;=1,'员工月薪汇总'!I17&lt;=1),10,IF('员工月薪汇总'!I17&gt;=2,5,NA()))</x:f>
+        <x:f>IF(AND('员工月薪汇总'!J17&gt;=1,'员工月薪汇总'!J17&lt;=1),10,IF('员工月薪汇总'!J17&gt;=2,5,NA()))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="I16" s="65" t="n">
@@ -3824,7 +3912,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H29" s="101" t="n">
-        <x:f>IF(AND('员工月薪汇总'!H18&gt;=0,'员工月薪汇总'!H18&lt;3),20,IF('员工月薪汇总'!H18&gt;=3,45,NA()))</x:f>
+        <x:f>IF(AND('员工月薪汇总'!I18&gt;=0,'员工月薪汇总'!I18&lt;3),20,IF('员工月薪汇总'!I18&gt;=3,45,NA()))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="I29" s="63" t="n">
@@ -3869,7 +3957,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H30" s="101" t="n">
-        <x:f>IF(AND('员工月薪汇总'!I18&gt;=1,'员工月薪汇总'!I18&lt;=1),10,IF('员工月薪汇总'!I18&gt;=2,5,NA()))</x:f>
+        <x:f>IF(AND('员工月薪汇总'!J18&gt;=1,'员工月薪汇总'!J18&lt;=1),10,IF('员工月薪汇总'!J18&gt;=2,5,NA()))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="I30" s="65" t="n">
@@ -4466,7 +4554,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H43" s="101" t="n">
-        <x:f>IF(AND('员工月薪汇总'!H19&gt;=0,'员工月薪汇总'!H19&lt;3),20,IF('员工月薪汇总'!H19&gt;=3,45,NA()))</x:f>
+        <x:f>IF(AND('员工月薪汇总'!I19&gt;=0,'员工月薪汇总'!I19&lt;3),20,IF('员工月薪汇总'!I19&gt;=3,45,NA()))</x:f>
         <x:v>45</x:v>
       </x:c>
       <x:c r="I43" s="63" t="n">
@@ -4511,7 +4599,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H44" s="101" t="n">
-        <x:f>IF(AND('员工月薪汇总'!I19&gt;=1,'员工月薪汇总'!I19&lt;=1),10,IF('员工月薪汇总'!I19&gt;=2,5,NA()))</x:f>
+        <x:f>IF(AND('员工月薪汇总'!J19&gt;=1,'员工月薪汇总'!J19&lt;=1),10,IF('员工月薪汇总'!J19&gt;=2,5,NA()))</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="I44" s="65" t="n">
@@ -5108,7 +5196,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H57" s="101" t="n">
-        <x:f>IF(AND('员工月薪汇总'!H20&gt;=0,'员工月薪汇总'!H20&lt;3),20,IF('员工月薪汇总'!H20&gt;=3,45,NA()))</x:f>
+        <x:f>IF(AND('员工月薪汇总'!I20&gt;=0,'员工月薪汇总'!I20&lt;3),20,IF('员工月薪汇总'!I20&gt;=3,45,NA()))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="I57" s="63" t="n">
@@ -5153,7 +5241,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H58" s="101" t="n">
-        <x:f>IF(AND('员工月薪汇总'!I20&gt;=1,'员工月薪汇总'!I20&lt;=1),10,IF('员工月薪汇总'!I20&gt;=2,5,NA()))</x:f>
+        <x:f>IF(AND('员工月薪汇总'!J20&gt;=1,'员工月薪汇总'!J20&lt;=1),10,IF('员工月薪汇总'!J20&gt;=2,5,NA()))</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="I58" s="65" t="n">
